--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>3.55</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>3.85</v>
+        <v>2.05</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="M21" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.85</v>
+        <v>3.55</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>2.05</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.8</v>
+        <v>3.85</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.78</v>
+        <v>2.17</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.85</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>1.78</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.55</v>
+        <v>1.85</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.05</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.85</v>
+        <v>1.8</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.17</v>
+        <v>1.78</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.8</v>
+        <v>3.85</v>
       </c>
       <c r="M22" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.78</v>
+        <v>2.17</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.55</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.05</v>
+        <v>3.85</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N21" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.08</v>
+        <v>3.85</v>
       </c>
       <c r="M20" t="n">
         <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.85</v>
+        <v>2.08</v>
       </c>
       <c r="M22" t="n">
         <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.85</v>
+        <v>1.8</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.17</v>
+        <v>1.78</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>1.92</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="M21" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.08</v>
+        <v>3.85</v>
       </c>
       <c r="M22" t="n">
         <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G18" t="n">

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>3.47</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="N13" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.78</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N21" t="n">
-        <v>3.8</v>
+        <v>3.92</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.08</v>
+        <v>3.6</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="N20" t="n">
-        <v>3.8</v>
+        <v>1.95</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.6</v>
+        <v>2.11</v>
       </c>
       <c r="M22" t="n">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>3.62</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI26"/>
+  <dimension ref="A1:AI27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46006.65625</v>
+        <v>46006.64583333334</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46006.6875</v>
+        <v>46006.65625</v>
       </c>
     </row>
     <row r="16">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46006.69791666666</v>
+        <v>46006.6875</v>
       </c>
     </row>
     <row r="21">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.41</v>
+        <v>3.04</v>
       </c>
       <c r="N21" t="n">
-        <v>3.92</v>
+        <v>1.95</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>3.41</v>
       </c>
       <c r="N23" t="n">
-        <v>3.85</v>
+        <v>3.92</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46006.70833333334</v>
+        <v>46006.69791666666</v>
       </c>
     </row>
     <row r="24">
@@ -3474,116 +3474,235 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>AFC Bournemouth</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="3" t="n">
+        <v>46006.70833333334</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>17:45</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Portugal Liga NOS</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Porto</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Estrela Amadora</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L26" t="n">
+      <c r="L27" t="n">
         <v>1.16</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M27" t="n">
         <v>7.1</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N27" t="n">
         <v>15</v>
       </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
         <v>1.55</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AB27" t="n">
         <v>2.3</v>
       </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" s="3" t="n">
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="3" t="n">
         <v>46006.73958333334</v>
       </c>
     </row>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3.13</v>
+        <v>3.41</v>
       </c>
       <c r="N22" t="n">
-        <v>3.62</v>
+        <v>3.92</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="M23" t="n">
-        <v>3.41</v>
+        <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>3.92</v>
+        <v>3.62</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G20" t="n">

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.6</v>
+        <v>2.11</v>
       </c>
       <c r="M21" t="n">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="N21" t="n">
-        <v>1.95</v>
+        <v>3.62</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.41</v>
+        <v>3.04</v>
       </c>
       <c r="N22" t="n">
-        <v>3.92</v>
+        <v>1.95</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>3.41</v>
       </c>
       <c r="N23" t="n">
-        <v>3.62</v>
+        <v>3.92</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.85</v>
+        <v>3.55</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>3.27</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>2.07</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.55</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>3.27</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.07</v>
+        <v>3.85</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>2.19</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.11</v>
+        <v>3.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.13</v>
+        <v>3.04</v>
       </c>
       <c r="N21" t="n">
-        <v>3.62</v>
+        <v>1.95</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3.04</v>
+        <v>3.41</v>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>3.92</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="M23" t="n">
-        <v>3.41</v>
+        <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>3.92</v>
+        <v>3.62</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>2.19</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.6</v>
+        <v>2.11</v>
       </c>
       <c r="M21" t="n">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="N21" t="n">
-        <v>1.95</v>
+        <v>3.62</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.41</v>
+        <v>3.04</v>
       </c>
       <c r="N22" t="n">
-        <v>3.92</v>
+        <v>1.95</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>3.41</v>
       </c>
       <c r="N23" t="n">
-        <v>3.62</v>
+        <v>3.92</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>2.19</v>
+        <v>6.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.11</v>
+        <v>3.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.13</v>
+        <v>3.04</v>
       </c>
       <c r="N21" t="n">
-        <v>3.62</v>
+        <v>1.95</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3.04</v>
+        <v>3.41</v>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>3.92</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="M23" t="n">
-        <v>3.41</v>
+        <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>3.92</v>
+        <v>3.62</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.66</v>
+        <v>3.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N16" t="n">
-        <v>4.8</v>
+        <v>2.18</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.6</v>
+        <v>2.11</v>
       </c>
       <c r="M21" t="n">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="N21" t="n">
-        <v>1.95</v>
+        <v>3.62</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.41</v>
+        <v>3.04</v>
       </c>
       <c r="N22" t="n">
-        <v>3.92</v>
+        <v>1.95</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>3.41</v>
       </c>
       <c r="N23" t="n">
-        <v>3.62</v>
+        <v>3.92</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.05</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>2.18</v>
+        <v>6.5</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.1</v>
+        <v>1.66</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>2.19</v>
+        <v>4.8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>6.5</v>
+        <v>2.19</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.66</v>
+        <v>3.05</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>2.18</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>3.13</v>
+        <v>3.41</v>
       </c>
       <c r="N21" t="n">
-        <v>3.62</v>
+        <v>3.92</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.6</v>
+        <v>2.11</v>
       </c>
       <c r="M22" t="n">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>3.62</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.41</v>
+        <v>3.04</v>
       </c>
       <c r="N23" t="n">
-        <v>3.92</v>
+        <v>1.95</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.85</v>
+        <v>3.55</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>3.27</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>2.07</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3685,10 +3685,10 @@
         <v>2.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>6.5</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M18" t="n">
         <v>3.1</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.15</v>
-      </c>
       <c r="N18" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.05</v>
+        <v>1.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>2.18</v>
+        <v>5.9</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.41</v>
+        <v>3.04</v>
       </c>
       <c r="N21" t="n">
-        <v>3.92</v>
+        <v>1.95</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3.13</v>
+        <v>3.41</v>
       </c>
       <c r="N22" t="n">
-        <v>3.62</v>
+        <v>3.92</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>2.11</v>
       </c>
       <c r="M23" t="n">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>1.95</v>
+        <v>3.62</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>3.55</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>3.27</v>
       </c>
       <c r="N25" t="n">
-        <v>3.85</v>
+        <v>2.07</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.55</v>
+        <v>1.85</v>
       </c>
       <c r="M26" t="n">
-        <v>3.27</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>2.07</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>5.9</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="M18" t="n">
         <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
         <v>1.65</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="M19" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="N19" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.5</v>
+        <v>3.05</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>5.9</v>
+        <v>2.18</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="M16" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>5.9</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>5.9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.55</v>
+        <v>3.05</v>
       </c>
       <c r="M19" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>5.2</v>
+        <v>2.18</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.05</v>
+        <v>1.44</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.18</v>
+        <v>6.5</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.1</v>
+        <v>1.55</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>5.2</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.5</v>
+        <v>3.05</v>
       </c>
       <c r="M18" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>5.9</v>
+        <v>2.18</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.05</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N19" t="n">
-        <v>2.18</v>
+        <v>5.9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>6.5</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>3.04</v>
+        <v>3.41</v>
       </c>
       <c r="N21" t="n">
-        <v>1.95</v>
+        <v>3.92</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="M22" t="n">
-        <v>3.41</v>
+        <v>3.13</v>
       </c>
       <c r="N22" t="n">
-        <v>3.92</v>
+        <v>3.62</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.11</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>3.04</v>
       </c>
       <c r="N23" t="n">
-        <v>3.62</v>
+        <v>1.95</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.55</v>
+        <v>3.1</v>
       </c>
       <c r="M16" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>5.2</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.44</v>
+        <v>3.05</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.5</v>
+        <v>2.18</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.05</v>
+        <v>1.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N18" t="n">
-        <v>2.18</v>
+        <v>5.9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="M19" t="n">
         <v>3.65</v>
       </c>
       <c r="N19" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>6.5</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.41</v>
+        <v>3.04</v>
       </c>
       <c r="N21" t="n">
-        <v>3.92</v>
+        <v>1.95</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.04</v>
+        <v>3.41</v>
       </c>
       <c r="N23" t="n">
-        <v>1.95</v>
+        <v>3.92</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.1</v>
+        <v>1.55</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>5.2</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="M17" t="n">
         <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
         <v>1.65</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.55</v>
+        <v>3.05</v>
       </c>
       <c r="M19" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>5.2</v>
+        <v>2.18</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.68</v>
+        <v>1.97</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="M17" t="n">
         <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB17" t="n">
         <v>1.65</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="N18" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.68</v>
+        <v>1.97</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="M19" t="n">
         <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
         <v>1.65</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="N20" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.6</v>
+        <v>2.11</v>
       </c>
       <c r="M21" t="n">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="N21" t="n">
-        <v>1.95</v>
+        <v>3.62</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3.13</v>
+        <v>3.41</v>
       </c>
       <c r="N22" t="n">
-        <v>3.62</v>
+        <v>3.92</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.41</v>
+        <v>3.04</v>
       </c>
       <c r="N23" t="n">
-        <v>3.92</v>
+        <v>1.95</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.55</v>
+        <v>1.85</v>
       </c>
       <c r="M24" t="n">
-        <v>3.27</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.07</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.85</v>
+        <v>3.55</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>3.27</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>2.07</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="M16" t="n">
         <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="M18" t="n">
         <v>3.65</v>
       </c>
       <c r="N18" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.55</v>
+        <v>1.85</v>
       </c>
       <c r="M26" t="n">
-        <v>3.27</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>2.07</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="M16" t="n">
         <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="M17" t="n">
         <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
         <v>1.65</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>5.9</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.44</v>
+        <v>3.05</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>6.5</v>
+        <v>2.18</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.11</v>
+        <v>3.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.13</v>
+        <v>3.04</v>
       </c>
       <c r="N21" t="n">
-        <v>3.62</v>
+        <v>1.95</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>2.11</v>
       </c>
       <c r="M23" t="n">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>1.95</v>
+        <v>3.62</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.55</v>
+        <v>3.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>5.2</v>
+        <v>2.18</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>2.15</v>
+        <v>5.9</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="N18" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="M19" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>5.9</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.05</v>
+        <v>1.44</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.18</v>
+        <v>6.5</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.6</v>
+        <v>2.11</v>
       </c>
       <c r="M21" t="n">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="N21" t="n">
-        <v>1.95</v>
+        <v>3.62</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.41</v>
+        <v>3.04</v>
       </c>
       <c r="N22" t="n">
-        <v>3.92</v>
+        <v>1.95</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>3.41</v>
       </c>
       <c r="N23" t="n">
-        <v>3.62</v>
+        <v>3.92</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,16 +2013,16 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="M16" t="n">
         <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
         <v>1.65</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.5</v>
+        <v>3.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>5.9</v>
+        <v>2.18</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>6.5</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.68</v>
+        <v>1.97</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3.04</v>
+        <v>3.41</v>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>3.92</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.41</v>
+        <v>3.04</v>
       </c>
       <c r="N23" t="n">
-        <v>3.92</v>
+        <v>1.95</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.85</v>
+        <v>3.55</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>3.27</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>2.07</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>5.31</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>5.17</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1858,40 +1858,40 @@
         <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA12" t="n">
         <v>1.9</v>
@@ -1900,22 +1900,22 @@
         <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>5.9</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.05</v>
+        <v>1.44</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>2.18</v>
+        <v>6.5</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.44</v>
+        <v>3.05</v>
       </c>
       <c r="M19" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>6.5</v>
+        <v>2.18</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>5.9</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>3.13</v>
+        <v>3.41</v>
       </c>
       <c r="N21" t="n">
-        <v>3.62</v>
+        <v>3.92</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="M22" t="n">
-        <v>3.41</v>
+        <v>3.13</v>
       </c>
       <c r="N22" t="n">
-        <v>3.92</v>
+        <v>3.62</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.6</v>
+        <v>2.31</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="N4" t="n">
-        <v>5.31</v>
+        <v>3.18</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.31</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="N5" t="n">
-        <v>3.18</v>
+        <v>5.31</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1501,40 +1501,40 @@
         <v>3.47</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA9" t="n">
         <v>1.77</v>
@@ -1543,22 +1543,22 @@
         <v>1.93</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46006.52083333334</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.45</v>
+        <v>1.34</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>8</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>1.75</v>
       </c>
       <c r="P12" t="n">
-        <v>2.12</v>
+        <v>2.53</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="S12" t="n">
-        <v>3.03</v>
+        <v>3.58</v>
       </c>
       <c r="T12" t="n">
-        <v>2.81</v>
+        <v>2.13</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>4.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>2.49</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AF12" t="n">
         <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="M13" t="n">
-        <v>5.9</v>
+        <v>3.56</v>
       </c>
       <c r="N13" t="n">
-        <v>1.15</v>
+        <v>1.61</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.33</v>
+        <v>1.94</v>
       </c>
       <c r="AB13" t="n">
-        <v>3</v>
+        <v>1.76</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.86</v>
+        <v>3.45</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="M14" t="n">
-        <v>3.56</v>
+        <v>5.9</v>
       </c>
       <c r="N14" t="n">
-        <v>1.61</v>
+        <v>1.15</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,16 +2132,16 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.94</v>
+        <v>1.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.76</v>
+        <v>3</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.44</v>
+        <v>3.05</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.5</v>
+        <v>2.18</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.68</v>
+        <v>2.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="M19" t="n">
         <v>3.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
         <v>1.65</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>1.55</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>5.2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="M21" t="n">
-        <v>3.41</v>
+        <v>3.13</v>
       </c>
       <c r="N21" t="n">
-        <v>3.92</v>
+        <v>3.62</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3.13</v>
+        <v>3.41</v>
       </c>
       <c r="N22" t="n">
-        <v>3.62</v>
+        <v>3.92</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -784,7 +784,7 @@
         <v>2.89</v>
       </c>
       <c r="N3" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.31</v>
+        <v>3.56</v>
       </c>
       <c r="M4" t="n">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="N4" t="n">
-        <v>3.18</v>
+        <v>1.97</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.56</v>
+        <v>2.31</v>
       </c>
       <c r="M6" t="n">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="N6" t="n">
-        <v>1.97</v>
+        <v>3.19</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="M13" t="n">
-        <v>3.56</v>
+        <v>5.9</v>
       </c>
       <c r="N13" t="n">
-        <v>1.61</v>
+        <v>1.15</v>
       </c>
       <c r="O13" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.94</v>
+        <v>1.33</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.76</v>
+        <v>3</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.45</v>
+        <v>1.86</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.84</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="M14" t="n">
-        <v>5.9</v>
+        <v>3.56</v>
       </c>
       <c r="N14" t="n">
-        <v>1.15</v>
+        <v>1.61</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.33</v>
+        <v>1.94</v>
       </c>
       <c r="AB14" t="n">
-        <v>3</v>
+        <v>1.76</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.86</v>
+        <v>3.45</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2453,40 +2453,40 @@
         <v>2.18</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA17" t="n">
         <v>2.08</v>
@@ -2495,22 +2495,22 @@
         <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.44</v>
       </c>
-      <c r="M18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N19" t="n">
-        <v>2.15</v>
+        <v>5.9</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2810,40 +2810,40 @@
         <v>5.2</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA20" t="n">
         <v>1.95</v>
@@ -2852,22 +2852,22 @@
         <v>1.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>3.13</v>
+        <v>3.41</v>
       </c>
       <c r="N21" t="n">
-        <v>3.62</v>
+        <v>3.92</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.41</v>
+        <v>3.04</v>
       </c>
       <c r="N22" t="n">
-        <v>3.92</v>
+        <v>1.95</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>2.11</v>
       </c>
       <c r="M23" t="n">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>1.95</v>
+        <v>3.62</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.56</v>
+        <v>1.6</v>
       </c>
       <c r="M4" t="n">
-        <v>3.12</v>
+        <v>3.35</v>
       </c>
       <c r="N4" t="n">
-        <v>1.97</v>
+        <v>5.31</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>2.31</v>
       </c>
       <c r="M5" t="n">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>5.31</v>
+        <v>3.19</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.31</v>
+        <v>3.56</v>
       </c>
       <c r="M6" t="n">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="N6" t="n">
-        <v>3.19</v>
+        <v>1.97</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.45</v>
+        <v>1.34</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="N11" t="n">
-        <v>2.75</v>
+        <v>8</v>
       </c>
       <c r="O11" t="n">
-        <v>2.8</v>
+        <v>1.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.12</v>
+        <v>2.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>3.03</v>
+        <v>3.58</v>
       </c>
       <c r="T11" t="n">
-        <v>2.81</v>
+        <v>2.13</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>4.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>2.49</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AF11" t="n">
         <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.34</v>
+        <v>2.45</v>
       </c>
       <c r="M12" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>8</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>2.53</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V12" t="n">
         <v>6.5</v>
       </c>
-      <c r="R12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.55</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.49</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AF12" t="n">
         <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.04</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.68</v>
+        <v>1.97</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46006.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>6</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z18" t="n">
         <v>3.1</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="O18" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.55</v>
-      </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.55</v>
+        <v>3.14</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.33</v>
+        <v>2.38</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.55</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>5.2</v>
+        <v>2.15</v>
       </c>
       <c r="O20" t="n">
-        <v>2.05</v>
+        <v>4.11</v>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>3.01</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>2.76</v>
+        <v>2.45</v>
       </c>
       <c r="T20" t="n">
-        <v>2.79</v>
+        <v>3.42</v>
       </c>
       <c r="U20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.36</v>
       </c>
-      <c r="V20" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH20" t="n">
-        <v>2.38</v>
+        <v>1.33</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.41</v>
+        <v>3.04</v>
       </c>
       <c r="N21" t="n">
-        <v>3.92</v>
+        <v>1.95</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.6</v>
+        <v>2.11</v>
       </c>
       <c r="M22" t="n">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>3.62</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>3.41</v>
       </c>
       <c r="N23" t="n">
-        <v>3.62</v>
+        <v>3.92</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.6</v>
+        <v>2.31</v>
       </c>
       <c r="M4" t="n">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="N4" t="n">
-        <v>5.31</v>
+        <v>3.19</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.31</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="N5" t="n">
-        <v>3.19</v>
+        <v>5.31</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1519,7 +1519,7 @@
         <v>2.55</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V9" t="n">
         <v>6</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="M13" t="n">
-        <v>5.9</v>
+        <v>3.56</v>
       </c>
       <c r="N13" t="n">
-        <v>1.15</v>
+        <v>1.61</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.33</v>
+        <v>1.94</v>
       </c>
       <c r="AB13" t="n">
-        <v>3</v>
+        <v>1.76</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.86</v>
+        <v>3.45</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="M14" t="n">
-        <v>3.56</v>
+        <v>5.9</v>
       </c>
       <c r="N14" t="n">
-        <v>1.61</v>
+        <v>1.15</v>
       </c>
       <c r="O14" t="n">
-        <v>5.83</v>
+        <v>7.5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.14</v>
+        <v>2.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.19</v>
+        <v>1.65</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="S14" t="n">
-        <v>2.66</v>
+        <v>3.42</v>
       </c>
       <c r="T14" t="n">
-        <v>2.95</v>
+        <v>2.1</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5</v>
+        <v>4.45</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
         <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.2</v>
+        <v>4.95</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.94</v>
+        <v>1.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.76</v>
+        <v>3</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.45</v>
+        <v>1.86</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.84</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2215,40 +2215,40 @@
         <v>7.3</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA15" t="n">
         <v>2.1</v>
@@ -2257,22 +2257,22 @@
         <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46006.65625</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.5</v>
+        <v>4.81</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="S16" t="n">
-        <v>2.69</v>
+        <v>3.36</v>
       </c>
       <c r="T16" t="n">
-        <v>2.92</v>
+        <v>2.45</v>
       </c>
       <c r="U16" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="V16" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.97</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.42</v>
+        <v>2.57</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.23</v>
+        <v>1.46</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.29</v>
+        <v>1.84</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.51</v>
+        <v>1.91</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="N19" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.68</v>
+        <v>1.97</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2929,40 +2929,40 @@
         <v>1.95</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA21" t="n">
         <v>2.17</v>
@@ -2971,22 +2971,22 @@
         <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3.13</v>
+        <v>3.41</v>
       </c>
       <c r="N22" t="n">
-        <v>3.62</v>
+        <v>3.92</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="M23" t="n">
-        <v>3.41</v>
+        <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>3.92</v>
+        <v>3.62</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.85</v>
+        <v>3.55</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>3.27</v>
       </c>
       <c r="N24" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC24" t="n">
         <v>3.85</v>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AD24" t="n">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.55</v>
+        <v>1.85</v>
       </c>
       <c r="M26" t="n">
-        <v>3.27</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>2.07</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3643,40 +3643,40 @@
         <v>15</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA27" t="n">
         <v>1.55</v>
@@ -3691,16 +3691,16 @@
         <v>1.55</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46006.73958333334</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>3.56</v>
       </c>
       <c r="M5" t="n">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="N5" t="n">
-        <v>5.31</v>
+        <v>1.97</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.56</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3.12</v>
+        <v>3.35</v>
       </c>
       <c r="N6" t="n">
-        <v>1.97</v>
+        <v>5.31</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1501,25 +1501,25 @@
         <v>3.47</v>
       </c>
       <c r="O9" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
         <v>2.77</v>
       </c>
       <c r="T9" t="n">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="U9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
         <v>6</v>
@@ -1543,7 +1543,7 @@
         <v>1.93</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
         <v>1.3</v>
@@ -1555,10 +1555,10 @@
         <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46006.52083333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="M10" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="N10" t="n">
-        <v>9.75</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S10" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="U10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V10" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.37</v>
+        <v>3.2</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="M11" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>9.75</v>
       </c>
       <c r="O11" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="P11" t="n">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="T11" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V11" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.49</v>
+        <v>2.39</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.2</v>
+        <v>3.37</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1870,16 +1870,16 @@
         <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>3.03</v>
+        <v>2.73</v>
       </c>
       <c r="T12" t="n">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="U12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="W12" t="n">
         <v>1.1</v>
@@ -1891,7 +1891,7 @@
         <v>1.27</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AA12" t="n">
         <v>1.9</v>
@@ -1903,16 +1903,16 @@
         <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
         <v>1.6</v>
@@ -1977,19 +1977,19 @@
         <v>1.61</v>
       </c>
       <c r="O13" t="n">
-        <v>5.83</v>
+        <v>4.8</v>
       </c>
       <c r="P13" t="n">
         <v>2.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="T13" t="n">
         <v>2.95</v>
@@ -2001,10 +2001,10 @@
         <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
         <v>1.31</v>
@@ -2105,16 +2105,16 @@
         <v>1.65</v>
       </c>
       <c r="R14" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S14" t="n">
         <v>3.42</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="U14" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V14" t="n">
         <v>4.45</v>
@@ -2126,10 +2126,10 @@
         <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="AA14" t="n">
         <v>1.33</v>
@@ -2150,10 +2150,10 @@
         <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2218,37 +2218,37 @@
         <v>2.05</v>
       </c>
       <c r="P15" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
         <v>6.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="S15" t="n">
         <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="U15" t="n">
         <v>1.31</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y15" t="n">
         <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AA15" t="n">
         <v>2.1</v>
@@ -2257,22 +2257,22 @@
         <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AD15" t="n">
         <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46006.65625</v>
@@ -2340,22 +2340,22 @@
         <v>2.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.81</v>
+        <v>6.1</v>
       </c>
       <c r="R16" t="n">
         <v>1.31</v>
       </c>
       <c r="S16" t="n">
-        <v>3.36</v>
+        <v>3.15</v>
       </c>
       <c r="T16" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="U16" t="n">
         <v>1.48</v>
       </c>
       <c r="V16" t="n">
-        <v>5.8</v>
+        <v>5.45</v>
       </c>
       <c r="W16" t="n">
         <v>1.08</v>
@@ -2376,10 +2376,10 @@
         <v>2.05</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AE16" t="n">
         <v>1.84</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="M17" t="n">
         <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="O17" t="n">
-        <v>4.14</v>
+        <v>3.8</v>
       </c>
       <c r="P17" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.93</v>
+        <v>3.04</v>
       </c>
       <c r="R17" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="T17" t="n">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="U17" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="V17" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
         <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.55</v>
+        <v>3.05</v>
       </c>
       <c r="M18" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>5.2</v>
+        <v>2.18</v>
       </c>
       <c r="O18" t="n">
-        <v>2.05</v>
+        <v>4.14</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="S18" t="n">
-        <v>2.76</v>
+        <v>2.39</v>
       </c>
       <c r="T18" t="n">
-        <v>2.79</v>
+        <v>3.28</v>
       </c>
       <c r="U18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V18" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.36</v>
       </c>
-      <c r="V18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH18" t="n">
-        <v>2.38</v>
+        <v>1.3</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2694,7 +2694,7 @@
         <v>1.85</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="Q19" t="n">
         <v>7.5</v>
@@ -2703,10 +2703,10 @@
         <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.92</v>
+        <v>3.01</v>
       </c>
       <c r="U19" t="n">
         <v>1.34</v>
@@ -2715,16 +2715,16 @@
         <v>7.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AA19" t="n">
         <v>1.97</v>
@@ -2736,19 +2736,19 @@
         <v>3.42</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
         <v>2.29</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>1.55</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P20" t="n">
         <v>2.15</v>
       </c>
-      <c r="O20" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.87</v>
-      </c>
       <c r="Q20" t="n">
-        <v>3.01</v>
+        <v>6.61</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="S20" t="n">
-        <v>2.45</v>
+        <v>2.71</v>
       </c>
       <c r="T20" t="n">
-        <v>3.42</v>
+        <v>2.73</v>
       </c>
       <c r="U20" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="V20" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
         <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.55</v>
+        <v>3.05</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.33</v>
+        <v>2.38</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.6</v>
+        <v>2.11</v>
       </c>
       <c r="M21" t="n">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="N21" t="n">
-        <v>1.95</v>
+        <v>3.62</v>
       </c>
       <c r="O21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q21" t="n">
         <v>4</v>
       </c>
-      <c r="P21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.46</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S21" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="T21" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.19</v>
+        <v>1.72</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3051,7 +3051,7 @@
         <v>2.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
         <v>4</v>
@@ -3066,7 +3066,7 @@
         <v>2.62</v>
       </c>
       <c r="U22" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V22" t="n">
         <v>5.95</v>
@@ -3075,13 +3075,13 @@
         <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
         <v>1.26</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="AA22" t="n">
         <v>1.77</v>
@@ -3093,7 +3093,7 @@
         <v>3.02</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE22" t="n">
         <v>1.7</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.11</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>3.04</v>
       </c>
       <c r="N23" t="n">
-        <v>3.62</v>
+        <v>1.95</v>
       </c>
       <c r="O23" t="n">
-        <v>2.88</v>
+        <v>4.7</v>
       </c>
       <c r="P23" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="R23" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="S23" t="n">
-        <v>2.67</v>
+        <v>2.47</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U23" t="n">
         <v>1.31</v>
       </c>
       <c r="V23" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3295,7 +3295,7 @@
         <v>3.01</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S24" t="n">
         <v>2.56</v>
@@ -3304,7 +3304,7 @@
         <v>2.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="V24" t="n">
         <v>6.5</v>
@@ -3313,13 +3313,13 @@
         <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
         <v>1.31</v>
       </c>
       <c r="Z24" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AA24" t="n">
         <v>2.03</v>
@@ -3337,7 +3337,7 @@
         <v>1.81</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG24" t="n">
         <v>1.36</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3643,13 +3643,13 @@
         <v>15</v>
       </c>
       <c r="O27" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="P27" t="n">
         <v>2.68</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R27" t="n">
         <v>1.25</v>
@@ -3658,7 +3658,7 @@
         <v>3.4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="U27" t="n">
         <v>1.53</v>
@@ -3676,7 +3676,7 @@
         <v>1.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="AA27" t="n">
         <v>1.55</v>
@@ -3691,7 +3691,7 @@
         <v>1.55</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AF27" t="n">
         <v>1.53</v>
@@ -3700,7 +3700,7 @@
         <v>1.11</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.68</v>
+        <v>4.4</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46006.73958333334</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.31</v>
+        <v>3.56</v>
       </c>
       <c r="M4" t="n">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="N4" t="n">
-        <v>3.19</v>
+        <v>1.97</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.56</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3.12</v>
+        <v>3.35</v>
       </c>
       <c r="N5" t="n">
-        <v>1.97</v>
+        <v>5.31</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.6</v>
+        <v>2.31</v>
       </c>
       <c r="M6" t="n">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="N6" t="n">
-        <v>5.31</v>
+        <v>3.19</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1611,19 +1611,19 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M10" t="n">
-        <v>5.2</v>
+        <v>4.75</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="O10" t="n">
         <v>1.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="Q10" t="n">
         <v>6.5</v>
@@ -1635,10 +1635,10 @@
         <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="U10" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="V10" t="n">
         <v>4.55</v>
@@ -1650,13 +1650,13 @@
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z10" t="n">
         <v>5.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB10" t="n">
         <v>2.49</v>
@@ -1674,7 +1674,7 @@
         <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AH10" t="n">
         <v>3.2</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.27</v>
       </c>
-      <c r="M11" t="n">
-        <v>6</v>
-      </c>
-      <c r="N11" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Z11" t="n">
-        <v>4.8</v>
+        <v>3.14</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.51</v>
+        <v>1.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.39</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.37</v>
+        <v>1.6</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.45</v>
+        <v>1.23</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>9.75</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>1.69</v>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>7.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="S12" t="n">
-        <v>2.73</v>
+        <v>3.34</v>
       </c>
       <c r="T12" t="n">
-        <v>2.62</v>
+        <v>2.27</v>
       </c>
       <c r="U12" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="V12" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.14</v>
+        <v>5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.9</v>
+        <v>1.51</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>3.05</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>6.5</v>
+        <v>2.18</v>
       </c>
       <c r="O16" t="n">
-        <v>1.91</v>
+        <v>4.14</v>
       </c>
       <c r="P16" t="n">
-        <v>2.38</v>
+        <v>1.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.1</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="S16" t="n">
-        <v>3.15</v>
+        <v>2.39</v>
       </c>
       <c r="T16" t="n">
-        <v>2.47</v>
+        <v>3.28</v>
       </c>
       <c r="U16" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="V16" t="n">
-        <v>5.45</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
         <v>1.08</v>
       </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
       <c r="Y16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46006.6875</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>2.15</v>
+        <v>5.9</v>
       </c>
       <c r="O17" t="n">
-        <v>3.8</v>
+        <v>1.85</v>
       </c>
       <c r="P17" t="n">
-        <v>1.98</v>
+        <v>2.29</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.04</v>
+        <v>7.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC17" t="n">
         <v>3.42</v>
       </c>
-      <c r="U17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.12</v>
+        <v>2.29</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.33</v>
+        <v>2.75</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="M18" t="n">
         <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
-        <v>4.14</v>
+        <v>3.8</v>
       </c>
       <c r="P18" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="R18" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="T18" t="n">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="U18" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="V18" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W18" t="n">
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
         <v>1.65</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AG18" t="n">
         <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="P19" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="T19" t="n">
-        <v>3.01</v>
+        <v>2.47</v>
       </c>
       <c r="U19" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="V19" t="n">
-        <v>7.5</v>
+        <v>5.45</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="Z19" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.42</v>
+        <v>2.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.29</v>
+        <v>1.84</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AG19" t="n">
         <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.11</v>
+        <v>3.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.13</v>
+        <v>3.04</v>
       </c>
       <c r="N21" t="n">
-        <v>3.62</v>
+        <v>1.95</v>
       </c>
       <c r="O21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2.63</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V21" t="n">
+        <v>9</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC21" t="n">
         <v>4</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U21" t="n">
+      <c r="AD21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.33</v>
       </c>
-      <c r="V21" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.72</v>
+        <v>1.24</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>2.11</v>
       </c>
       <c r="M23" t="n">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>1.95</v>
+        <v>3.62</v>
       </c>
       <c r="O23" t="n">
-        <v>4.7</v>
+        <v>2.63</v>
       </c>
       <c r="P23" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="T23" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="U23" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.24</v>
+        <v>1.72</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.55</v>
+        <v>1.85</v>
       </c>
       <c r="M24" t="n">
-        <v>3.27</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.07</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
-        <v>3.55</v>
+        <v>2.3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.01</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="S24" t="n">
-        <v>2.56</v>
+        <v>3.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="U24" t="n">
-        <v>1.32</v>
+        <v>1.61</v>
       </c>
       <c r="V24" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.94</v>
+        <v>4.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.85</v>
+        <v>2.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.87</v>
+        <v>2.37</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>3.55</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>3.27</v>
       </c>
       <c r="N25" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC25" t="n">
         <v>3.85</v>
       </c>
-      <c r="O25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V25" t="n">
-        <v>5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AD25" t="n">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.37</v>
+        <v>1.87</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.56</v>
+        <v>2.31</v>
       </c>
       <c r="M4" t="n">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="N4" t="n">
-        <v>1.97</v>
+        <v>3.19</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>3.56</v>
       </c>
       <c r="M5" t="n">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="N5" t="n">
-        <v>5.31</v>
+        <v>1.97</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.31</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="N6" t="n">
-        <v>3.19</v>
+        <v>5.31</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="M13" t="n">
-        <v>3.56</v>
+        <v>5.9</v>
       </c>
       <c r="N13" t="n">
-        <v>1.61</v>
+        <v>1.15</v>
       </c>
       <c r="O13" t="n">
-        <v>4.8</v>
+        <v>7.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.14</v>
+        <v>2.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>2.84</v>
+        <v>3.42</v>
       </c>
       <c r="T13" t="n">
-        <v>2.95</v>
+        <v>2.16</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>4.45</v>
       </c>
       <c r="W13" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.94</v>
+        <v>1.33</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.76</v>
+        <v>3</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.45</v>
+        <v>1.86</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.84</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="M14" t="n">
-        <v>5.9</v>
+        <v>3.56</v>
       </c>
       <c r="N14" t="n">
-        <v>1.15</v>
+        <v>1.61</v>
       </c>
       <c r="O14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V14" t="n">
         <v>7.5</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V14" t="n">
-        <v>4.45</v>
-      </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="Z14" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.33</v>
+        <v>1.94</v>
       </c>
       <c r="AB14" t="n">
-        <v>3</v>
+        <v>1.76</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.86</v>
+        <v>3.45</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="P17" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="T17" t="n">
-        <v>3.01</v>
+        <v>2.47</v>
       </c>
       <c r="U17" t="n">
-        <v>1.34</v>
+        <v>1.48</v>
       </c>
       <c r="V17" t="n">
-        <v>7.5</v>
+        <v>5.45</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.42</v>
+        <v>2.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.29</v>
+        <v>1.84</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AG17" t="n">
         <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>5.9</v>
       </c>
       <c r="O18" t="n">
-        <v>3.8</v>
+        <v>1.85</v>
       </c>
       <c r="P18" t="n">
-        <v>1.98</v>
+        <v>2.29</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.04</v>
+        <v>7.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC18" t="n">
         <v>3.42</v>
       </c>
-      <c r="U18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.12</v>
+        <v>2.29</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.33</v>
+        <v>2.75</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.44</v>
       </c>
-      <c r="M19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z19" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.7</v>
+        <v>1.33</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>3.04</v>
+        <v>3.41</v>
       </c>
       <c r="N21" t="n">
-        <v>1.95</v>
+        <v>3.92</v>
       </c>
       <c r="O21" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.47</v>
+        <v>2.89</v>
       </c>
       <c r="T21" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="U21" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>9</v>
+        <v>5.95</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AC21" t="n">
-        <v>4</v>
+        <v>3.02</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AE21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.24</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="M22" t="n">
-        <v>3.41</v>
+        <v>3.13</v>
       </c>
       <c r="N22" t="n">
-        <v>3.92</v>
+        <v>3.62</v>
       </c>
       <c r="O22" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="Q22" t="n">
         <v>4</v>
       </c>
       <c r="R22" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.36</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V22" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.26</v>
-      </c>
       <c r="Z22" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.02</v>
+        <v>4.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.11</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>3.04</v>
       </c>
       <c r="N23" t="n">
-        <v>3.62</v>
+        <v>1.95</v>
       </c>
       <c r="O23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q23" t="n">
         <v>2.63</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V23" t="n">
+        <v>9</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC23" t="n">
         <v>4</v>
       </c>
-      <c r="R23" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U23" t="n">
+      <c r="AD23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.33</v>
       </c>
-      <c r="V23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.72</v>
+        <v>1.24</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.85</v>
+        <v>2.51</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>2.6</v>
       </c>
       <c r="O24" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="P24" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="R24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AD24" t="n">
         <v>1.28</v>
       </c>
-      <c r="S24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V24" t="n">
-        <v>5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AE24" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.37</v>
+        <v>2.13</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.51</v>
+        <v>1.85</v>
       </c>
       <c r="M26" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="P26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V26" t="n">
+        <v>5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC26" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q26" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V26" t="n">
-        <v>7</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB26" t="n">
+      <c r="AD26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.55</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.31</v>
+        <v>3.56</v>
       </c>
       <c r="M4" t="n">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="N4" t="n">
-        <v>3.19</v>
+        <v>1.97</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.56</v>
+        <v>2.31</v>
       </c>
       <c r="M5" t="n">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>1.97</v>
+        <v>3.19</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,37 +1611,37 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="M10" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="N10" t="n">
-        <v>6.2</v>
+        <v>9.75</v>
       </c>
       <c r="O10" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="P10" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="S10" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="T10" t="n">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="U10" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="V10" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="W10" t="n">
         <v>1.13</v>
@@ -1650,34 +1650,34 @@
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="N12" t="n">
-        <v>9.75</v>
+        <v>6.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="P12" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="T12" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="V12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.05</v>
+        <v>1.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>2.18</v>
+        <v>5.9</v>
       </c>
       <c r="O16" t="n">
-        <v>4.14</v>
+        <v>1.85</v>
       </c>
       <c r="P16" t="n">
-        <v>1.88</v>
+        <v>2.29</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>3.28</v>
+        <v>3.01</v>
       </c>
       <c r="U16" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="V16" t="n">
-        <v>9.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.2</v>
+        <v>3.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.3</v>
+        <v>2.75</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46006.6875</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.44</v>
+        <v>3.05</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.5</v>
+        <v>2.18</v>
       </c>
       <c r="O17" t="n">
-        <v>1.91</v>
+        <v>4.14</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.1</v>
+        <v>2.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="S17" t="n">
-        <v>3.15</v>
+        <v>2.39</v>
       </c>
       <c r="T17" t="n">
-        <v>2.47</v>
+        <v>3.28</v>
       </c>
       <c r="U17" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="V17" t="n">
-        <v>5.45</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
         <v>1.08</v>
       </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
       <c r="Y17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="M18" t="n">
         <v>3.65</v>
       </c>
       <c r="N18" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="P18" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.5</v>
+        <v>6.61</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="T18" t="n">
-        <v>3.01</v>
+        <v>2.73</v>
       </c>
       <c r="U18" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="V18" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="N20" t="n">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="O20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB20" t="n">
         <v>2.05</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>6.61</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V20" t="n">
-        <v>7</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC20" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE20" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF20" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.41</v>
+        <v>3.04</v>
       </c>
       <c r="N21" t="n">
-        <v>3.92</v>
+        <v>1.95</v>
       </c>
       <c r="O21" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V21" t="n">
+        <v>9</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC21" t="n">
         <v>4</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.02</v>
-      </c>
       <c r="AD21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.91</v>
+        <v>1.24</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.04</v>
+        <v>3.41</v>
       </c>
       <c r="N23" t="n">
-        <v>1.95</v>
+        <v>3.92</v>
       </c>
       <c r="O23" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="P23" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>2.89</v>
       </c>
       <c r="T23" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="U23" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>9</v>
+        <v>5.95</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AC23" t="n">
-        <v>4</v>
+        <v>3.02</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.24</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.56</v>
+        <v>2.31</v>
       </c>
       <c r="M4" t="n">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="N4" t="n">
-        <v>1.97</v>
+        <v>3.19</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.31</v>
+        <v>3.56</v>
       </c>
       <c r="M5" t="n">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="N5" t="n">
-        <v>3.19</v>
+        <v>1.97</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1510,10 +1510,10 @@
         <v>3.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S9" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
         <v>2.69</v>
@@ -1531,7 +1531,7 @@
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
         <v>3.5</v>
@@ -1549,16 +1549,16 @@
         <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AF9" t="n">
         <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46006.52083333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="M10" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="N10" t="n">
-        <v>9.75</v>
+        <v>6.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="V10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.45</v>
+        <v>1.23</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="N11" t="n">
-        <v>2.75</v>
+        <v>9.75</v>
       </c>
       <c r="O11" t="n">
-        <v>2.8</v>
+        <v>1.69</v>
       </c>
       <c r="P11" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.5</v>
+        <v>7.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>2.73</v>
+        <v>3.34</v>
       </c>
       <c r="T11" t="n">
-        <v>2.62</v>
+        <v>2.27</v>
       </c>
       <c r="U11" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="V11" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.14</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.9</v>
+        <v>1.51</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>2.45</v>
       </c>
       <c r="M12" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V12" t="n">
         <v>6.5</v>
       </c>
-      <c r="O12" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>7</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.5</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.4</v>
+        <v>3.22</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.46</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.12</v>
+        <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.66</v>
+        <v>1.26</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF12" t="n">
         <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.95</v>
+        <v>1.6</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1977,7 +1977,7 @@
         <v>1.15</v>
       </c>
       <c r="O13" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="P13" t="n">
         <v>2.75</v>
@@ -1986,16 +1986,16 @@
         <v>1.65</v>
       </c>
       <c r="R13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S13" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="T13" t="n">
         <v>2.16</v>
       </c>
       <c r="U13" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="V13" t="n">
         <v>4.45</v>
@@ -2004,13 +2004,13 @@
         <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA13" t="n">
         <v>1.33</v>
@@ -2031,10 +2031,10 @@
         <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2096,13 +2096,13 @@
         <v>1.61</v>
       </c>
       <c r="O14" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="P14" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="R14" t="n">
         <v>1.36</v>
@@ -2111,7 +2111,7 @@
         <v>2.84</v>
       </c>
       <c r="T14" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
         <v>1.36</v>
@@ -2123,7 +2123,7 @@
         <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
         <v>1.31</v>
@@ -2153,7 +2153,7 @@
         <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2215,7 +2215,7 @@
         <v>7.3</v>
       </c>
       <c r="O15" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="P15" t="n">
         <v>2.05</v>
@@ -2224,13 +2224,13 @@
         <v>6.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S15" t="n">
         <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="U15" t="n">
         <v>1.31</v>
@@ -2242,13 +2242,13 @@
         <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AA15" t="n">
         <v>2.1</v>
@@ -2257,22 +2257,22 @@
         <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="AD15" t="n">
         <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46006.65625</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="M16" t="n">
         <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="P16" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="W16" t="n">
         <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z16" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46006.6875</v>
@@ -2453,19 +2453,19 @@
         <v>2.18</v>
       </c>
       <c r="O17" t="n">
-        <v>4.14</v>
+        <v>3.75</v>
       </c>
       <c r="P17" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R17" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="T17" t="n">
         <v>3.28</v>
@@ -2474,19 +2474,19 @@
         <v>1.26</v>
       </c>
       <c r="V17" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AA17" t="n">
         <v>2.08</v>
@@ -2495,16 +2495,16 @@
         <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AD17" t="n">
         <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
         <v>1.36</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.55</v>
+        <v>3.1</v>
       </c>
       <c r="M18" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>5.2</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
-        <v>2.05</v>
+        <v>3.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.61</v>
+        <v>3.01</v>
       </c>
       <c r="R18" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.71</v>
+        <v>2.4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.73</v>
+        <v>3.42</v>
       </c>
       <c r="U18" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.4</v>
+        <v>2.49</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.38</v>
+        <v>1.28</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S19" t="n">
         <v>3.1</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="O19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.31</v>
-      </c>
       <c r="T19" t="n">
-        <v>3.42</v>
+        <v>2.4</v>
       </c>
       <c r="U19" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="V19" t="n">
-        <v>9.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="W19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X19" t="n">
         <v>1</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.33</v>
+        <v>2.7</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="O20" t="n">
         <v>1.96</v>
       </c>
       <c r="P20" t="n">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>7.92</v>
       </c>
       <c r="R20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U20" t="n">
         <v>1.32</v>
       </c>
-      <c r="S20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
+        <v>8</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.53</v>
       </c>
-      <c r="V20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>3.04</v>
+        <v>3.41</v>
       </c>
       <c r="N21" t="n">
-        <v>1.95</v>
+        <v>3.92</v>
       </c>
       <c r="O21" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.47</v>
+        <v>2.88</v>
       </c>
       <c r="T21" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="U21" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X21" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.8</v>
+        <v>3.83</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AC21" t="n">
-        <v>4</v>
+        <v>3.02</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.24</v>
+        <v>1.98</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3048,31 +3048,31 @@
         <v>3.62</v>
       </c>
       <c r="O22" t="n">
-        <v>2.63</v>
+        <v>2.92</v>
       </c>
       <c r="P22" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
         <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="T22" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V22" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
         <v>1.08</v>
@@ -3081,7 +3081,7 @@
         <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AA22" t="n">
         <v>2.15</v>
@@ -3096,16 +3096,16 @@
         <v>1.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG22" t="n">
         <v>1.38</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.41</v>
+        <v>3.04</v>
       </c>
       <c r="N23" t="n">
-        <v>3.92</v>
+        <v>1.95</v>
       </c>
       <c r="O23" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V23" t="n">
+        <v>9</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC23" t="n">
         <v>4</v>
       </c>
-      <c r="R23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V23" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.02</v>
-      </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.91</v>
+        <v>1.24</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.51</v>
+        <v>1.85</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.6</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="P24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V24" t="n">
+        <v>5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC24" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q24" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.24</v>
-      </c>
       <c r="AD24" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.13</v>
+        <v>2.48</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.55</v>
+        <v>2.04</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3423,16 +3423,16 @@
         <v>2.75</v>
       </c>
       <c r="U25" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>6.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W25" t="n">
         <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
         <v>1.31</v>
@@ -3450,13 +3450,13 @@
         <v>3.85</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG25" t="n">
         <v>1.36</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.85</v>
+        <v>2.51</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="R26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V26" t="n">
+        <v>7</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.28</v>
       </c>
-      <c r="S26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V26" t="n">
-        <v>5</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AE26" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.37</v>
+        <v>2.13</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3643,31 +3643,31 @@
         <v>15</v>
       </c>
       <c r="O27" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="P27" t="n">
         <v>2.68</v>
       </c>
       <c r="Q27" t="n">
-        <v>13</v>
+        <v>9.1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S27" t="n">
         <v>3.4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="V27" t="n">
         <v>5.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X27" t="n">
         <v>1.03</v>
@@ -3676,7 +3676,7 @@
         <v>1.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA27" t="n">
         <v>1.55</v>
@@ -3691,16 +3691,16 @@
         <v>1.55</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG27" t="n">
         <v>1.11</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46006.73958333334</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -784,7 +784,7 @@
         <v>2.89</v>
       </c>
       <c r="N3" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.31</v>
+        <v>3.56</v>
       </c>
       <c r="M4" t="n">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="N4" t="n">
-        <v>3.19</v>
+        <v>1.97</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.56</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3.12</v>
+        <v>3.35</v>
       </c>
       <c r="N5" t="n">
-        <v>1.97</v>
+        <v>5.31</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.6</v>
+        <v>2.31</v>
       </c>
       <c r="M6" t="n">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="N6" t="n">
-        <v>5.31</v>
+        <v>3.18</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="M10" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="N10" t="n">
-        <v>6.5</v>
+        <v>9.75</v>
       </c>
       <c r="O10" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="P10" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="S10" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="T10" t="n">
-        <v>2.17</v>
+        <v>2.27</v>
       </c>
       <c r="U10" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="V10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.23</v>
+        <v>2.44</v>
       </c>
       <c r="M11" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>9.75</v>
+        <v>2.95</v>
       </c>
       <c r="O11" t="n">
-        <v>1.69</v>
+        <v>2.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.8</v>
+        <v>3.5</v>
       </c>
       <c r="R11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.26</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U11" t="n">
+      <c r="AE11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.6</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>3.6</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.45</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>6.5</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>1.74</v>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>2.73</v>
+        <v>3.58</v>
       </c>
       <c r="T12" t="n">
-        <v>2.62</v>
+        <v>2.17</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.22</v>
+        <v>5.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.9</v>
+        <v>1.46</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.6</v>
+        <v>2.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.26</v>
+        <v>1.66</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AF12" t="n">
         <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.6</v>
+        <v>2.95</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="M16" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q16" t="n">
         <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z16" t="n">
         <v>2.92</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46006.6875</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="N17" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P17" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.82</v>
+        <v>3.01</v>
       </c>
       <c r="R17" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="T17" t="n">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="U17" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="V17" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.69</v>
+        <v>2.49</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.1</v>
+        <v>1.33</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>8</v>
       </c>
       <c r="O18" t="n">
-        <v>3.8</v>
+        <v>1.96</v>
       </c>
       <c r="P18" t="n">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.01</v>
+        <v>7.92</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC18" t="n">
         <v>3.42</v>
       </c>
-      <c r="U18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.28</v>
+        <v>2.66</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>5.9</v>
+        <v>2.21</v>
       </c>
       <c r="O20" t="n">
-        <v>1.96</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.92</v>
+        <v>2.82</v>
       </c>
       <c r="R20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.4</v>
       </c>
-      <c r="S20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y20" t="n">
+      <c r="Z20" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>2.66</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.85</v>
+        <v>2.51</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>2.6</v>
       </c>
       <c r="O24" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="P24" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>3.38</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z24" t="n">
         <v>3.5</v>
       </c>
-      <c r="T24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V24" t="n">
-        <v>5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AA24" t="n">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.25</v>
+        <v>3.24</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.48</v>
+        <v>2.13</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.04</v>
+        <v>1.55</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.55</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>3.27</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.07</v>
+        <v>3.85</v>
       </c>
       <c r="O25" t="n">
-        <v>3.55</v>
+        <v>2.3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.01</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>2.56</v>
+        <v>3.5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="V25" t="n">
-        <v>8.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.94</v>
+        <v>4.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.85</v>
+        <v>2.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.21</v>
+        <v>1.57</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.91</v>
+        <v>2.48</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.36</v>
+        <v>2.04</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.51</v>
+        <v>3.55</v>
       </c>
       <c r="M26" t="n">
-        <v>3.35</v>
+        <v>3.27</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="O26" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.38</v>
+        <v>3.01</v>
       </c>
       <c r="R26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U26" t="n">
         <v>1.4</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.41</v>
-      </c>
       <c r="V26" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.24</v>
+        <v>3.85</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI27"/>
+  <dimension ref="A1:AI29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.56</v>
+        <v>2.31</v>
       </c>
       <c r="M4" t="n">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="N4" t="n">
-        <v>1.97</v>
+        <v>3.18</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>3.56</v>
       </c>
       <c r="M5" t="n">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="N5" t="n">
-        <v>5.31</v>
+        <v>1.97</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.31</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="N6" t="n">
-        <v>3.18</v>
+        <v>5.31</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
         <v>2.45</v>
@@ -1510,16 +1510,16 @@
         <v>3.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T9" t="n">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V9" t="n">
         <v>6</v>
@@ -1537,10 +1537,10 @@
         <v>3.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
         <v>3.1</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.23</v>
+        <v>2.44</v>
       </c>
       <c r="M10" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>9.75</v>
+        <v>2.95</v>
       </c>
       <c r="O10" t="n">
-        <v>1.69</v>
+        <v>2.8</v>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.8</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.26</v>
       </c>
-      <c r="S10" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U10" t="n">
+      <c r="AE10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.6</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>3.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.44</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="N11" t="n">
-        <v>2.95</v>
+        <v>6.2</v>
       </c>
       <c r="O11" t="n">
-        <v>2.8</v>
+        <v>1.74</v>
       </c>
       <c r="P11" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>2.73</v>
+        <v>3.58</v>
       </c>
       <c r="T11" t="n">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.91</v>
+        <v>1.46</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.2</v>
+        <v>2.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.26</v>
+        <v>1.62</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AF11" t="n">
         <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.6</v>
+        <v>2.99</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="M12" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="N12" t="n">
-        <v>6.5</v>
+        <v>9.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="P12" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="T12" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="V12" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="M13" t="n">
-        <v>5.9</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>1.15</v>
+        <v>1.61</v>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="P13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.16</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>4.45</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.25</v>
+        <v>3.08</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.33</v>
+        <v>1.97</v>
       </c>
       <c r="AB13" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.86</v>
+        <v>3.45</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="M14" t="n">
-        <v>3.56</v>
+        <v>5.9</v>
       </c>
       <c r="N14" t="n">
-        <v>1.61</v>
+        <v>1.15</v>
       </c>
       <c r="O14" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.26</v>
+        <v>1.65</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="S14" t="n">
-        <v>2.84</v>
+        <v>3.42</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5</v>
+        <v>4.45</v>
       </c>
       <c r="W14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.07</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.13</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2206,28 +2206,28 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="O15" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q15" t="n">
         <v>6.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="T15" t="n">
         <v>3.15</v>
@@ -2248,25 +2248,25 @@
         <v>1.35</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC15" t="n">
         <v>3.84</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
         <v>1.09</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="P16" t="n">
         <v>2.09</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.08</v>
-      </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>7.92</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.87</v>
+        <v>2.01</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.91</v>
+        <v>2.29</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46006.6875</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="O17" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.01</v>
+        <v>2.82</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="T17" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="U17" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="V17" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.8</v>
+        <v>4.15</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.28</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.33</v>
+        <v>3.11</v>
       </c>
       <c r="M18" t="n">
-        <v>4.2</v>
+        <v>2.99</v>
       </c>
       <c r="N18" t="n">
-        <v>8</v>
+        <v>2.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.96</v>
+        <v>3.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.92</v>
+        <v>3.01</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AA18" t="n">
         <v>2.5</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y18" t="n">
+      <c r="AB18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z18" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH18" t="n">
-        <v>2.66</v>
+        <v>1.28</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2682,37 +2682,37 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="M19" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="N19" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="O19" t="n">
         <v>1.96</v>
       </c>
       <c r="P19" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
         <v>6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="U19" t="n">
         <v>1.53</v>
       </c>
       <c r="V19" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="W19" t="n">
         <v>1.08</v>
@@ -2727,10 +2727,10 @@
         <v>4.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC19" t="n">
         <v>2.75</v>
@@ -2739,10 +2739,10 @@
         <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AG19" t="n">
         <v>1.22</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V20" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC20" t="n">
         <v>3</v>
       </c>
-      <c r="M20" t="n">
-        <v>3</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="O20" t="n">
-        <v>4</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4.15</v>
-      </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.3</v>
+        <v>2.38</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="M21" t="n">
-        <v>3.41</v>
+        <v>2.97</v>
       </c>
       <c r="N21" t="n">
-        <v>3.92</v>
+        <v>3.45</v>
       </c>
       <c r="O21" t="n">
-        <v>2.3</v>
+        <v>2.92</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
         <v>4</v>
       </c>
       <c r="R21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V21" t="n">
+        <v>9</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.36</v>
       </c>
-      <c r="S21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.26</v>
-      </c>
       <c r="Z21" t="n">
-        <v>3.83</v>
+        <v>3.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.02</v>
+        <v>4.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="M22" t="n">
-        <v>3.13</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>3.62</v>
+        <v>4.1</v>
       </c>
       <c r="O22" t="n">
-        <v>2.92</v>
+        <v>2.45</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
         <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="T22" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="U22" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="V22" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.85</v>
+        <v>3.92</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AF22" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3158,31 +3158,31 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="M23" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="O23" t="n">
         <v>4</v>
       </c>
       <c r="P23" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Q23" t="n">
         <v>2.67</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S23" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="T23" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
         <v>1.35</v>
@@ -3200,10 +3200,10 @@
         <v>1.38</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB23" t="n">
         <v>1.62</v>
@@ -3212,7 +3212,7 @@
         <v>4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE23" t="n">
         <v>1.91</v>
@@ -3221,10 +3221,10 @@
         <v>1.8</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3277,22 +3277,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
         <v>2.6</v>
       </c>
       <c r="O24" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.38</v>
+        <v>3.15</v>
       </c>
       <c r="R24" t="n">
         <v>1.4</v>
@@ -3307,22 +3307,22 @@
         <v>1.41</v>
       </c>
       <c r="V24" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W24" t="n">
         <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
         <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AB24" t="n">
         <v>1.95</v>
@@ -3331,19 +3331,19 @@
         <v>3.24</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE24" t="n">
         <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE25" t="n">
         <v>1.85</v>
       </c>
-      <c r="M25" t="n">
-        <v>4</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>4</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V25" t="n">
-        <v>5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AF25" t="n">
-        <v>2.48</v>
+        <v>1.91</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.04</v>
+        <v>1.36</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.55</v>
+        <v>1.83</v>
       </c>
       <c r="M26" t="n">
-        <v>3.27</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>2.07</v>
+        <v>4</v>
       </c>
       <c r="O26" t="n">
-        <v>3.55</v>
+        <v>2.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.01</v>
+        <v>3.95</v>
       </c>
       <c r="R26" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>2.56</v>
+        <v>3.5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="V26" t="n">
-        <v>8.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.94</v>
+        <v>4.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.03</v>
+        <v>1.57</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>2.38</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.85</v>
+        <v>2.45</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.21</v>
+        <v>1.61</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.91</v>
+        <v>2.48</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3634,22 +3634,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="M27" t="n">
-        <v>7.1</v>
+        <v>6.75</v>
       </c>
       <c r="N27" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O27" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="P27" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
       <c r="R27" t="n">
         <v>1.28</v>
@@ -3673,37 +3673,275 @@
         <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AB27" t="n">
         <v>2.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46006.73958333334</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Spanish Town Police FC</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3" t="n">
+        <v>46006.79166666666</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Arnett Gardens</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Montego Bay United</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3" t="n">
+        <v>46006.89583333334</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.31</v>
+        <v>3.56</v>
       </c>
       <c r="M4" t="n">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="N4" t="n">
-        <v>3.18</v>
+        <v>1.97</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.56</v>
+        <v>2.31</v>
       </c>
       <c r="M5" t="n">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>1.97</v>
+        <v>3.18</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.44</v>
+        <v>1.27</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="N10" t="n">
-        <v>2.95</v>
+        <v>9.75</v>
       </c>
       <c r="O10" t="n">
-        <v>2.8</v>
+        <v>1.69</v>
       </c>
       <c r="P10" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>2.73</v>
+        <v>3.42</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="V10" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.26</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.27</v>
+        <v>2.44</v>
       </c>
       <c r="M12" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>9.75</v>
+        <v>2.95</v>
       </c>
       <c r="O12" t="n">
-        <v>1.69</v>
+        <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.9</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>3.42</v>
+        <v>2.73</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="U12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.6</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>3.6</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>3.11</v>
       </c>
       <c r="M16" t="n">
-        <v>4.2</v>
+        <v>2.99</v>
       </c>
       <c r="N16" t="n">
-        <v>8</v>
+        <v>2.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.96</v>
+        <v>3.8</v>
       </c>
       <c r="P16" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.92</v>
+        <v>3.01</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2.5</v>
       </c>
-      <c r="T16" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V16" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y16" t="n">
+      <c r="AB16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z16" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH16" t="n">
-        <v>2.66</v>
+        <v>1.28</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46006.6875</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>1.44</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.21</v>
+        <v>5.8</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>1.87</v>
       </c>
       <c r="P17" t="n">
-        <v>1.93</v>
+        <v>2.36</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.82</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.48</v>
+        <v>1.34</v>
       </c>
       <c r="S17" t="n">
-        <v>2.36</v>
+        <v>3.36</v>
       </c>
       <c r="T17" t="n">
-        <v>3.28</v>
+        <v>2.47</v>
       </c>
       <c r="U17" t="n">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="V17" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
         <v>1</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z17" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AE17" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.11</v>
+        <v>1.48</v>
       </c>
       <c r="M18" t="n">
-        <v>2.99</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.8</v>
+        <v>2.09</v>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.01</v>
+        <v>6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>2.31</v>
+        <v>2.67</v>
       </c>
       <c r="T18" t="n">
-        <v>3.42</v>
+        <v>2.75</v>
       </c>
       <c r="U18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.24</v>
       </c>
-      <c r="V18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.42</v>
-      </c>
       <c r="Z18" t="n">
-        <v>2.49</v>
+        <v>2.92</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.28</v>
+        <v>2.38</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.38</v>
+        <v>3.2</v>
       </c>
       <c r="M19" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>5.8</v>
+        <v>2.24</v>
       </c>
       <c r="O19" t="n">
-        <v>1.96</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>2.82</v>
       </c>
       <c r="R19" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>2.34</v>
       </c>
       <c r="T19" t="n">
-        <v>2.47</v>
+        <v>3.34</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="V19" t="n">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="AA19" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF19" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="P20" t="n">
         <v>2.09</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.08</v>
-      </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>7.92</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>2.75</v>
+        <v>2.92</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V20" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Z20" t="n">
         <v>2.92</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AC20" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.91</v>
+        <v>2.31</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AG20" t="n">
         <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="M21" t="n">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="O21" t="n">
-        <v>2.92</v>
+        <v>2.45</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
         <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.53</v>
+        <v>2.89</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="U21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.33</v>
       </c>
-      <c r="V21" t="n">
-        <v>9</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="O22" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
         <v>4</v>
       </c>
       <c r="R22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V22" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.36</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.26</v>
-      </c>
       <c r="Z22" t="n">
-        <v>3.92</v>
+        <v>3.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC22" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AF22" t="n">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N24" t="n">
         <v>2.6</v>
@@ -3289,16 +3289,16 @@
         <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="R24" t="n">
         <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.93</v>
+        <v>3.03</v>
       </c>
       <c r="T24" t="n">
         <v>2.89</v>
@@ -3310,13 +3310,13 @@
         <v>7.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
         <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z24" t="n">
         <v>3.45</v>
@@ -3325,7 +3325,7 @@
         <v>1.99</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
         <v>3.24</v>
@@ -3337,7 +3337,7 @@
         <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AG24" t="n">
         <v>1.25</v>
@@ -3399,10 +3399,10 @@
         <v>3.17</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="N25" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="O25" t="n">
         <v>3.55</v>
@@ -3411,7 +3411,7 @@
         <v>2.08</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="R25" t="n">
         <v>1.45</v>
@@ -3444,7 +3444,7 @@
         <v>2.18</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC25" t="n">
         <v>3.8</v>
@@ -3453,7 +3453,7 @@
         <v>1.25</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AF25" t="n">
         <v>1.91</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -784,7 +784,7 @@
         <v>2.89</v>
       </c>
       <c r="N3" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
         <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.27</v>
+        <v>2.45</v>
       </c>
       <c r="M10" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>9.75</v>
+        <v>2.75</v>
       </c>
       <c r="O10" t="n">
-        <v>1.69</v>
+        <v>2.8</v>
       </c>
       <c r="P10" t="n">
-        <v>2.75</v>
+        <v>2.03</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.9</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>3.42</v>
+        <v>2.69</v>
       </c>
       <c r="T10" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.6</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>3.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M11" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="N11" t="n">
-        <v>6.2</v>
+        <v>9.75</v>
       </c>
       <c r="O11" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="P11" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="T11" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="V11" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.99</v>
+        <v>3.6</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.44</v>
+        <v>1.26</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="N12" t="n">
-        <v>2.95</v>
+        <v>6.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>1.74</v>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>2.73</v>
+        <v>3.58</v>
       </c>
       <c r="T12" t="n">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.91</v>
+        <v>1.46</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.2</v>
+        <v>2.12</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.26</v>
+        <v>1.62</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AF12" t="n">
         <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.6</v>
+        <v>2.99</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="N13" t="n">
-        <v>1.61</v>
+        <v>1.15</v>
       </c>
       <c r="O13" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="P13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q13" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>4.45</v>
       </c>
       <c r="W13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.07</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.17</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="M14" t="n">
-        <v>5.9</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>1.15</v>
+        <v>1.61</v>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="P14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.1</v>
-      </c>
       <c r="U14" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>4.45</v>
+        <v>7.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="Z14" t="n">
-        <v>5</v>
+        <v>3.08</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.43</v>
+        <v>1.97</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.15</v>
+        <v>3.45</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.12</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.07</v>
+        <v>1.17</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2206,19 +2206,19 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="N15" t="n">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="O15" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="P15" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
         <v>6.25</v>
@@ -2227,7 +2227,7 @@
         <v>1.46</v>
       </c>
       <c r="S15" t="n">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="T15" t="n">
         <v>3.15</v>
@@ -2236,40 +2236,40 @@
         <v>1.31</v>
       </c>
       <c r="V15" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X15" t="n">
         <v>1.02</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y15" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="AD15" t="n">
         <v>1.19</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
         <v>2.5</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.11</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
-        <v>2.99</v>
+        <v>4.2</v>
       </c>
       <c r="N16" t="n">
-        <v>2.2</v>
+        <v>5.8</v>
       </c>
       <c r="O16" t="n">
-        <v>3.8</v>
+        <v>1.87</v>
       </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>2.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.01</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="S16" t="n">
-        <v>2.31</v>
+        <v>3.36</v>
       </c>
       <c r="T16" t="n">
-        <v>3.42</v>
+        <v>2.47</v>
       </c>
       <c r="U16" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="V16" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.49</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.28</v>
+        <v>2.7</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46006.6875</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.44</v>
       </c>
-      <c r="M17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="AA17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.7</v>
       </c>
-      <c r="AB17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.48</v>
+        <v>3.1</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
-        <v>2.09</v>
+        <v>4.18</v>
       </c>
       <c r="P18" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>2.9</v>
       </c>
       <c r="R18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.38</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V18" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Z18" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AC18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="AE18" t="n">
         <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.38</v>
+        <v>1.23</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z19" t="n">
         <v>3.2</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="O19" t="n">
-        <v>4</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AA19" t="n">
-        <v>2.52</v>
+        <v>1.95</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.45</v>
+        <v>3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.3</v>
+        <v>1.98</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="M20" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>8.699999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="O20" t="n">
         <v>1.96</v>
@@ -2846,10 +2846,10 @@
         <v>2.92</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AC20" t="n">
         <v>3.48</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="O21" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
         <v>4</v>
       </c>
       <c r="R21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V21" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.36</v>
       </c>
-      <c r="S21" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.26</v>
-      </c>
       <c r="Z21" t="n">
-        <v>3.92</v>
+        <v>3.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC21" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AF21" t="n">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="O22" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
         <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>2.53</v>
+        <v>2.89</v>
       </c>
       <c r="T22" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="U22" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="V22" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.1</v>
+        <v>3.92</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.1</v>
+        <v>2.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S24" t="n">
-        <v>3.03</v>
+        <v>3.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.89</v>
+        <v>2.33</v>
       </c>
       <c r="U24" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="V24" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.99</v>
+        <v>1.57</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.24</v>
+        <v>2.45</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.13</v>
+        <v>2.48</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.83</v>
       </c>
-      <c r="M26" t="n">
-        <v>4</v>
-      </c>
-      <c r="N26" t="n">
-        <v>4</v>
-      </c>
-      <c r="O26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V26" t="n">
-        <v>5</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AC26" t="n">
-        <v>2.45</v>
+        <v>3.24</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="AE26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.95</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="M27" t="n">
-        <v>6.75</v>
+        <v>7.1</v>
       </c>
       <c r="N27" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O27" t="n">
         <v>1.53</v>
@@ -3655,7 +3655,7 @@
         <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="T27" t="n">
         <v>2.3</v>
@@ -3679,16 +3679,16 @@
         <v>3.95</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AB27" t="n">
         <v>2.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AE27" t="n">
         <v>2.51</v>
@@ -3700,7 +3700,7 @@
         <v>1.03</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.4</v>
+        <v>4.92</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46006.73958333334</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.56</v>
+        <v>2.31</v>
       </c>
       <c r="M4" t="n">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="N4" t="n">
-        <v>1.97</v>
+        <v>3.19</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.31</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="N5" t="n">
-        <v>3.19</v>
+        <v>5.31</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.6</v>
+        <v>3.56</v>
       </c>
       <c r="M6" t="n">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="N6" t="n">
-        <v>5.31</v>
+        <v>1.97</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="O9" t="n">
         <v>2.45</v>
@@ -1513,10 +1513,10 @@
         <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>2.98</v>
+        <v>2.73</v>
       </c>
       <c r="T9" t="n">
-        <v>2.87</v>
+        <v>2.73</v>
       </c>
       <c r="U9" t="n">
         <v>1.39</v>
@@ -1534,19 +1534,19 @@
         <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1</v>
+        <v>3.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE9" t="n">
         <v>1.73</v>
@@ -1555,10 +1555,10 @@
         <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46006.52083333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.45</v>
+        <v>1.27</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="N10" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="P10" t="n">
         <v>2.75</v>
       </c>
-      <c r="O10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.03</v>
-      </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>2.69</v>
+        <v>3.42</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="V10" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.28</v>
+        <v>2.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="N11" t="n">
-        <v>9.75</v>
+        <v>6.2</v>
       </c>
       <c r="O11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>7</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.69</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE11" t="n">
+      <c r="AF11" t="n">
         <v>2</v>
       </c>
-      <c r="AF11" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.6</v>
+        <v>2.99</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.26</v>
+        <v>2.45</v>
       </c>
       <c r="M12" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>6.2</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.74</v>
+        <v>2.8</v>
       </c>
       <c r="P12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T12" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q12" t="n">
-        <v>7</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.95</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.46</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.12</v>
+        <v>3.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AF12" t="n">
         <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.99</v>
+        <v>1.6</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="M13" t="n">
-        <v>5.9</v>
+        <v>3.56</v>
       </c>
       <c r="N13" t="n">
-        <v>1.15</v>
+        <v>1.61</v>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="P13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.1</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>4.45</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.43</v>
+        <v>1.94</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.6</v>
+        <v>1.76</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.15</v>
+        <v>3.45</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.12</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="N14" t="n">
-        <v>1.61</v>
+        <v>1.15</v>
       </c>
       <c r="O14" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.26</v>
+        <v>1.65</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="S14" t="n">
-        <v>2.66</v>
+        <v>3.42</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>2.13</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5</v>
+        <v>4.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.08</v>
+        <v>5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.97</v>
+        <v>1.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.45</v>
+        <v>1.86</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.84</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="M16" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="P16" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="Q16" t="n">
         <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>3.36</v>
+        <v>2.88</v>
       </c>
       <c r="T16" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>5.8</v>
+        <v>7.1</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.7</v>
+        <v>1.98</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46006.6875</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="M17" t="n">
         <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>4.18</v>
       </c>
       <c r="P17" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="R17" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>2.34</v>
+        <v>2.57</v>
       </c>
       <c r="T17" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="V17" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.45</v>
+        <v>2.86</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
         <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="AD17" t="n">
         <v>1.15</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N18" t="n">
-        <v>2.15</v>
+        <v>5.9</v>
       </c>
       <c r="O18" t="n">
-        <v>4.18</v>
+        <v>1.96</v>
       </c>
       <c r="P18" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.9</v>
+        <v>7.92</v>
       </c>
       <c r="R18" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="U18" t="n">
         <v>1.32</v>
       </c>
       <c r="V18" t="n">
-        <v>8.6</v>
+        <v>7.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC18" t="n">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>2.31</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.23</v>
+        <v>2.66</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="P19" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
         <v>6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="T19" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="V19" t="n">
-        <v>7.1</v>
+        <v>5.45</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.98</v>
+        <v>2.7</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.5</v>
+        <v>3.05</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>5.9</v>
+        <v>2.18</v>
       </c>
       <c r="O20" t="n">
-        <v>1.96</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.92</v>
+        <v>2.82</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="T20" t="n">
-        <v>2.92</v>
+        <v>3.34</v>
       </c>
       <c r="U20" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="V20" t="n">
-        <v>7.5</v>
+        <v>9.6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.92</v>
+        <v>2.45</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.48</v>
+        <v>4.45</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.66</v>
+        <v>1.3</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="N21" t="n">
-        <v>3.45</v>
+        <v>3.92</v>
       </c>
       <c r="O21" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
         <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.53</v>
+        <v>2.89</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="U21" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="V21" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.1</v>
+        <v>2.95</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.13</v>
       </c>
       <c r="N22" t="n">
-        <v>4.1</v>
+        <v>3.62</v>
       </c>
       <c r="O22" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
         <v>4</v>
       </c>
       <c r="R22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V22" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.36</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.26</v>
-      </c>
       <c r="Z22" t="n">
-        <v>3.92</v>
+        <v>3.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AB22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC22" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AF22" t="n">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="N23" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="O23" t="n">
         <v>4</v>
@@ -3176,10 +3176,10 @@
         <v>2.67</v>
       </c>
       <c r="R23" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="T23" t="n">
         <v>3</v>
@@ -3203,7 +3203,7 @@
         <v>2.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB23" t="n">
         <v>1.62</v>
@@ -3218,7 +3218,7 @@
         <v>1.91</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AG23" t="n">
         <v>1.33</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.83</v>
       </c>
-      <c r="M24" t="n">
-        <v>4</v>
-      </c>
-      <c r="N24" t="n">
-        <v>4</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V24" t="n">
-        <v>5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AC24" t="n">
-        <v>2.45</v>
+        <v>3.24</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="AE24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.95</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3396,22 +3396,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.17</v>
+        <v>3.55</v>
       </c>
       <c r="M25" t="n">
-        <v>2.98</v>
+        <v>3.27</v>
       </c>
       <c r="N25" t="n">
-        <v>2.24</v>
+        <v>2.07</v>
       </c>
       <c r="O25" t="n">
         <v>3.55</v>
       </c>
       <c r="P25" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="R25" t="n">
         <v>1.45</v>
@@ -3423,10 +3423,10 @@
         <v>2.75</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="V25" t="n">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="W25" t="n">
         <v>1.02</v>
@@ -3441,10 +3441,10 @@
         <v>3</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.18</v>
+        <v>2.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
         <v>3.8</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.63</v>
+        <v>1.85</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S26" t="n">
-        <v>3.03</v>
+        <v>3.5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.89</v>
+        <v>2.33</v>
       </c>
       <c r="U26" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="V26" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.99</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.24</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.13</v>
+        <v>2.48</v>
       </c>
       <c r="AG26" t="n">
         <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="M4" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="N4" t="n">
-        <v>3.19</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -936,16 +936,16 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3.35</v>
+        <v>2.85</v>
       </c>
       <c r="N5" t="n">
-        <v>5.31</v>
+        <v>2.15</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.56</v>
+        <v>1.95</v>
       </c>
       <c r="M6" t="n">
-        <v>3.12</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>1.97</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5.17</v>
+        <v>3.9</v>
       </c>
       <c r="M7" t="n">
-        <v>3.28</v>
+        <v>2.8</v>
       </c>
       <c r="N7" t="n">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1510,7 +1510,7 @@
         <v>3.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
         <v>2.73</v>
@@ -1525,7 +1525,7 @@
         <v>6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
@@ -1534,7 +1534,7 @@
         <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA9" t="n">
         <v>1.77</v>
@@ -1543,19 +1543,19 @@
         <v>1.93</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
         <v>1.73</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
         <v>1.73</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.27</v>
+        <v>2.45</v>
       </c>
       <c r="M10" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>9.75</v>
+        <v>2.75</v>
       </c>
       <c r="O10" t="n">
-        <v>1.69</v>
+        <v>2.8</v>
       </c>
       <c r="P10" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.9</v>
+        <v>3.77</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>3.42</v>
+        <v>2.73</v>
       </c>
       <c r="T10" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.6</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>3.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="M11" t="n">
-        <v>5.2</v>
+        <v>5.37</v>
       </c>
       <c r="N11" t="n">
         <v>6.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="P11" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="R11" t="n">
         <v>1.22</v>
@@ -1760,7 +1760,7 @@
         <v>1.67</v>
       </c>
       <c r="V11" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="W11" t="n">
         <v>1.13</v>
@@ -1796,7 +1796,7 @@
         <v>1.17</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.45</v>
+        <v>1.16</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="N12" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="P12" t="n">
         <v>2.75</v>
       </c>
-      <c r="O12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.03</v>
-      </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="S12" t="n">
-        <v>2.69</v>
+        <v>3.8</v>
       </c>
       <c r="T12" t="n">
-        <v>2.62</v>
+        <v>2.16</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.28</v>
+        <v>2.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1980,19 +1980,19 @@
         <v>4.75</v>
       </c>
       <c r="P13" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
         <v>2.26</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.87</v>
+        <v>2.66</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>2.98</v>
       </c>
       <c r="U13" t="n">
         <v>1.36</v>
@@ -2004,7 +2004,7 @@
         <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
         <v>1.32</v>
@@ -2031,10 +2031,10 @@
         <v>1.78</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2096,7 +2096,7 @@
         <v>1.15</v>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="P14" t="n">
         <v>2.75</v>
@@ -2123,7 +2123,7 @@
         <v>1.14</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
         <v>1.11</v>
@@ -2147,7 +2147,7 @@
         <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG14" t="n">
         <v>1.14</v>
@@ -2215,10 +2215,10 @@
         <v>7.3</v>
       </c>
       <c r="O15" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="Q15" t="n">
         <v>6.25</v>
@@ -2227,7 +2227,7 @@
         <v>1.46</v>
       </c>
       <c r="S15" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="T15" t="n">
         <v>3.15</v>
@@ -2236,16 +2236,16 @@
         <v>1.31</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z15" t="n">
         <v>2.9</v>
@@ -2257,22 +2257,22 @@
         <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AF15" t="n">
         <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46006.65625</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.55</v>
+        <v>3.1</v>
       </c>
       <c r="M16" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>5.2</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>2.09</v>
+        <v>4.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>2.62</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.98</v>
+        <v>1.29</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46006.6875</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>2.15</v>
+        <v>6.5</v>
       </c>
       <c r="O17" t="n">
-        <v>4.18</v>
+        <v>1.91</v>
       </c>
       <c r="P17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB17" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AC17" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.23</v>
+        <v>2.7</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2575,37 +2575,37 @@
         <v>1.96</v>
       </c>
       <c r="P18" t="n">
-        <v>2.09</v>
+        <v>2.29</v>
       </c>
       <c r="Q18" t="n">
         <v>7.92</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="T18" t="n">
-        <v>2.92</v>
+        <v>3.01</v>
       </c>
       <c r="U18" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="V18" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W18" t="n">
         <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
         <v>1.31</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AA18" t="n">
         <v>1.97</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="M19" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="N19" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="O19" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
         <v>6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>3.15</v>
+        <v>2.67</v>
       </c>
       <c r="T19" t="n">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="U19" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>5.45</v>
+        <v>7.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AG19" t="n">
         <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2810,16 +2810,16 @@
         <v>2.18</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="P20" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
         <v>2.34</v>
@@ -2831,7 +2831,7 @@
         <v>1.25</v>
       </c>
       <c r="V20" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W20" t="n">
         <v>1</v>
@@ -2843,7 +2843,7 @@
         <v>1.44</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="AA20" t="n">
         <v>2.08</v>
@@ -2855,19 +2855,19 @@
         <v>4.45</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -2935,25 +2935,25 @@
         <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="T21" t="n">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="U21" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
         <v>6.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
         <v>1</v>
@@ -2962,7 +2962,7 @@
         <v>1.26</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="AA21" t="n">
         <v>1.77</v>
@@ -2974,7 +2974,7 @@
         <v>2.95</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE21" t="n">
         <v>1.7</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.11</v>
+        <v>3.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.13</v>
+        <v>3.04</v>
       </c>
       <c r="N22" t="n">
-        <v>3.62</v>
+        <v>1.95</v>
       </c>
       <c r="O22" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S22" t="n">
         <v>2.63</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="T22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC22" t="n">
         <v>4</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V22" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AD22" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>2.11</v>
       </c>
       <c r="M23" t="n">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>1.95</v>
+        <v>3.62</v>
       </c>
       <c r="O23" t="n">
-        <v>4</v>
+        <v>2.85</v>
       </c>
       <c r="P23" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.67</v>
+        <v>4.45</v>
       </c>
       <c r="R23" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S23" t="n">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>3.41</v>
       </c>
       <c r="U23" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF23" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.76</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.63</v>
+        <v>3.55</v>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>3.27</v>
       </c>
       <c r="N24" t="n">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.45</v>
+        <v>2.99</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S24" t="n">
-        <v>3.03</v>
+        <v>2.56</v>
       </c>
       <c r="T24" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="V24" t="n">
         <v>7.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
         <v>1.31</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.24</v>
+        <v>3.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.55</v>
+        <v>2.59</v>
       </c>
       <c r="M25" t="n">
-        <v>3.27</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.99</v>
+        <v>3.32</v>
       </c>
       <c r="R25" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.56</v>
+        <v>2.93</v>
       </c>
       <c r="T25" t="n">
-        <v>2.75</v>
+        <v>2.93</v>
       </c>
       <c r="U25" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="V25" t="n">
         <v>7.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
         <v>1.31</v>
       </c>
       <c r="Z25" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.8</v>
+        <v>3.24</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3548,7 +3548,7 @@
         <v>5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
@@ -3572,7 +3572,7 @@
         <v>1.57</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AF26" t="n">
         <v>2.48</v>
@@ -3581,7 +3581,7 @@
         <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3649,7 +3649,7 @@
         <v>2.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R27" t="n">
         <v>1.28</v>
@@ -3658,25 +3658,25 @@
         <v>3.34</v>
       </c>
       <c r="T27" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U27" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="V27" t="n">
         <v>5.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="AA27" t="n">
         <v>1.55</v>
@@ -3691,7 +3691,7 @@
         <v>1.55</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.51</v>
+        <v>2.38</v>
       </c>
       <c r="AF27" t="n">
         <v>1.42</v>
@@ -3700,7 +3700,7 @@
         <v>1.03</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.92</v>
+        <v>4.4</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46006.73958333334</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="M4" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -936,16 +936,16 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
         <v>2.85</v>
       </c>
       <c r="N5" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1055,16 +1055,16 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.95</v>
+        <v>3.6</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>2.15</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.45</v>
+        <v>1.33</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>5.37</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>6.2</v>
       </c>
       <c r="O10" t="n">
-        <v>2.8</v>
+        <v>1.76</v>
       </c>
       <c r="P10" t="n">
-        <v>2.15</v>
+        <v>2.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.77</v>
+        <v>6.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>2.73</v>
+        <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>1.95</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="V10" t="n">
-        <v>6.2</v>
+        <v>4.55</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>1.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.3</v>
+        <v>2.12</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.33</v>
+        <v>2.45</v>
       </c>
       <c r="M11" t="n">
-        <v>5.37</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V11" t="n">
         <v>6.2</v>
       </c>
-      <c r="O11" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.55</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.46</v>
+        <v>1.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.12</v>
+        <v>3.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>6.5</v>
       </c>
       <c r="O16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>6</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V16" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z16" t="n">
         <v>4.2</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3</v>
-      </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.29</v>
+        <v>2.7</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46006.6875</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.5</v>
+        <v>2.15</v>
       </c>
       <c r="O17" t="n">
-        <v>1.91</v>
+        <v>4.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>2.62</v>
       </c>
       <c r="R17" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>3.15</v>
+        <v>2.56</v>
       </c>
       <c r="T17" t="n">
-        <v>2.47</v>
+        <v>3.04</v>
       </c>
       <c r="U17" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>5.45</v>
+        <v>7.9</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.7</v>
+        <v>1.29</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="M18" t="n">
         <v>3.65</v>
       </c>
       <c r="N18" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="P18" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.92</v>
+        <v>6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="T18" t="n">
-        <v>3.01</v>
+        <v>2.75</v>
       </c>
       <c r="U18" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC18" t="n">
         <v>3</v>
       </c>
-      <c r="AA18" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.48</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.31</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AG18" t="n">
         <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
         <v>3.65</v>
       </c>
       <c r="N19" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="O19" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>7.92</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="T19" t="n">
-        <v>2.75</v>
+        <v>3.01</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V19" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC19" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.91</v>
+        <v>2.31</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AG19" t="n">
         <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.41</v>
+        <v>3.04</v>
       </c>
       <c r="N21" t="n">
-        <v>3.92</v>
+        <v>1.95</v>
       </c>
       <c r="O21" t="n">
-        <v>2.45</v>
+        <v>4.7</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.83</v>
+        <v>2.67</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="S21" t="n">
-        <v>2.94</v>
+        <v>2.63</v>
       </c>
       <c r="T21" t="n">
-        <v>2.59</v>
+        <v>3.15</v>
       </c>
       <c r="U21" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="W21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X21" t="n">
         <v>1.07</v>
       </c>
-      <c r="X21" t="n">
-        <v>1</v>
-      </c>
       <c r="Y21" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.92</v>
+        <v>2.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.77</v>
+        <v>2.17</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.6</v>
+        <v>2.11</v>
       </c>
       <c r="M22" t="n">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>3.62</v>
       </c>
       <c r="O22" t="n">
-        <v>4.7</v>
+        <v>2.85</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.67</v>
+        <v>4.45</v>
       </c>
       <c r="R22" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S22" t="n">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="T22" t="n">
-        <v>3.15</v>
+        <v>3.41</v>
       </c>
       <c r="U22" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>3.41</v>
       </c>
       <c r="N23" t="n">
-        <v>3.62</v>
+        <v>3.92</v>
       </c>
       <c r="O23" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="P23" t="n">
-        <v>1.96</v>
+        <v>2.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.45</v>
+        <v>3.83</v>
       </c>
       <c r="R23" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>2.53</v>
+        <v>2.94</v>
       </c>
       <c r="T23" t="n">
-        <v>3.41</v>
+        <v>2.59</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.1</v>
+        <v>3.92</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2</v>
-      </c>
       <c r="AF23" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.55</v>
+        <v>2.59</v>
       </c>
       <c r="M24" t="n">
-        <v>3.27</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="O24" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.99</v>
+        <v>3.32</v>
       </c>
       <c r="R24" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.56</v>
+        <v>2.93</v>
       </c>
       <c r="T24" t="n">
-        <v>2.75</v>
+        <v>2.93</v>
       </c>
       <c r="U24" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="V24" t="n">
         <v>7.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
         <v>1.31</v>
       </c>
       <c r="Z24" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.8</v>
+        <v>3.24</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.59</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>3.85</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.32</v>
+        <v>3.95</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S25" t="n">
-        <v>2.93</v>
+        <v>3.5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.93</v>
+        <v>2.33</v>
       </c>
       <c r="U25" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="V25" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.24</v>
+        <v>2.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.13</v>
+        <v>2.48</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.85</v>
+        <v>3.55</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>3.27</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>2.07</v>
       </c>
       <c r="O26" t="n">
-        <v>2.3</v>
+        <v>3.55</v>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.95</v>
+        <v>2.99</v>
       </c>
       <c r="R26" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="S26" t="n">
-        <v>3.5</v>
+        <v>2.56</v>
       </c>
       <c r="T26" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="U26" t="n">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>3.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.52</v>
+        <v>1.81</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.48</v>
+        <v>1.91</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="M4" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -936,16 +936,16 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="M5" t="n">
         <v>2.85</v>
       </c>
       <c r="N5" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1055,16 +1055,16 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="M6" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>2.15</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.33</v>
+        <v>2.45</v>
       </c>
       <c r="M10" t="n">
-        <v>5.37</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V10" t="n">
         <v>6.2</v>
       </c>
-      <c r="O10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.55</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.46</v>
+        <v>1.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.12</v>
+        <v>3.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.45</v>
+        <v>1.34</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="N11" t="n">
-        <v>2.75</v>
+        <v>6.2</v>
       </c>
       <c r="O11" t="n">
-        <v>2.8</v>
+        <v>1.65</v>
       </c>
       <c r="P11" t="n">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.77</v>
+        <v>6.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>2.73</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.62</v>
+        <v>2.13</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="V11" t="n">
-        <v>6.2</v>
+        <v>4.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.4</v>
+        <v>5.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.9</v>
+        <v>1.47</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.6</v>
+        <v>2.95</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="M16" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>6.5</v>
+        <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>1.91</v>
+        <v>4.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>2.62</v>
       </c>
       <c r="R16" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>3.15</v>
+        <v>2.56</v>
       </c>
       <c r="T16" t="n">
-        <v>2.47</v>
+        <v>3.04</v>
       </c>
       <c r="U16" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>5.45</v>
+        <v>7.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.7</v>
+        <v>1.29</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46006.6875</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.1</v>
+        <v>1.55</v>
       </c>
       <c r="M17" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P17" t="n">
         <v>2.15</v>
       </c>
-      <c r="O17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q17" t="n">
-        <v>2.62</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="T17" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z17" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC17" t="n">
         <v>3</v>
       </c>
-      <c r="AA17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AD17" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.29</v>
+        <v>2.38</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.55</v>
+        <v>3.05</v>
       </c>
       <c r="M18" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>5.2</v>
+        <v>2.18</v>
       </c>
       <c r="O18" t="n">
-        <v>2.05</v>
+        <v>4.03</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="S18" t="n">
-        <v>2.67</v>
+        <v>2.34</v>
       </c>
       <c r="T18" t="n">
-        <v>2.75</v>
+        <v>3.34</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="V18" t="n">
-        <v>7.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="AA18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AF18" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.38</v>
+        <v>1.26</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="P19" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.92</v>
+        <v>6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="S19" t="n">
-        <v>2.69</v>
+        <v>3.15</v>
       </c>
       <c r="T19" t="n">
-        <v>3.01</v>
+        <v>2.47</v>
       </c>
       <c r="U19" t="n">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="V19" t="n">
-        <v>8</v>
+        <v>5.45</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.48</v>
+        <v>2.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.31</v>
+        <v>1.83</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
         <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.05</v>
+        <v>1.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>2.18</v>
+        <v>5.9</v>
       </c>
       <c r="O20" t="n">
-        <v>4.03</v>
+        <v>1.96</v>
       </c>
       <c r="P20" t="n">
-        <v>1.85</v>
+        <v>2.29</v>
       </c>
       <c r="Q20" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z20" t="n">
         <v>3</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AA20" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.45</v>
+        <v>3.48</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.95</v>
+        <v>2.31</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.26</v>
+        <v>2.66</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.59</v>
+        <v>1.85</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>2.6</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.32</v>
+        <v>3.95</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="S24" t="n">
-        <v>2.93</v>
+        <v>3.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.93</v>
+        <v>2.33</v>
       </c>
       <c r="U24" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="V24" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.24</v>
+        <v>2.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.13</v>
+        <v>2.48</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>2.59</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.85</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.95</v>
+        <v>3.32</v>
       </c>
       <c r="R25" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>3.5</v>
+        <v>2.93</v>
       </c>
       <c r="T25" t="n">
-        <v>2.33</v>
+        <v>2.93</v>
       </c>
       <c r="U25" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="V25" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.25</v>
+        <v>3.24</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.48</v>
+        <v>2.13</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46006.70833333334</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -778,22 +778,22 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="M3" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="N3" t="n">
-        <v>3.23</v>
+        <v>4.2</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -823,28 +823,28 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AB3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46006.39583333334</v>
@@ -906,34 +906,34 @@
         <v>3.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
         <v>1.7</v>
@@ -945,25 +945,25 @@
         <v>3</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46006.40625</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,55 +1016,55 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="M5" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z5" t="n">
         <v>2.15</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
       <c r="AA5" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.95</v>
+        <v>3.6</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>2.15</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46006.40625</v>
@@ -1263,34 +1263,34 @@
         <v>2.1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y7" t="n">
         <v>1.62</v>
@@ -1299,28 +1299,28 @@
         <v>2.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="n">
         <v>1.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46006.47916666666</v>
@@ -1510,13 +1510,13 @@
         <v>3.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="T9" t="n">
-        <v>2.73</v>
+        <v>2.89</v>
       </c>
       <c r="U9" t="n">
         <v>1.39</v>
@@ -1531,10 +1531,10 @@
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="AA9" t="n">
         <v>1.77</v>
@@ -1543,7 +1543,7 @@
         <v>1.93</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AD9" t="n">
         <v>1.3</v>
@@ -1552,10 +1552,10 @@
         <v>1.73</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
         <v>1.73</v>
@@ -1623,13 +1623,13 @@
         <v>2.8</v>
       </c>
       <c r="P10" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S10" t="n">
         <v>2.73</v>
@@ -1638,10 +1638,10 @@
         <v>2.62</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V10" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="W10" t="n">
         <v>1.1</v>
@@ -1650,10 +1650,10 @@
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="AA10" t="n">
         <v>1.9</v>
@@ -1662,10 +1662,10 @@
         <v>1.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE10" t="n">
         <v>1.73</v>
@@ -1674,10 +1674,10 @@
         <v>1.97</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="M12" t="n">
         <v>6</v>
@@ -1858,31 +1858,31 @@
         <v>9.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="P12" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="R12" t="n">
         <v>1.26</v>
       </c>
       <c r="S12" t="n">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="T12" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="U12" t="n">
         <v>1.6</v>
       </c>
       <c r="V12" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
         <v>1.02</v>
@@ -1897,7 +1897,7 @@
         <v>1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AC12" t="n">
         <v>2.25</v>
@@ -1906,10 +1906,10 @@
         <v>1.66</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG12" t="n">
         <v>1.13</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="M13" t="n">
-        <v>3.56</v>
+        <v>5.9</v>
       </c>
       <c r="N13" t="n">
-        <v>1.61</v>
+        <v>1.15</v>
       </c>
       <c r="O13" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.26</v>
+        <v>1.73</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="S13" t="n">
-        <v>2.66</v>
+        <v>3.42</v>
       </c>
       <c r="T13" t="n">
-        <v>2.98</v>
+        <v>2.16</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>4.45</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.94</v>
+        <v>1.33</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.76</v>
+        <v>3</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.45</v>
+        <v>1.86</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.84</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="M14" t="n">
-        <v>5.9</v>
+        <v>3.56</v>
       </c>
       <c r="N14" t="n">
-        <v>1.15</v>
+        <v>1.61</v>
       </c>
       <c r="O14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V14" t="n">
         <v>7.5</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V14" t="n">
-        <v>4.4</v>
-      </c>
       <c r="W14" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.11</v>
+        <v>1.32</v>
       </c>
       <c r="Z14" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.33</v>
+        <v>1.94</v>
       </c>
       <c r="AB14" t="n">
-        <v>3</v>
+        <v>1.76</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.86</v>
+        <v>3.45</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.84</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2215,37 +2215,37 @@
         <v>7.3</v>
       </c>
       <c r="O15" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="P15" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
         <v>6.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="T15" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V15" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="W15" t="n">
         <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z15" t="n">
         <v>2.9</v>
@@ -2263,16 +2263,16 @@
         <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AF15" t="n">
         <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46006.65625</v>
@@ -2334,40 +2334,40 @@
         <v>2.15</v>
       </c>
       <c r="O16" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="T16" t="n">
-        <v>3.04</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V16" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="AA16" t="n">
         <v>2.1</v>
@@ -2376,22 +2376,22 @@
         <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46006.6875</v>
@@ -2453,40 +2453,40 @@
         <v>5.2</v>
       </c>
       <c r="O17" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="P17" t="n">
         <v>2.05</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
         <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="T17" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="V17" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.34</v>
+        <v>3.11</v>
       </c>
       <c r="AA17" t="n">
         <v>1.95</v>
@@ -2495,22 +2495,22 @@
         <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.05</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="N18" t="n">
-        <v>2.18</v>
+        <v>6.5</v>
       </c>
       <c r="O18" t="n">
-        <v>4.03</v>
+        <v>1.93</v>
       </c>
       <c r="P18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.85</v>
       </c>
-      <c r="Q18" t="n">
-        <v>3</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.26</v>
+        <v>2.69</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.44</v>
       </c>
-      <c r="M19" t="n">
+      <c r="S19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC19" t="n">
         <v>4.5</v>
       </c>
-      <c r="N19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>6</v>
-      </c>
-      <c r="R19" t="n">
+      <c r="AD19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.31</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH19" t="n">
-        <v>2.7</v>
+        <v>1.26</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2810,40 +2810,40 @@
         <v>5.9</v>
       </c>
       <c r="O20" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="P20" t="n">
-        <v>2.29</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>7.92</v>
+        <v>8.1</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>2.69</v>
+        <v>2.47</v>
       </c>
       <c r="T20" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="U20" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="V20" t="n">
         <v>8</v>
       </c>
       <c r="W20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X20" t="n">
         <v>1.03</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
         <v>1.31</v>
       </c>
       <c r="Z20" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="AA20" t="n">
         <v>1.97</v>
@@ -2852,10 +2852,10 @@
         <v>1.73</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE20" t="n">
         <v>2.31</v>
@@ -2929,10 +2929,10 @@
         <v>1.95</v>
       </c>
       <c r="O21" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Q21" t="n">
         <v>2.67</v>
@@ -2941,13 +2941,13 @@
         <v>1.48</v>
       </c>
       <c r="S21" t="n">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="T21" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="U21" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
         <v>7.6</v>
@@ -2956,13 +2956,13 @@
         <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="AA21" t="n">
         <v>2.17</v>
@@ -2983,10 +2983,10 @@
         <v>1.8</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3051,31 +3051,31 @@
         <v>2.85</v>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.45</v>
+        <v>3.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="S22" t="n">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="T22" t="n">
-        <v>3.41</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V22" t="n">
         <v>8.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
         <v>1.36</v>
@@ -3099,13 +3099,13 @@
         <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3167,40 +3167,40 @@
         <v>3.92</v>
       </c>
       <c r="O23" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
         <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
         <v>2.59</v>
       </c>
       <c r="U23" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V23" t="n">
         <v>6.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
         <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="AA23" t="n">
         <v>1.77</v>
@@ -3215,7 +3215,7 @@
         <v>1.34</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AF23" t="n">
         <v>2.1</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.85</v>
+        <v>3.55</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>3.27</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>2.07</v>
       </c>
       <c r="O24" t="n">
-        <v>2.3</v>
+        <v>3.55</v>
       </c>
       <c r="P24" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.95</v>
+        <v>2.99</v>
       </c>
       <c r="R24" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="S24" t="n">
-        <v>3.5</v>
+        <v>2.56</v>
       </c>
       <c r="T24" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="Z24" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.25</v>
+        <v>3.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.52</v>
+        <v>1.81</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.48</v>
+        <v>1.91</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.59</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>3.85</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.32</v>
+        <v>3.95</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>2.93</v>
+        <v>3.5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.93</v>
+        <v>2.35</v>
       </c>
       <c r="U25" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="V25" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.24</v>
+        <v>2.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.55</v>
+        <v>2.59</v>
       </c>
       <c r="M26" t="n">
-        <v>3.27</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="P26" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.99</v>
+        <v>3.32</v>
       </c>
       <c r="R26" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>2.56</v>
+        <v>2.93</v>
       </c>
       <c r="T26" t="n">
-        <v>2.75</v>
+        <v>2.93</v>
       </c>
       <c r="U26" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="V26" t="n">
         <v>7.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X26" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
         <v>1.31</v>
       </c>
       <c r="Z26" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.8</v>
+        <v>3.24</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3646,37 +3646,37 @@
         <v>1.53</v>
       </c>
       <c r="P27" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="Q27" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="R27" t="n">
         <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="T27" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="U27" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="V27" t="n">
         <v>5.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA27" t="n">
         <v>1.55</v>
@@ -3691,7 +3691,7 @@
         <v>1.55</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AF27" t="n">
         <v>1.42</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI29"/>
+  <dimension ref="A1:AI30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.15</v>
       </c>
-      <c r="M4" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="T4" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AA4" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46006.40625</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46006.40625</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.45</v>
+        <v>1.26</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>9.75</v>
       </c>
       <c r="O10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="P10" t="n">
         <v>2.8</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.12</v>
-      </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>2.73</v>
+        <v>3.42</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="V10" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>1.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.97</v>
+        <v>1.79</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.4</v>
+        <v>4.13</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.34</v>
+        <v>2.45</v>
       </c>
       <c r="M11" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>6.2</v>
+        <v>2.75</v>
       </c>
       <c r="O11" t="n">
-        <v>1.65</v>
+        <v>2.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.56</v>
+        <v>2.12</v>
       </c>
       <c r="Q11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V11" t="n">
         <v>6.5</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.55</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.2</v>
+        <v>3.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.18</v>
+        <v>3.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.62</v>
+        <v>1.32</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.95</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="M12" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="N12" t="n">
-        <v>9.75</v>
+        <v>6.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="P12" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="V12" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
         <v>1.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AE12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF12" t="n">
         <v>2</v>
       </c>
-      <c r="AF12" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AG12" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,76 +1968,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>12</v>
+        <v>2.35</v>
       </c>
       <c r="M13" t="n">
-        <v>5.9</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>1.15</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>2.88</v>
       </c>
       <c r="P13" t="n">
-        <v>2.66</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.73</v>
+        <v>3.94</v>
       </c>
       <c r="R13" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>3.42</v>
+        <v>2.55</v>
       </c>
       <c r="T13" t="n">
-        <v>2.16</v>
+        <v>3.04</v>
       </c>
       <c r="U13" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>4.45</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>5</v>
+        <v>2.85</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.33</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.86</v>
+        <v>3.62</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.06</v>
+        <v>1.57</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46006.64583333334</v>
+        <v>46006.60416666666</v>
       </c>
     </row>
     <row r="14">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,76 +2206,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.48</v>
+        <v>12</v>
       </c>
       <c r="M15" t="n">
-        <v>3.95</v>
+        <v>5.9</v>
       </c>
       <c r="N15" t="n">
-        <v>7.3</v>
+        <v>1.15</v>
       </c>
       <c r="O15" t="n">
-        <v>2.05</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>2.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.25</v>
+        <v>1.73</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="S15" t="n">
-        <v>2.75</v>
+        <v>3.42</v>
       </c>
       <c r="T15" t="n">
-        <v>3.4</v>
+        <v>2.16</v>
       </c>
       <c r="U15" t="n">
-        <v>1.32</v>
+        <v>1.63</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5</v>
+        <v>4.45</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.34</v>
+        <v>1.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.82</v>
+        <v>1.86</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>1.84</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.5</v>
+        <v>1.06</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46006.65625</v>
+        <v>46006.64583333334</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>2.15</v>
+        <v>7</v>
       </c>
       <c r="O16" t="n">
-        <v>4.5</v>
+        <v>2.05</v>
       </c>
       <c r="P16" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.71</v>
+        <v>6.25</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
         <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.72</v>
+        <v>1.56</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.25</v>
+        <v>2.4</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46006.6875</v>
+        <v>46006.65625</v>
       </c>
     </row>
     <row r="17">
@@ -2444,19 +2444,19 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O17" t="n">
         <v>2.07</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="Q17" t="n">
         <v>6</v>
@@ -2465,22 +2465,22 @@
         <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="T17" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="U17" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
         <v>1.3</v>
@@ -2489,28 +2489,28 @@
         <v>3.11</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AF17" t="n">
         <v>1.7</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.05</v>
+        <v>1.33</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="N19" t="n">
-        <v>2.18</v>
+        <v>7</v>
       </c>
       <c r="O19" t="n">
-        <v>4.1</v>
+        <v>1.85</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.98</v>
+        <v>8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>3.34</v>
+        <v>3.01</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="V19" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.5</v>
+        <v>3.48</v>
       </c>
       <c r="AD19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.17</v>
       </c>
-      <c r="AE19" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.26</v>
+        <v>2.25</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>5.9</v>
+        <v>1.95</v>
       </c>
       <c r="O20" t="n">
-        <v>1.85</v>
+        <v>4.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.1</v>
+        <v>2.71</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S20" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="T20" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.01</v>
+        <v>2.62</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.42</v>
+        <v>4.15</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.66</v>
+        <v>1.25</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,76 +2920,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.6</v>
+        <v>3.19</v>
       </c>
       <c r="M21" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="N21" t="n">
-        <v>1.95</v>
+        <v>2.24</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P21" t="n">
         <v>1.98</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="T21" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="V21" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.17</v>
+        <v>2.49</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46006.69791666666</v>
+        <v>46006.6875</v>
       </c>
     </row>
     <row r="22">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.11</v>
+        <v>3.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.13</v>
+        <v>3.04</v>
       </c>
       <c r="N22" t="n">
-        <v>3.62</v>
+        <v>1.95</v>
       </c>
       <c r="O22" t="n">
-        <v>2.85</v>
+        <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.9</v>
+        <v>2.67</v>
       </c>
       <c r="R22" t="n">
         <v>1.48</v>
       </c>
       <c r="S22" t="n">
-        <v>2.67</v>
+        <v>2.47</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.35</v>
       </c>
-      <c r="V22" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z22" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.67</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="M23" t="n">
-        <v>3.41</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.92</v>
+        <v>3.45</v>
       </c>
       <c r="O23" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="R23" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.35</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.45</v>
-      </c>
       <c r="V23" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,76 +3277,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.55</v>
+        <v>1.75</v>
       </c>
       <c r="M24" t="n">
-        <v>3.27</v>
+        <v>3.41</v>
       </c>
       <c r="N24" t="n">
-        <v>2.07</v>
+        <v>3.92</v>
       </c>
       <c r="O24" t="n">
-        <v>3.55</v>
+        <v>2.4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.99</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U24" t="n">
         <v>1.45</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.32</v>
-      </c>
       <c r="V24" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="Z24" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.03</v>
+        <v>1.77</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.93</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AF24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.91</v>
       </c>
-      <c r="AG24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AI24" s="3" t="n">
-        <v>46006.70833333334</v>
+        <v>46006.69791666666</v>
       </c>
     </row>
     <row r="25">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>3.55</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>3.27</v>
       </c>
       <c r="N25" t="n">
-        <v>3.85</v>
+        <v>2.07</v>
       </c>
       <c r="O25" t="n">
-        <v>2.3</v>
+        <v>3.65</v>
       </c>
       <c r="P25" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.95</v>
+        <v>2.96</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
-        <v>3.5</v>
+        <v>2.58</v>
       </c>
       <c r="T25" t="n">
-        <v>2.35</v>
+        <v>2.75</v>
       </c>
       <c r="U25" t="n">
-        <v>1.62</v>
+        <v>1.32</v>
       </c>
       <c r="V25" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
         <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="Z25" t="n">
-        <v>5</v>
+        <v>2.94</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.25</v>
+        <v>3.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
         <v>2.6</v>
@@ -3530,40 +3530,40 @@
         <v>2.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.32</v>
+        <v>3.12</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
         <v>2.93</v>
       </c>
       <c r="T26" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
         <v>7.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z26" t="n">
         <v>3.45</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AC26" t="n">
         <v>3.24</v>
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,25 +3634,25 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.16</v>
+        <v>1.85</v>
       </c>
       <c r="M27" t="n">
-        <v>7.1</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>15</v>
+        <v>3.85</v>
       </c>
       <c r="O27" t="n">
-        <v>1.53</v>
+        <v>2.3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>3.95</v>
       </c>
       <c r="R27" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
         <v>3.5</v>
@@ -3661,49 +3661,49 @@
         <v>2.35</v>
       </c>
       <c r="U27" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="V27" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
         <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.42</v>
+        <v>2.4</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>4.4</v>
+        <v>2.05</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46006.73958333334</v>
+        <v>46006.70833333334</v>
       </c>
     </row>
     <row r="28">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,76 +3753,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46006.79166666666</v>
+        <v>46006.73958333334</v>
       </c>
     </row>
     <row r="29">
@@ -3831,116 +3831,235 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Spanish Town Police FC</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3" t="n">
+        <v>46006.79166666666</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Arnett Gardens</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Montego Bay United</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="inlineStr">
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" s="3" t="n">
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3" t="n">
         <v>46006.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>2.77</v>
+        <v>3.02</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.7</v>
+        <v>5.46</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46006.39583333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="M4" t="n">
         <v>2.95</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46006.40625</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z5" t="n">
         <v>2.15</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.02</v>
       </c>
       <c r="AA5" t="n">
         <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46006.40625</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="M6" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>2.15</v>
+        <v>5.75</v>
       </c>
       <c r="O6" t="n">
-        <v>4.61</v>
+        <v>2.45</v>
       </c>
       <c r="P6" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.05</v>
+        <v>6.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="S6" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="T6" t="n">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="V6" t="n">
-        <v>7.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.05</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AE6" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.24</v>
+        <v>1.98</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46006.40625</v>
@@ -1254,16 +1254,16 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="P7" t="n">
         <v>1.75</v>
@@ -1272,13 +1272,13 @@
         <v>2.96</v>
       </c>
       <c r="R7" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="S7" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T7" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="U7" t="n">
         <v>1.15</v>
@@ -1293,19 +1293,19 @@
         <v>1.09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AA7" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.65</v>
+        <v>6.6</v>
       </c>
       <c r="AD7" t="n">
         <v>1.05</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N9" t="n">
-        <v>3.47</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
         <v>2.45</v>
@@ -1513,19 +1513,19 @@
         <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>2.95</v>
+        <v>2.65</v>
       </c>
       <c r="T9" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="U9" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
         <v>6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
         <v>1.01</v>
@@ -1537,28 +1537,28 @@
         <v>3.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AF9" t="n">
         <v>1.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46006.52083333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="M10" t="n">
-        <v>5.75</v>
+        <v>4.8</v>
       </c>
       <c r="N10" t="n">
-        <v>9.75</v>
+        <v>6.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="P10" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S10" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="V10" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="W10" t="n">
         <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.13</v>
+        <v>3.2</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="N11" t="n">
-        <v>2.75</v>
+        <v>2.97</v>
       </c>
       <c r="O11" t="n">
         <v>2.8</v>
@@ -1748,10 +1748,10 @@
         <v>3.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="T11" t="n">
         <v>2.62</v>
@@ -1775,28 +1775,28 @@
         <v>3.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
         <v>1.73</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="M12" t="n">
-        <v>4.8</v>
+        <v>5.75</v>
       </c>
       <c r="N12" t="n">
-        <v>6.2</v>
+        <v>9.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="P12" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="T12" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="V12" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="W12" t="n">
         <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
         <v>1.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.95</v>
+        <v>4.13</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -2090,16 +2090,16 @@
         <v>4.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="N14" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="O14" t="n">
         <v>4.75</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
         <v>2.26</v>
@@ -2108,10 +2108,10 @@
         <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
         <v>1.36</v>
@@ -2120,22 +2120,22 @@
         <v>7.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
         <v>3.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
         <v>3.45</v>
@@ -2150,10 +2150,10 @@
         <v>1.78</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2218,19 +2218,19 @@
         <v>6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R15" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S15" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U15" t="n">
         <v>1.63</v>
@@ -2251,16 +2251,16 @@
         <v>5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AB15" t="n">
-        <v>3</v>
+        <v>2.46</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="AE15" t="n">
         <v>1.73</v>
@@ -2269,10 +2269,10 @@
         <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2566,13 +2566,13 @@
         <v>1.44</v>
       </c>
       <c r="M18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="N18" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="P18" t="n">
         <v>2.36</v>
@@ -2608,10 +2608,10 @@
         <v>4.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC18" t="n">
         <v>2.75</v>
@@ -2623,13 +2623,13 @@
         <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.33</v>
+        <v>3.19</v>
       </c>
       <c r="M19" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="N19" t="n">
-        <v>7</v>
+        <v>2.24</v>
       </c>
       <c r="O19" t="n">
-        <v>1.85</v>
+        <v>4.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
         <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>3.01</v>
+        <v>3.42</v>
       </c>
       <c r="U19" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="V19" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>2.49</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.48</v>
+        <v>4.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.31</v>
+        <v>1.88</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.25</v>
+        <v>1.26</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.19</v>
+        <v>1.33</v>
       </c>
       <c r="M21" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="N21" t="n">
-        <v>2.24</v>
+        <v>7</v>
       </c>
       <c r="O21" t="n">
-        <v>4.1</v>
+        <v>1.85</v>
       </c>
       <c r="P21" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
         <v>2.5</v>
       </c>
       <c r="T21" t="n">
-        <v>3.42</v>
+        <v>3.01</v>
       </c>
       <c r="U21" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="V21" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.49</v>
+        <v>2.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.8</v>
+        <v>3.48</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.88</v>
+        <v>2.31</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.26</v>
+        <v>2.25</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46006.6875</v>
@@ -3039,19 +3039,19 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="M22" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="O22" t="n">
         <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
         <v>2.67</v>
@@ -3081,13 +3081,13 @@
         <v>1.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC22" t="n">
         <v>4</v>
@@ -3102,7 +3102,7 @@
         <v>1.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AH22" t="n">
         <v>1.22</v>
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="M24" t="n">
-        <v>3.41</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="O24" t="n">
         <v>2.4</v>
@@ -3295,16 +3295,16 @@
         <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
         <v>3.2</v>
       </c>
       <c r="T24" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="U24" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="V24" t="n">
         <v>6.5</v>
@@ -3316,34 +3316,34 @@
         <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z24" t="n">
         <v>3.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC24" t="n">
         <v>2.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="M25" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>2.07</v>
+        <v>2.32</v>
       </c>
       <c r="O25" t="n">
         <v>3.65</v>
@@ -3414,10 +3414,10 @@
         <v>2.96</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="T25" t="n">
         <v>2.75</v>
@@ -3426,25 +3426,25 @@
         <v>1.32</v>
       </c>
       <c r="V25" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="W25" t="n">
         <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y25" t="n">
         <v>1.31</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC25" t="n">
         <v>3.8</v>
@@ -3536,13 +3536,13 @@
         <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>2.93</v>
+        <v>3.03</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V26" t="n">
         <v>7.5</v>
@@ -3634,19 +3634,19 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="N27" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O27" t="n">
         <v>2.3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
         <v>3.95</v>
@@ -3658,10 +3658,10 @@
         <v>3.5</v>
       </c>
       <c r="T27" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="U27" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V27" t="n">
         <v>5</v>
@@ -3679,28 +3679,28 @@
         <v>5</v>
       </c>
       <c r="AA27" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.6</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.57</v>
       </c>
       <c r="AE27" t="n">
         <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AG27" t="n">
         <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46006.70833333334</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.25</v>
+        <v>1.7</v>
       </c>
       <c r="M4" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.2</v>
+        <v>5.75</v>
       </c>
       <c r="O4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T4" t="n">
         <v>4.2</v>
       </c>
-      <c r="P4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.78</v>
-      </c>
       <c r="U4" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="V4" t="n">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="AA4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE4" t="n">
         <v>2.75</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AF4" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>1.98</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46006.40625</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.7</v>
+        <v>3.25</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>5.75</v>
+        <v>2.2</v>
       </c>
       <c r="O6" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.7</v>
+        <v>2.95</v>
       </c>
       <c r="R6" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="S6" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="T6" t="n">
-        <v>4.2</v>
+        <v>3.78</v>
       </c>
       <c r="U6" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="V6" t="n">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
         <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.6</v>
+        <v>5.55</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.75</v>
+        <v>2.28</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.98</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46006.40625</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="M10" t="n">
-        <v>4.8</v>
+        <v>5.75</v>
       </c>
       <c r="N10" t="n">
-        <v>6.2</v>
+        <v>9.75</v>
       </c>
       <c r="O10" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="P10" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="T10" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="V10" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="W10" t="n">
         <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.2</v>
+        <v>4.13</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.32</v>
+        <v>1.34</v>
       </c>
       <c r="M11" t="n">
-        <v>3.29</v>
+        <v>4.8</v>
       </c>
       <c r="N11" t="n">
-        <v>2.97</v>
+        <v>6.2</v>
       </c>
       <c r="O11" t="n">
-        <v>2.8</v>
+        <v>1.74</v>
       </c>
       <c r="P11" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="S11" t="n">
-        <v>2.69</v>
+        <v>3.58</v>
       </c>
       <c r="T11" t="n">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="U11" t="n">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>4.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.05</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.28</v>
+        <v>2.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AF11" t="n">
         <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.55</v>
+        <v>3.2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.26</v>
+        <v>2.32</v>
       </c>
       <c r="M12" t="n">
-        <v>5.75</v>
+        <v>3.29</v>
       </c>
       <c r="N12" t="n">
-        <v>9.75</v>
+        <v>2.97</v>
       </c>
       <c r="O12" t="n">
-        <v>1.66</v>
+        <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>3.42</v>
+        <v>2.69</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="V12" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.46</v>
+        <v>1.91</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.25</v>
+        <v>3.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.13</v>
+        <v>1.55</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="M14" t="n">
-        <v>3.55</v>
+        <v>5.9</v>
       </c>
       <c r="N14" t="n">
-        <v>1.69</v>
+        <v>1.15</v>
       </c>
       <c r="O14" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>2.58</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.26</v>
+        <v>1.74</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="S14" t="n">
-        <v>2.84</v>
+        <v>3.5</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5</v>
+        <v>4.45</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.97</v>
+        <v>1.43</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>2.46</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.45</v>
+        <v>2.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="M15" t="n">
-        <v>5.9</v>
+        <v>3.55</v>
       </c>
       <c r="N15" t="n">
-        <v>1.15</v>
+        <v>1.69</v>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="P15" t="n">
-        <v>2.58</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.74</v>
+        <v>2.26</v>
       </c>
       <c r="R15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.22</v>
       </c>
-      <c r="S15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="W15" t="n">
+      <c r="AH15" t="n">
         <v>1.14</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.02</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.57</v>
+        <v>3.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>5.4</v>
+        <v>1.95</v>
       </c>
       <c r="O17" t="n">
-        <v>2.07</v>
+        <v>4.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.28</v>
+        <v>2.03</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>2.71</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>2.63</v>
+        <v>2.49</v>
       </c>
       <c r="T17" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="W17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X17" t="n">
         <v>1.08</v>
       </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.11</v>
+        <v>2.62</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2.3</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.44</v>
       </c>
-      <c r="M18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N18" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.34</v>
-      </c>
       <c r="S18" t="n">
-        <v>3.36</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.47</v>
+        <v>3.42</v>
       </c>
       <c r="U18" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="V18" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.7</v>
+        <v>2.49</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.86</v>
+        <v>1.26</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.19</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="N19" t="n">
-        <v>2.24</v>
+        <v>7.5</v>
       </c>
       <c r="O19" t="n">
-        <v>4.1</v>
+        <v>1.91</v>
       </c>
       <c r="P19" t="n">
-        <v>1.98</v>
+        <v>2.36</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>6.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>3.36</v>
       </c>
       <c r="T19" t="n">
-        <v>3.42</v>
+        <v>2.47</v>
       </c>
       <c r="U19" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="V19" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="W19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X19" t="n">
         <v>1</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.49</v>
+        <v>1.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.26</v>
+        <v>2.86</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.4</v>
+        <v>1.57</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N20" t="n">
-        <v>1.95</v>
+        <v>5.4</v>
       </c>
       <c r="O20" t="n">
-        <v>4.5</v>
+        <v>2.07</v>
       </c>
       <c r="P20" t="n">
-        <v>2.03</v>
+        <v>2.28</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.71</v>
+        <v>6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="S20" t="n">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="T20" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="V20" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.62</v>
+        <v>3.11</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AE20" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.5</v>
+        <v>2.03</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="N22" t="n">
-        <v>2.04</v>
+        <v>3.45</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>2.85</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.67</v>
+        <v>4.45</v>
       </c>
       <c r="R22" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S22" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="T22" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.36</v>
       </c>
-      <c r="V22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.35</v>
-      </c>
       <c r="Z22" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="P23" t="n">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>2.53</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="U23" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="V23" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.1</v>
+        <v>2.95</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O24" t="n">
         <v>4</v>
       </c>
-      <c r="O24" t="n">
-        <v>2.4</v>
-      </c>
       <c r="P24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA24" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="AB24" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC24" t="n">
         <v>4</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.95</v>
-      </c>
       <c r="AD24" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.28</v>
+        <v>1.83</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.94</v>
+        <v>1.22</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.96</v>
+        <v>3.12</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.7</v>
+        <v>3.03</v>
       </c>
       <c r="T25" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="U25" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="V25" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.8</v>
+        <v>3.24</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.6</v>
+        <v>3.15</v>
       </c>
       <c r="M26" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="O26" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="P26" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.12</v>
+        <v>2.98</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>3.03</v>
+        <v>2.56</v>
       </c>
       <c r="T26" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="U26" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="V26" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W26" t="n">
         <v>1.08</v>
       </c>
       <c r="X26" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.24</v>
+        <v>3.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -778,34 +778,34 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="M3" t="n">
         <v>2.85</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O3" t="n">
-        <v>3.02</v>
+        <v>2.82</v>
       </c>
       <c r="P3" t="n">
         <v>1.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.46</v>
+        <v>5.25</v>
       </c>
       <c r="R3" t="n">
         <v>1.66</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T3" t="n">
-        <v>3.9</v>
+        <v>4.33</v>
       </c>
       <c r="U3" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="V3" t="n">
         <v>9.800000000000001</v>
@@ -814,37 +814,37 @@
         <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AA3" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>6</v>
+        <v>6.95</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46006.39583333334</v>
@@ -897,31 +897,31 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="N4" t="n">
-        <v>5.75</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="P4" t="n">
         <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="R4" t="n">
         <v>1.74</v>
       </c>
       <c r="S4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T4" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="U4" t="n">
         <v>1.15</v>
@@ -933,37 +933,37 @@
         <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AA4" t="n">
         <v>3</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AG4" t="n">
         <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46006.40625</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,43 +1016,43 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="M5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q5" t="n">
         <v>2.95</v>
       </c>
-      <c r="N5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
         <v>1.57</v>
@@ -1061,28 +1061,28 @@
         <v>2.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46006.40625</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.25</v>
+        <v>1.95</v>
       </c>
       <c r="M6" t="n">
         <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46006.40625</v>
@@ -1254,16 +1254,16 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N7" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="O7" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="P7" t="n">
         <v>1.75</v>
@@ -1293,16 +1293,16 @@
         <v>1.09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AC7" t="n">
         <v>6.6</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.34</v>
+        <v>2.45</v>
       </c>
       <c r="M11" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>6.2</v>
+        <v>2.75</v>
       </c>
       <c r="O11" t="n">
-        <v>1.74</v>
+        <v>2.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.56</v>
+        <v>2.12</v>
       </c>
       <c r="Q11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V11" t="n">
         <v>6.5</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.55</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>3.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.18</v>
+        <v>3.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.66</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AF11" t="n">
         <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.2</v>
+        <v>1.56</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.32</v>
+        <v>1.34</v>
       </c>
       <c r="M12" t="n">
-        <v>3.29</v>
+        <v>4.8</v>
       </c>
       <c r="N12" t="n">
-        <v>2.97</v>
+        <v>6.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>1.74</v>
       </c>
       <c r="P12" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="S12" t="n">
-        <v>2.69</v>
+        <v>3.58</v>
       </c>
       <c r="T12" t="n">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="U12" t="n">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>4.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.05</v>
+        <v>5.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.91</v>
+        <v>1.47</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.28</v>
+        <v>2.18</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>1.66</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AF12" t="n">
         <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.55</v>
+        <v>3.2</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
         <v>3.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="P13" t="n">
         <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.94</v>
+        <v>3.83</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>2.55</v>
+        <v>2.82</v>
       </c>
       <c r="T13" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="U13" t="n">
         <v>1.33</v>
@@ -2031,7 +2031,7 @@
         <v>1.88</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
         <v>1.57</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="M14" t="n">
-        <v>5.9</v>
+        <v>3.55</v>
       </c>
       <c r="N14" t="n">
-        <v>1.15</v>
+        <v>1.69</v>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="P14" t="n">
-        <v>2.58</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.74</v>
+        <v>2.26</v>
       </c>
       <c r="R14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.22</v>
       </c>
-      <c r="S14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V14" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="W14" t="n">
+      <c r="AH14" t="n">
         <v>1.14</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.02</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="M15" t="n">
-        <v>3.55</v>
+        <v>5.9</v>
       </c>
       <c r="N15" t="n">
-        <v>1.69</v>
+        <v>1.15</v>
       </c>
       <c r="O15" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2.58</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.26</v>
+        <v>1.74</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="S15" t="n">
-        <v>2.84</v>
+        <v>3.5</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.63</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5</v>
+        <v>4.45</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.97</v>
+        <v>1.43</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>2.46</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.45</v>
+        <v>2.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2328,7 +2328,7 @@
         <v>1.5</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="N16" t="n">
         <v>7</v>
@@ -2343,19 +2343,19 @@
         <v>6.25</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
         <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V16" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
         <v>1.02</v>
@@ -2364,34 +2364,34 @@
         <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AB16" t="n">
         <v>1.64</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
         <v>2.2</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46006.65625</v>
@@ -2444,16 +2444,16 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="M17" t="n">
         <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="P17" t="n">
         <v>2.03</v>
@@ -2462,10 +2462,10 @@
         <v>2.71</v>
       </c>
       <c r="R17" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="S17" t="n">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="T17" t="n">
         <v>3.2</v>
@@ -2474,7 +2474,7 @@
         <v>1.27</v>
       </c>
       <c r="V17" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="W17" t="n">
         <v>1.01</v>
@@ -2486,16 +2486,16 @@
         <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="AD17" t="n">
         <v>1.17</v>
@@ -2504,10 +2504,10 @@
         <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="AH17" t="n">
         <v>1.25</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.19</v>
+        <v>1.58</v>
       </c>
       <c r="M18" t="n">
-        <v>2.8</v>
+        <v>3.59</v>
       </c>
       <c r="N18" t="n">
-        <v>2.24</v>
+        <v>5.3</v>
       </c>
       <c r="O18" t="n">
-        <v>4.1</v>
+        <v>2.07</v>
       </c>
       <c r="P18" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T18" t="n">
-        <v>3.42</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.29</v>
       </c>
-      <c r="V18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.45</v>
-      </c>
       <c r="Z18" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.49</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AF18" t="n">
         <v>1.73</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.26</v>
+        <v>2.25</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.44</v>
       </c>
-      <c r="M19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N19" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.34</v>
-      </c>
       <c r="S19" t="n">
-        <v>3.36</v>
+        <v>2.34</v>
       </c>
       <c r="T19" t="n">
-        <v>2.47</v>
+        <v>3.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="V19" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.08</v>
       </c>
-      <c r="X19" t="n">
-        <v>1</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.2</v>
+        <v>2.62</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.75</v>
+        <v>3.85</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.86</v>
+        <v>1.3</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,37 +2801,37 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="M20" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="N20" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O20" t="n">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="P20" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="R20" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="S20" t="n">
-        <v>2.63</v>
+        <v>3.36</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="U20" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="V20" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="W20" t="n">
         <v>1.08</v>
@@ -2840,34 +2840,34 @@
         <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.11</v>
+        <v>4.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AB20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AF20" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="M21" t="n">
-        <v>4.2</v>
+        <v>3.83</v>
       </c>
       <c r="N21" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="O21" t="n">
         <v>1.85</v>
       </c>
       <c r="P21" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="T21" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="U21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
         <v>8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46006.6875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.03</v>
+        <v>1.89</v>
       </c>
       <c r="M22" t="n">
-        <v>2.97</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="O22" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="P22" t="n">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>2.53</v>
+        <v>3.2</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="U22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.33</v>
       </c>
-      <c r="V22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.89</v>
+        <v>2.03</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>2.97</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="O23" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>1.96</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="R23" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.36</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.26</v>
-      </c>
       <c r="Z23" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.95</v>
+        <v>4.1</v>
       </c>
       <c r="AD23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE23" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.94</v>
+        <v>1.67</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3408,7 +3408,7 @@
         <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="Q25" t="n">
         <v>3.12</v>
@@ -3426,7 +3426,7 @@
         <v>1.41</v>
       </c>
       <c r="V25" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W25" t="n">
         <v>1.08</v>
@@ -3435,7 +3435,7 @@
         <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z25" t="n">
         <v>3.45</v>
@@ -3444,7 +3444,7 @@
         <v>1.93</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
         <v>3.24</v>
@@ -3459,10 +3459,10 @@
         <v>2.13</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3637,16 +3637,16 @@
         <v>1.75</v>
       </c>
       <c r="M27" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N27" t="n">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="O27" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="P27" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="Q27" t="n">
         <v>3.95</v>
@@ -3676,13 +3676,13 @@
         <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA27" t="n">
         <v>1.63</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.37</v>
+        <v>2.49</v>
       </c>
       <c r="AC27" t="n">
         <v>2.43</v>
@@ -3694,13 +3694,13 @@
         <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AG27" t="n">
         <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="M28" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="N28" t="n">
         <v>16</v>
@@ -3777,7 +3777,7 @@
         <v>3.34</v>
       </c>
       <c r="T28" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="U28" t="n">
         <v>1.52</v>
@@ -3789,13 +3789,13 @@
         <v>1.09</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
         <v>1.14</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="AA28" t="n">
         <v>1.57</v>
@@ -3810,7 +3810,7 @@
         <v>1.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.51</v>
+        <v>2.35</v>
       </c>
       <c r="AF28" t="n">
         <v>1.42</v>
@@ -3819,7 +3819,7 @@
         <v>1.04</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.85</v>
+        <v>4.6</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46006.73958333334</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.15</v>
       </c>
-      <c r="M4" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="V4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AA4" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46006.40625</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
         <v>2.85</v>
       </c>
       <c r="N5" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
-        <v>4.2</v>
+        <v>2.42</v>
       </c>
       <c r="P5" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.95</v>
+        <v>6.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="S5" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="T5" t="n">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="U5" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="V5" t="n">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.25</v>
+        <v>2.79</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46006.40625</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,43 +1135,43 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.95</v>
+        <v>3.6</v>
       </c>
       <c r="M6" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q6" t="n">
         <v>2.95</v>
       </c>
-      <c r="N6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
         <v>1.57</v>
@@ -1180,28 +1180,28 @@
         <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46006.40625</v>
@@ -1492,19 +1492,19 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>3.47</v>
       </c>
       <c r="O9" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="P9" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
         <v>3.8</v>
@@ -1513,13 +1513,13 @@
         <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="T9" t="n">
         <v>2.87</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
         <v>6</v>
@@ -1537,28 +1537,28 @@
         <v>3.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AC9" t="n">
         <v>2.97</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AF9" t="n">
         <v>1.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46006.52083333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="M10" t="n">
-        <v>5.75</v>
+        <v>4.8</v>
       </c>
       <c r="N10" t="n">
-        <v>9.75</v>
+        <v>6.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="P10" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S10" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="V10" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="W10" t="n">
         <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.13</v>
+        <v>3.2</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="M12" t="n">
-        <v>4.8</v>
+        <v>5.75</v>
       </c>
       <c r="N12" t="n">
-        <v>6.2</v>
+        <v>9.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="P12" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="T12" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="V12" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="W12" t="n">
         <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.2</v>
+        <v>4.13</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1971,10 +1971,10 @@
         <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O13" t="n">
         <v>2.76</v>
@@ -2013,10 +2013,10 @@
         <v>2.85</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC13" t="n">
         <v>3.62</v>
@@ -2090,25 +2090,25 @@
         <v>4.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="N14" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="O14" t="n">
         <v>4.75</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
         <v>2.26</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="T14" t="n">
         <v>3</v>
@@ -2132,28 +2132,28 @@
         <v>3.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF14" t="n">
         <v>1.78</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2218,10 +2218,10 @@
         <v>6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R15" t="n">
         <v>1.22</v>
@@ -2230,7 +2230,7 @@
         <v>3.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="U15" t="n">
         <v>1.63</v>
@@ -2251,16 +2251,16 @@
         <v>5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.46</v>
+        <v>2.59</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="AE15" t="n">
         <v>1.73</v>
@@ -2272,7 +2272,7 @@
         <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M16" t="n">
-        <v>3.92</v>
+        <v>3.95</v>
       </c>
       <c r="N16" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="O16" t="n">
         <v>2.05</v>
@@ -2370,10 +2370,10 @@
         <v>2.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
         <v>3.84</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.47</v>
+        <v>1.44</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="O17" t="n">
-        <v>4.3</v>
+        <v>1.91</v>
       </c>
       <c r="P17" t="n">
-        <v>2.03</v>
+        <v>2.36</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.71</v>
+        <v>6.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.46</v>
+        <v>1.34</v>
       </c>
       <c r="S17" t="n">
-        <v>2.41</v>
+        <v>3.36</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2</v>
+        <v>2.47</v>
       </c>
       <c r="U17" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="V17" t="n">
-        <v>8.5</v>
+        <v>5.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z17" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,40 +2682,40 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.25</v>
+        <v>3.47</v>
       </c>
       <c r="M19" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>4.05</v>
+        <v>4.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.98</v>
+        <v>2.71</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S19" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="T19" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V19" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
         <v>1.08</v>
@@ -2724,31 +2724,31 @@
         <v>1.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.31</v>
+        <v>1.7</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R20" t="n">
         <v>1.44</v>
       </c>
-      <c r="M20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.34</v>
-      </c>
       <c r="S20" t="n">
-        <v>3.36</v>
+        <v>2.34</v>
       </c>
       <c r="T20" t="n">
-        <v>2.47</v>
+        <v>3.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
         <v>1.08</v>
       </c>
-      <c r="X20" t="n">
-        <v>1</v>
-      </c>
       <c r="Y20" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.2</v>
+        <v>2.62</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.75</v>
+        <v>3.85</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.4</v>
+        <v>1.15</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.89</v>
+        <v>3.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="N22" t="n">
-        <v>3.75</v>
+        <v>1.95</v>
       </c>
       <c r="O22" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC22" t="n">
         <v>4</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.95</v>
-      </c>
       <c r="AD22" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="M23" t="n">
-        <v>2.97</v>
+        <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="O23" t="n">
         <v>2.85</v>
@@ -3203,10 +3203,10 @@
         <v>3.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
         <v>4.1</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N24" t="n">
-        <v>2.04</v>
+        <v>3.92</v>
       </c>
       <c r="O24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q24" t="n">
         <v>4</v>
       </c>
-      <c r="P24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T24" t="n">
         <v>2.67</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.25</v>
-      </c>
       <c r="U24" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="V24" t="n">
-        <v>7.6</v>
+        <v>6.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="AC24" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AE24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.15</v>
+        <v>1.85</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>2.32</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
-        <v>3.65</v>
+        <v>2.38</v>
       </c>
       <c r="P26" t="n">
-        <v>2.12</v>
+        <v>2.29</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.98</v>
+        <v>3.95</v>
       </c>
       <c r="R26" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>2.56</v>
+        <v>3.5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="U26" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="V26" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X26" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.95</v>
+        <v>5.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.72</v>
+        <v>2.35</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG26" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.75</v>
+        <v>3.55</v>
       </c>
       <c r="M27" t="n">
-        <v>3.9</v>
+        <v>3.27</v>
       </c>
       <c r="N27" t="n">
-        <v>3.92</v>
+        <v>2.07</v>
       </c>
       <c r="O27" t="n">
-        <v>2.38</v>
+        <v>3.65</v>
       </c>
       <c r="P27" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.95</v>
+        <v>2.98</v>
       </c>
       <c r="R27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V27" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.25</v>
       </c>
-      <c r="S27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V27" t="n">
-        <v>5</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AE27" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="M28" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="N28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O28" t="n">
         <v>1.53</v>
@@ -3798,16 +3798,16 @@
         <v>3.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AE28" t="n">
         <v>2.35</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -823,10 +823,10 @@
         <v>2</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC3" t="n">
         <v>6.95</v>
@@ -838,7 +838,7 @@
         <v>2.57</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG3" t="n">
         <v>1.33</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="M4" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.4</v>
+        <v>2.94</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46006.40625</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="M5" t="n">
         <v>2.85</v>
       </c>
       <c r="N5" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="O5" t="n">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.9</v>
+        <v>2.95</v>
       </c>
       <c r="R5" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="T5" t="n">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="V5" t="n">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>3</v>
+        <v>2.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.79</v>
+        <v>2.41</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH5" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46006.40625</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,43 +1135,43 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="M6" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>2.15</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.95</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>1.57</v>
@@ -1180,28 +1180,28 @@
         <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46006.40625</v>
@@ -1272,10 +1272,10 @@
         <v>2.96</v>
       </c>
       <c r="R7" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T7" t="n">
         <v>4.2</v>
@@ -1299,10 +1299,10 @@
         <v>2.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AC7" t="n">
         <v>6.6</v>
@@ -1510,13 +1510,13 @@
         <v>3.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
         <v>2.73</v>
       </c>
       <c r="T9" t="n">
-        <v>2.87</v>
+        <v>2.69</v>
       </c>
       <c r="U9" t="n">
         <v>1.4</v>
@@ -1531,10 +1531,10 @@
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AA9" t="n">
         <v>1.77</v>
@@ -1543,13 +1543,13 @@
         <v>1.93</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AD9" t="n">
         <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AF9" t="n">
         <v>1.95</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="M10" t="n">
-        <v>4.8</v>
+        <v>5.75</v>
       </c>
       <c r="N10" t="n">
-        <v>6.2</v>
+        <v>9.75</v>
       </c>
       <c r="O10" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="P10" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="T10" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="V10" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="W10" t="n">
         <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.2</v>
+        <v>4.13</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1742,7 +1742,7 @@
         <v>2.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
         <v>3.5</v>
@@ -1781,7 +1781,7 @@
         <v>1.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD11" t="n">
         <v>1.3</v>
@@ -1790,13 +1790,13 @@
         <v>1.73</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="M12" t="n">
-        <v>5.75</v>
+        <v>4.8</v>
       </c>
       <c r="N12" t="n">
-        <v>9.75</v>
+        <v>6.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="P12" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S12" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="V12" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="W12" t="n">
         <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.96</v>
+        <v>1.74</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AH12" t="n">
-        <v>4.13</v>
+        <v>3.2</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1977,22 +1977,22 @@
         <v>3.15</v>
       </c>
       <c r="O13" t="n">
-        <v>2.76</v>
+        <v>3.04</v>
       </c>
       <c r="P13" t="n">
         <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="R13" t="n">
         <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>2.82</v>
+        <v>2.53</v>
       </c>
       <c r="T13" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="U13" t="n">
         <v>1.33</v>
@@ -2010,7 +2010,7 @@
         <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="AA13" t="n">
         <v>2.05</v>
@@ -2019,10 +2019,10 @@
         <v>1.68</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
         <v>1.83</v>
@@ -2031,7 +2031,7 @@
         <v>1.88</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
         <v>1.57</v>
@@ -2105,13 +2105,13 @@
         <v>2.26</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
         <v>2.66</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U14" t="n">
         <v>1.36</v>
@@ -2141,7 +2141,7 @@
         <v>3.55</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
         <v>1.83</v>
@@ -2215,7 +2215,7 @@
         <v>1.15</v>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>6.97</v>
       </c>
       <c r="P15" t="n">
         <v>2.63</v>
@@ -2230,10 +2230,10 @@
         <v>3.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="U15" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V15" t="n">
         <v>4.45</v>
@@ -2266,13 +2266,13 @@
         <v>1.73</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG15" t="n">
         <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2334,7 +2334,7 @@
         <v>7.3</v>
       </c>
       <c r="O16" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="P16" t="n">
         <v>2.08</v>
@@ -2346,16 +2346,16 @@
         <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>2.53</v>
+        <v>2.64</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="U16" t="n">
         <v>1.31</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>8.1</v>
       </c>
       <c r="W16" t="n">
         <v>1.02</v>
@@ -2364,7 +2364,7 @@
         <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
         <v>2.8</v>
@@ -2385,13 +2385,13 @@
         <v>2.2</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46006.65625</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.44</v>
+        <v>3.25</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>2.94</v>
       </c>
       <c r="N17" t="n">
-        <v>6.5</v>
+        <v>2.22</v>
       </c>
       <c r="O17" t="n">
-        <v>1.91</v>
+        <v>4.05</v>
       </c>
       <c r="P17" t="n">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.2</v>
+        <v>2.92</v>
       </c>
       <c r="R17" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="S17" t="n">
-        <v>3.36</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.47</v>
+        <v>3.28</v>
       </c>
       <c r="U17" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="V17" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
         <v>1.08</v>
       </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.75</v>
+        <v>3.85</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.4</v>
       </c>
-      <c r="AE17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH17" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="M18" t="n">
-        <v>3.59</v>
+        <v>3.83</v>
       </c>
       <c r="N18" t="n">
-        <v>5.3</v>
+        <v>7.7</v>
       </c>
       <c r="O18" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="P18" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>2.97</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="W18" t="n">
         <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.25</v>
+        <v>2.87</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.92</v>
+        <v>2.29</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.47</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="O19" t="n">
-        <v>4.3</v>
+        <v>1.92</v>
       </c>
       <c r="P19" t="n">
-        <v>2.03</v>
+        <v>2.36</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.71</v>
+        <v>6.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="S19" t="n">
-        <v>2.41</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>3.2</v>
+        <v>2.54</v>
       </c>
       <c r="U19" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="V19" t="n">
-        <v>8.5</v>
+        <v>5.8</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z19" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AE19" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.7</v>
+        <v>1.21</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.25</v>
+        <v>2.72</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,40 +2801,40 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.25</v>
+        <v>3.47</v>
       </c>
       <c r="M20" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.98</v>
+        <v>2.71</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S20" t="n">
-        <v>2.34</v>
+        <v>2.49</v>
       </c>
       <c r="T20" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U20" t="n">
         <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
         <v>1.08</v>
@@ -2843,31 +2843,31 @@
         <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="M21" t="n">
-        <v>3.83</v>
+        <v>3.59</v>
       </c>
       <c r="N21" t="n">
-        <v>7.7</v>
+        <v>5.3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>7.6</v>
+        <v>6.67</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="S21" t="n">
-        <v>2.47</v>
+        <v>2.78</v>
       </c>
       <c r="T21" t="n">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W21" t="n">
         <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.29</v>
+        <v>1.92</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46006.6875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.6</v>
+        <v>2.11</v>
       </c>
       <c r="M22" t="n">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>3.62</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>2.59</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.67</v>
+        <v>3.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S22" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="T22" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="U22" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="W22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X22" t="n">
         <v>1.03</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y22" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>3.41</v>
       </c>
       <c r="N23" t="n">
-        <v>3.62</v>
+        <v>3.92</v>
       </c>
       <c r="O23" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="P23" t="n">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>2.53</v>
+        <v>3.2</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="V23" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE23" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2</v>
-      </c>
       <c r="AF23" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.41</v>
+        <v>3.04</v>
       </c>
       <c r="N24" t="n">
-        <v>3.92</v>
+        <v>1.95</v>
       </c>
       <c r="O24" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="Q24" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC24" t="n">
         <v>4</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y24" t="n">
+      <c r="AD24" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z24" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD24" t="n">
+      <c r="AE24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.91</v>
+        <v>1.24</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.6</v>
+        <v>3.55</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>3.27</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="P25" t="n">
         <v>2.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.12</v>
+        <v>2.99</v>
       </c>
       <c r="R25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.36</v>
       </c>
-      <c r="S25" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V25" t="n">
-        <v>7</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="P26" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.95</v>
+        <v>3.12</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>3.5</v>
+        <v>3.03</v>
       </c>
       <c r="T26" t="n">
-        <v>2.36</v>
+        <v>2.89</v>
       </c>
       <c r="U26" t="n">
-        <v>1.61</v>
+        <v>1.41</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W26" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.25</v>
+        <v>3.45</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>3.24</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.05</v>
+        <v>1.43</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.55</v>
+        <v>1.85</v>
       </c>
       <c r="M27" t="n">
-        <v>3.27</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.07</v>
+        <v>3.85</v>
       </c>
       <c r="O27" t="n">
-        <v>3.65</v>
+        <v>2.3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.98</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="S27" t="n">
-        <v>2.56</v>
+        <v>3.5</v>
       </c>
       <c r="T27" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="U27" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="V27" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X27" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.95</v>
+        <v>5</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="AD27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.25</v>
       </c>
-      <c r="AE27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.36</v>
+        <v>2.05</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3792,7 +3792,7 @@
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z28" t="n">
         <v>3.95</v>
@@ -3816,7 +3816,7 @@
         <v>1.42</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AH28" t="n">
         <v>4.6</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="M4" t="n">
         <v>2.85</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="O4" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.4</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="S4" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="T4" t="n">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="U4" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="V4" t="n">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.94</v>
+        <v>2.35</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.79</v>
+        <v>2.41</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.99</v>
+        <v>1.25</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46006.40625</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,43 +1016,43 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="M5" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>2.15</v>
+        <v>4.1</v>
       </c>
       <c r="O5" t="n">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="P5" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.95</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>1.57</v>
@@ -1061,28 +1061,28 @@
         <v>2.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46006.40625</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.4</v>
+        <v>2.94</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46006.40625</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="N10" t="n">
-        <v>9.75</v>
+        <v>6.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>5.22</v>
       </c>
       <c r="R10" t="n">
         <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="T10" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="W10" t="n">
         <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA10" t="n">
         <v>1.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.96</v>
+        <v>1.69</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.13</v>
+        <v>3</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.45</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="N11" t="n">
-        <v>2.75</v>
+        <v>9.75</v>
       </c>
       <c r="O11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="P11" t="n">
         <v>2.8</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Q11" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="S11" t="n">
-        <v>2.73</v>
+        <v>3.34</v>
       </c>
       <c r="T11" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.28</v>
+        <v>2.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AE11" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.73</v>
       </c>
-      <c r="AF11" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>3.37</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.34</v>
+        <v>2.45</v>
       </c>
       <c r="M12" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>6.2</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.74</v>
+        <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>2.56</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V12" t="n">
         <v>6.5</v>
       </c>
-      <c r="R12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.55</v>
-      </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.5</v>
+        <v>3.05</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.18</v>
+        <v>3.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.66</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,40 +2444,40 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.25</v>
+        <v>3.47</v>
       </c>
       <c r="M17" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.92</v>
+        <v>2.71</v>
       </c>
       <c r="R17" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="T17" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
         <v>1.08</v>
@@ -2486,31 +2486,31 @@
         <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.44</v>
+        <v>3.25</v>
       </c>
       <c r="M19" t="n">
-        <v>4.5</v>
+        <v>2.94</v>
       </c>
       <c r="N19" t="n">
-        <v>6.5</v>
+        <v>2.22</v>
       </c>
       <c r="O19" t="n">
-        <v>1.92</v>
+        <v>4.05</v>
       </c>
       <c r="P19" t="n">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.2</v>
+        <v>2.92</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.54</v>
+        <v>3.28</v>
       </c>
       <c r="U19" t="n">
-        <v>1.52</v>
+        <v>1.26</v>
       </c>
       <c r="V19" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.08</v>
       </c>
-      <c r="X19" t="n">
-        <v>1</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.75</v>
+        <v>3.85</v>
       </c>
       <c r="AD19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.4</v>
       </c>
-      <c r="AE19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH19" t="n">
-        <v>2.72</v>
+        <v>1.3</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.47</v>
+        <v>1.44</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="O20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z20" t="n">
         <v>4.2</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y20" t="n">
+      <c r="AA20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.25</v>
+        <v>2.72</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.11</v>
+        <v>3.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.13</v>
+        <v>3.04</v>
       </c>
       <c r="N22" t="n">
-        <v>3.62</v>
+        <v>1.95</v>
       </c>
       <c r="O22" t="n">
-        <v>2.59</v>
+        <v>4.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.9</v>
+        <v>2.66</v>
       </c>
       <c r="R22" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="S22" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="T22" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V22" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD22" t="n">
         <v>1.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AG22" t="n">
         <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="M23" t="n">
-        <v>3.41</v>
+        <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>3.92</v>
+        <v>3.62</v>
       </c>
       <c r="O23" t="n">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
       <c r="P23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA23" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q23" t="n">
-        <v>4</v>
-      </c>
-      <c r="R23" t="n">
+      <c r="AB23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.33</v>
       </c>
-      <c r="S23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="M24" t="n">
-        <v>3.04</v>
+        <v>3.41</v>
       </c>
       <c r="N24" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.95</v>
-      </c>
-      <c r="O24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.24</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.55</v>
+        <v>2.56</v>
       </c>
       <c r="M25" t="n">
-        <v>3.27</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.07</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.99</v>
+        <v>3.11</v>
       </c>
       <c r="R25" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.53</v>
+        <v>2.93</v>
       </c>
       <c r="T25" t="n">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="U25" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="V25" t="n">
-        <v>8.4</v>
+        <v>6.75</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.95</v>
+        <v>3.24</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.87</v>
+        <v>2.13</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.6</v>
+        <v>3.55</v>
       </c>
       <c r="M26" t="n">
-        <v>3.35</v>
+        <v>3.27</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>2.07</v>
       </c>
       <c r="O26" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="P26" t="n">
         <v>2.12</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.12</v>
+        <v>2.99</v>
       </c>
       <c r="R26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG26" t="n">
         <v>1.36</v>
       </c>
-      <c r="S26" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V26" t="n">
-        <v>7</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI30"/>
+  <dimension ref="A1:AI24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -698,34 +698,34 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46006.29166666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="M4" t="n">
         <v>2.85</v>
       </c>
       <c r="N4" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="P4" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.95</v>
+        <v>6.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="S4" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="T4" t="n">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="U4" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="V4" t="n">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.35</v>
+        <v>2.94</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.41</v>
+        <v>2.79</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.31</v>
+        <v>1.07</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>1.99</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46006.40625</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="M6" t="n">
         <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="O6" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.4</v>
+        <v>2.95</v>
       </c>
       <c r="R6" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="S6" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="T6" t="n">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="V6" t="n">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.94</v>
+        <v>2.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.79</v>
+        <v>2.41</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.99</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46006.40625</v>
@@ -1376,19 +1376,19 @@
         <v>1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1412,34 +1412,34 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46006.5</v>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,76 +1492,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.89</v>
+        <v>1.26</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>5.75</v>
       </c>
       <c r="N9" t="n">
-        <v>3.47</v>
+        <v>9.75</v>
       </c>
       <c r="O9" t="n">
-        <v>2.37</v>
+        <v>1.66</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>2.73</v>
+        <v>3.34</v>
       </c>
       <c r="T9" t="n">
-        <v>2.69</v>
+        <v>2.25</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="V9" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.8</v>
+        <v>3.37</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46006.52083333334</v>
+        <v>46006.58333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1611,34 +1611,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>5.4</v>
+        <v>4.65</v>
       </c>
       <c r="N10" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="O10" t="n">
         <v>1.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.22</v>
+        <v>6.66</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S10" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="U10" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="V10" t="n">
         <v>4.55</v>
@@ -1647,34 +1647,34 @@
         <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
         <v>1.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AB10" t="n">
         <v>2.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AH10" t="n">
         <v>3</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.26</v>
+        <v>2.45</v>
       </c>
       <c r="M11" t="n">
-        <v>5.75</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>9.75</v>
+        <v>2.75</v>
       </c>
       <c r="O11" t="n">
-        <v>1.66</v>
+        <v>2.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>3.34</v>
+        <v>2.73</v>
       </c>
       <c r="T11" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="U11" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="V11" t="n">
-        <v>4.9</v>
+        <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.8</v>
+        <v>3.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.3</v>
+        <v>3.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.97</v>
       </c>
-      <c r="AF11" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.37</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>3.84</v>
       </c>
       <c r="R12" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>2.73</v>
+        <v>2.53</v>
       </c>
       <c r="T12" t="n">
-        <v>2.62</v>
+        <v>3.04</v>
       </c>
       <c r="U12" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46006.58333333334</v>
+        <v>46006.60416666666</v>
       </c>
     </row>
     <row r="13">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,76 +1968,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="N13" t="n">
-        <v>3.15</v>
+        <v>7.3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.04</v>
+        <v>2.09</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.84</v>
+        <v>6.25</v>
       </c>
       <c r="R13" t="n">
         <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>2.53</v>
+        <v>2.64</v>
       </c>
       <c r="T13" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="W13" t="n">
         <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.54</v>
+        <v>3.84</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.57</v>
+        <v>2.43</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46006.60416666666</v>
+        <v>46006.65625</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.56</v>
+        <v>2.94</v>
       </c>
       <c r="N14" t="n">
-        <v>1.61</v>
+        <v>2.22</v>
       </c>
       <c r="O14" t="n">
-        <v>4.75</v>
+        <v>4.05</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.26</v>
+        <v>2.92</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="S14" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.85</v>
+        <v>3.28</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.94</v>
+        <v>2.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.3</v>
       </c>
-      <c r="AH14" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AI14" s="3" t="n">
-        <v>46006.64583333334</v>
+        <v>46006.6875</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,76 +2206,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>12</v>
+        <v>1.41</v>
       </c>
       <c r="M15" t="n">
-        <v>5.9</v>
+        <v>3.83</v>
       </c>
       <c r="N15" t="n">
-        <v>1.15</v>
+        <v>7.7</v>
       </c>
       <c r="O15" t="n">
-        <v>6.97</v>
+        <v>1.85</v>
       </c>
       <c r="P15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH15" t="n">
         <v>2.63</v>
       </c>
-      <c r="Q15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AI15" s="3" t="n">
-        <v>46006.64583333334</v>
+        <v>46006.6875</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="M16" t="n">
-        <v>3.95</v>
+        <v>3.59</v>
       </c>
       <c r="N16" t="n">
-        <v>7.3</v>
+        <v>5.3</v>
       </c>
       <c r="O16" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="P16" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.25</v>
+        <v>6.67</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>2.64</v>
+        <v>2.78</v>
       </c>
       <c r="T16" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="U16" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.84</v>
+        <v>3.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AE16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH16" t="n">
         <v>2.2</v>
       </c>
-      <c r="AF16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>2.43</v>
-      </c>
       <c r="AI16" s="3" t="n">
-        <v>46006.65625</v>
+        <v>46006.6875</v>
       </c>
     </row>
     <row r="17">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,76 +2563,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.41</v>
+        <v>2.11</v>
       </c>
       <c r="M18" t="n">
-        <v>3.83</v>
+        <v>3.13</v>
       </c>
       <c r="N18" t="n">
-        <v>7.7</v>
+        <v>3.62</v>
       </c>
       <c r="O18" t="n">
-        <v>1.85</v>
+        <v>2.59</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.5</v>
+        <v>3.9</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S18" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="T18" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="U18" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="W18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X18" t="n">
         <v>1.03</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AD18" t="n">
         <v>1.22</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.29</v>
+        <v>1.98</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.63</v>
+        <v>1.67</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46006.6875</v>
+        <v>46006.69791666666</v>
       </c>
     </row>
     <row r="19">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,76 +2682,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="M19" t="n">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="N19" t="n">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="O19" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.92</v>
+        <v>2.66</v>
       </c>
       <c r="R19" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="T19" t="n">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="U19" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V19" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z19" t="n">
         <v>2.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46006.6875</v>
+        <v>46006.69791666666</v>
       </c>
     </row>
     <row r="20">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,76 +2801,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>6.5</v>
+        <v>3.85</v>
       </c>
       <c r="O20" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="P20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T20" t="n">
         <v>2.36</v>
       </c>
-      <c r="Q20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.54</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="V20" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AB20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH20" t="n">
         <v>2.05</v>
       </c>
-      <c r="AC20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>2.72</v>
-      </c>
       <c r="AI20" s="3" t="n">
-        <v>46006.6875</v>
+        <v>46006.70833333334</v>
       </c>
     </row>
     <row r="21">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,76 +2920,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.58</v>
+        <v>3.55</v>
       </c>
       <c r="M21" t="n">
-        <v>3.59</v>
+        <v>3.27</v>
       </c>
       <c r="N21" t="n">
-        <v>5.3</v>
+        <v>2.07</v>
       </c>
       <c r="O21" t="n">
-        <v>2.11</v>
+        <v>3.65</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.67</v>
+        <v>2.99</v>
       </c>
       <c r="R21" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>2.78</v>
+        <v>2.53</v>
       </c>
       <c r="T21" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46006.6875</v>
+        <v>46006.70833333334</v>
       </c>
     </row>
     <row r="22">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,76 +3039,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.6</v>
+        <v>1.16</v>
       </c>
       <c r="M22" t="n">
-        <v>3.04</v>
+        <v>7.1</v>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>15</v>
       </c>
       <c r="O22" t="n">
-        <v>4.2</v>
+        <v>1.53</v>
       </c>
       <c r="P22" t="n">
-        <v>1.97</v>
+        <v>2.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.66</v>
+        <v>10</v>
       </c>
       <c r="R22" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>2.47</v>
+        <v>3.34</v>
       </c>
       <c r="T22" t="n">
-        <v>2.88</v>
+        <v>2.36</v>
       </c>
       <c r="U22" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="V22" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="W22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X22" t="n">
         <v>1.03</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y22" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.8</v>
+        <v>3.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>1.55</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>4</v>
+        <v>2.37</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.91</v>
+        <v>2.35</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.8</v>
+        <v>1.42</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.03</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.24</v>
+        <v>4.6</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46006.69791666666</v>
+        <v>46006.73958333334</v>
       </c>
     </row>
     <row r="23">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,76 +3158,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46006.69791666666</v>
+        <v>46006.79166666666</v>
       </c>
     </row>
     <row r="24">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,789 +3277,75 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46006.69791666666</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
-        <v>46006</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Spain La Liga</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Rayo Vallecano</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Real Betis</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="M25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V25" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI25" s="3" t="n">
-        <v>46006.70833333334</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>46006</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>England Championship</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Sheffield Wednesday</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Derby County</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="M26" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="N26" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="O26" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V26" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI26" s="3" t="n">
-        <v>46006.70833333334</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
-        <v>46006</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>England Premier League</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Manchester United</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>AFC Bournemouth</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="M27" t="n">
-        <v>4</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>4</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V27" t="n">
-        <v>5</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI27" s="3" t="n">
-        <v>46006.70833333334</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>46006</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Portugal Liga NOS</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Estrela Amadora</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="M28" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>15</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>10</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V28" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AI28" s="3" t="n">
-        <v>46006.73958333334</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>46006</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Spanish Town Police FC</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Waterhouse</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" s="3" t="n">
-        <v>46006.79166666666</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>46006</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Arnett Gardens</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Montego Bay United</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" s="3" t="n">
         <v>46006.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI24"/>
+  <dimension ref="A1:AI30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="M4" t="n">
         <v>2.85</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="O4" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.4</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="S4" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="T4" t="n">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="U4" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="V4" t="n">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.94</v>
+        <v>2.35</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.79</v>
+        <v>2.41</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.99</v>
+        <v>1.25</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46006.40625</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="M6" t="n">
         <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="P6" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.95</v>
+        <v>6.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="S6" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="U6" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="V6" t="n">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.35</v>
+        <v>2.94</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.41</v>
+        <v>2.79</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.31</v>
+        <v>1.07</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.99</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46006.40625</v>
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,76 +1492,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.26</v>
+        <v>1.89</v>
       </c>
       <c r="M9" t="n">
-        <v>5.75</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>9.75</v>
+        <v>3.47</v>
       </c>
       <c r="O9" t="n">
-        <v>1.66</v>
+        <v>2.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>4.76</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>3.34</v>
+        <v>3.01</v>
       </c>
       <c r="T9" t="n">
-        <v>2.25</v>
+        <v>2.85</v>
       </c>
       <c r="U9" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
-        <v>4.9</v>
+        <v>6.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.8</v>
+        <v>3.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.37</v>
+        <v>1.8</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46006.58333333334</v>
+        <v>46006.52083333334</v>
       </c>
     </row>
     <row r="10">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.35</v>
       </c>
-      <c r="M10" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6.66</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AH10" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.45</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="N11" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P11" t="n">
         <v>2.75</v>
       </c>
-      <c r="O11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Q11" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>2.73</v>
+        <v>3.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.37</v>
+        <v>1.6</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.28</v>
+        <v>2.32</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>4.65</v>
       </c>
       <c r="N12" t="n">
-        <v>3.15</v>
+        <v>5.9</v>
       </c>
       <c r="O12" t="n">
-        <v>3.04</v>
+        <v>1.75</v>
       </c>
       <c r="P12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T12" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q12" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.04</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="V12" t="n">
-        <v>8.199999999999999</v>
+        <v>4.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.99</v>
+        <v>5</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>1.47</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.68</v>
+        <v>2.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.54</v>
+        <v>2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.57</v>
+        <v>3</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46006.60416666666</v>
+        <v>46006.58333333334</v>
       </c>
     </row>
     <row r="13">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,76 +1968,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>7.3</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
-        <v>2.09</v>
+        <v>3.02</v>
       </c>
       <c r="P13" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.25</v>
+        <v>3.84</v>
       </c>
       <c r="R13" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="T13" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="U13" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W13" t="n">
         <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.84</v>
+        <v>3.62</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.43</v>
+        <v>1.54</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46006.65625</v>
+        <v>46006.60416666666</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="M14" t="n">
-        <v>2.94</v>
+        <v>3.56</v>
       </c>
       <c r="N14" t="n">
-        <v>2.22</v>
+        <v>1.61</v>
       </c>
       <c r="O14" t="n">
-        <v>4.05</v>
+        <v>5.35</v>
       </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.92</v>
+        <v>2.28</v>
       </c>
       <c r="R14" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC14" t="n">
         <v>3.28</v>
       </c>
-      <c r="U14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AD14" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46006.6875</v>
+        <v>46006.64583333334</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,76 +2206,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.41</v>
+        <v>12</v>
       </c>
       <c r="M15" t="n">
-        <v>3.83</v>
+        <v>5.9</v>
       </c>
       <c r="N15" t="n">
-        <v>7.7</v>
+        <v>1.15</v>
       </c>
       <c r="O15" t="n">
-        <v>1.85</v>
+        <v>7</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.5</v>
+        <v>1.77</v>
       </c>
       <c r="R15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V15" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1.44</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AB15" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE15" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.29</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.63</v>
+        <v>1.08</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46006.6875</v>
+        <v>46006.64583333334</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="M16" t="n">
-        <v>3.59</v>
+        <v>3.95</v>
       </c>
       <c r="N16" t="n">
-        <v>5.3</v>
+        <v>7.3</v>
       </c>
       <c r="O16" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="P16" t="n">
         <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.67</v>
+        <v>7.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>2.78</v>
+        <v>2.53</v>
       </c>
       <c r="T16" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="U16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.35</v>
       </c>
-      <c r="V16" t="n">
-        <v>7</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.29</v>
-      </c>
       <c r="Z16" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46006.6875</v>
+        <v>46006.65625</v>
       </c>
     </row>
     <row r="17">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.47</v>
+        <v>1.44</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="O17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z17" t="n">
         <v>4.2</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V17" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y17" t="n">
+      <c r="AA17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2522,12 +2522,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,76 +2563,76 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.11</v>
+        <v>1.41</v>
       </c>
       <c r="M18" t="n">
-        <v>3.13</v>
+        <v>3.83</v>
       </c>
       <c r="N18" t="n">
-        <v>3.62</v>
+        <v>7.7</v>
       </c>
       <c r="O18" t="n">
-        <v>2.59</v>
+        <v>1.85</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.9</v>
+        <v>7.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="T18" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AD18" t="n">
         <v>1.22</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.98</v>
+        <v>2.29</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.67</v>
+        <v>2.63</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46006.69791666666</v>
+        <v>46006.6875</v>
       </c>
     </row>
     <row r="19">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,76 +2682,76 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="M19" t="n">
-        <v>3.04</v>
+        <v>2.94</v>
       </c>
       <c r="N19" t="n">
-        <v>1.95</v>
+        <v>2.22</v>
       </c>
       <c r="O19" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="P19" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="R19" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S19" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="U19" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="V19" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z19" t="n">
         <v>2.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AC19" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>46006.69791666666</v>
+        <v>46006.6875</v>
       </c>
     </row>
     <row r="20">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,76 +2801,76 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>3.59</v>
       </c>
       <c r="N20" t="n">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="O20" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="P20" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>6.67</v>
       </c>
       <c r="R20" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>3.5</v>
+        <v>2.78</v>
       </c>
       <c r="T20" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.14</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH20" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>46006.70833333334</v>
+        <v>46006.6875</v>
       </c>
     </row>
     <row r="21">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,76 +2920,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.55</v>
+        <v>3.47</v>
       </c>
       <c r="M21" t="n">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.99</v>
+        <v>2.71</v>
       </c>
       <c r="R21" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="S21" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="T21" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="U21" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="V21" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46006.70833333334</v>
+        <v>46006.6875</v>
       </c>
     </row>
     <row r="22">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,76 +3039,76 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.16</v>
+        <v>2.11</v>
       </c>
       <c r="M22" t="n">
-        <v>7.1</v>
+        <v>3.13</v>
       </c>
       <c r="N22" t="n">
-        <v>15</v>
+        <v>3.62</v>
       </c>
       <c r="O22" t="n">
-        <v>1.53</v>
+        <v>2.59</v>
       </c>
       <c r="P22" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>10</v>
+        <v>3.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.51</v>
       </c>
       <c r="S22" t="n">
-        <v>3.34</v>
+        <v>2.53</v>
       </c>
       <c r="T22" t="n">
-        <v>2.36</v>
+        <v>2.95</v>
       </c>
       <c r="U22" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
         <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.37</v>
+        <v>4.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.42</v>
+        <v>1.87</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>4.6</v>
+        <v>1.67</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>46006.73958333334</v>
+        <v>46006.69791666666</v>
       </c>
     </row>
     <row r="23">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,76 +3158,76 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>46006.79166666666</v>
+        <v>46006.69791666666</v>
       </c>
     </row>
     <row r="24">
@@ -3236,116 +3236,830 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Scotland Premiership</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Rangers</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI24" s="3" t="n">
+        <v>46006.69791666666</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Spain La Liga</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V25" t="n">
+        <v>7</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AI25" s="3" t="n">
+        <v>46006.70833333334</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>England Premier League</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>AFC Bournemouth</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V26" t="n">
+        <v>5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI26" s="3" t="n">
+        <v>46006.70833333334</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Sheffield Wednesday</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Derby County</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="O27" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI27" s="3" t="n">
+        <v>46006.70833333334</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Portugal Liga NOS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Estrela Amadora</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="M28" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="N28" t="n">
+        <v>15</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>10</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="AI28" s="3" t="n">
+        <v>46006.73958333334</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Spanish Town Police FC</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3" t="n">
+        <v>46006.79166666666</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Arnett Gardens</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Montego Bay United</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" s="3" t="n">
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3" t="n">
         <v>46006.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="M2" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>3.6</v>
+        <v>4.45</v>
       </c>
       <c r="O2" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="P2" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46006.29166666666</v>
@@ -787,13 +787,13 @@
         <v>4.4</v>
       </c>
       <c r="O3" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="P3" t="n">
         <v>1.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.25</v>
+        <v>5.53</v>
       </c>
       <c r="R3" t="n">
         <v>1.66</v>
@@ -838,7 +838,7 @@
         <v>2.57</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG3" t="n">
         <v>1.33</v>
@@ -906,7 +906,7 @@
         <v>2.15</v>
       </c>
       <c r="O4" t="n">
-        <v>4.2</v>
+        <v>4.43</v>
       </c>
       <c r="P4" t="n">
         <v>1.85</v>
@@ -921,7 +921,7 @@
         <v>2.22</v>
       </c>
       <c r="T4" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="U4" t="n">
         <v>1.19</v>
@@ -948,16 +948,16 @@
         <v>1.52</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="AD4" t="n">
         <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG4" t="n">
         <v>1.31</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>6.95</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.4</v>
+        <v>2.94</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46006.40625</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="M6" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="S6" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="T6" t="n">
-        <v>4.25</v>
+        <v>3.82</v>
       </c>
       <c r="U6" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
         <v>1.09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.94</v>
+        <v>2.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.75</v>
+        <v>5.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.79</v>
+        <v>2.35</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.99</v>
+        <v>1.62</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46006.40625</v>
@@ -1263,19 +1263,19 @@
         <v>2.1</v>
       </c>
       <c r="O7" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="P7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q7" t="n">
         <v>2.96</v>
       </c>
       <c r="R7" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="S7" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T7" t="n">
         <v>4.2</v>
@@ -1314,7 +1314,7 @@
         <v>2.45</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AG7" t="n">
         <v>1.34</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>4.35</v>
+        <v>4.05</v>
       </c>
       <c r="O8" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.65</v>
+        <v>4.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46006.5</v>
@@ -1492,31 +1492,31 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="M9" t="n">
         <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.47</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
         <v>2.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.76</v>
+        <v>4.82</v>
       </c>
       <c r="R9" t="n">
         <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>3.01</v>
+        <v>2.73</v>
       </c>
       <c r="T9" t="n">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="U9" t="n">
         <v>1.4</v>
@@ -1534,13 +1534,13 @@
         <v>1.24</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AC9" t="n">
         <v>3.2</v>
@@ -1549,10 +1549,10 @@
         <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AG9" t="n">
         <v>1.25</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.45</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>4.85</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>6.3</v>
       </c>
       <c r="O10" t="n">
-        <v>2.8</v>
+        <v>1.75</v>
       </c>
       <c r="P10" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC10" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.28</v>
-      </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.26</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>5.7</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>9.75</v>
+        <v>2.95</v>
       </c>
       <c r="O11" t="n">
-        <v>1.65</v>
+        <v>2.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.75</v>
+        <v>2.21</v>
       </c>
       <c r="Q11" t="n">
-        <v>8</v>
+        <v>3.55</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="S11" t="n">
-        <v>3.8</v>
+        <v>2.69</v>
       </c>
       <c r="T11" t="n">
-        <v>2.25</v>
+        <v>2.86</v>
       </c>
       <c r="U11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.6</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>3.6</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="M12" t="n">
-        <v>4.65</v>
+        <v>5.7</v>
       </c>
       <c r="N12" t="n">
-        <v>5.9</v>
+        <v>9.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="P12" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.66</v>
+        <v>8</v>
       </c>
       <c r="R12" t="n">
         <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="T12" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="V12" t="n">
-        <v>4.55</v>
+        <v>4.75</v>
       </c>
       <c r="W12" t="n">
         <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AD12" t="n">
         <v>1.62</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AH12" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="M13" t="n">
+        <v>3</v>
+      </c>
+      <c r="N13" t="n">
         <v>3.2</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.05</v>
       </c>
       <c r="O13" t="n">
         <v>3.02</v>
@@ -1989,7 +1989,7 @@
         <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="T13" t="n">
         <v>3.04</v>
@@ -2007,25 +2007,25 @@
         <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z13" t="n">
         <v>2.85</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AB13" t="n">
         <v>1.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="AD13" t="n">
         <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AF13" t="n">
         <v>1.88</v>
@@ -2034,7 +2034,7 @@
         <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46006.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="M14" t="n">
-        <v>3.56</v>
+        <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>1.61</v>
+        <v>1.34</v>
       </c>
       <c r="O14" t="n">
-        <v>5.35</v>
+        <v>7</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.28</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>2.66</v>
+        <v>3.42</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="V14" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.05</v>
+        <v>4.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.94</v>
+        <v>1.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.76</v>
+        <v>2.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.28</v>
+        <v>2.31</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="M15" t="n">
-        <v>5.9</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>1.15</v>
+        <v>1.68</v>
       </c>
       <c r="O15" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="P15" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
-        <v>3.55</v>
+        <v>2.66</v>
       </c>
       <c r="T15" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>4.45</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.14</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.08</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2325,25 +2325,25 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="O16" t="n">
         <v>2.07</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="Q16" t="n">
         <v>7.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
         <v>2.53</v>
@@ -2355,7 +2355,7 @@
         <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="W16" t="n">
         <v>1.02</v>
@@ -2370,10 +2370,10 @@
         <v>2.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
         <v>3.85</v>
@@ -2385,7 +2385,7 @@
         <v>2.2</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG16" t="n">
         <v>1.25</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="N17" t="n">
         <v>6.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.36</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R17" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>2.47</v>
       </c>
       <c r="T17" t="n">
-        <v>2.55</v>
+        <v>2.97</v>
       </c>
       <c r="U17" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="V17" t="n">
-        <v>5.5</v>
+        <v>7.7</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>2.92</v>
       </c>
       <c r="AA17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.68</v>
       </c>
-      <c r="AB17" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AC17" t="n">
-        <v>2.75</v>
+        <v>3.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.92</v>
+        <v>2.29</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
-        <v>3.83</v>
+        <v>4.4</v>
       </c>
       <c r="N18" t="n">
-        <v>7.7</v>
+        <v>5.75</v>
       </c>
       <c r="O18" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="S18" t="n">
-        <v>2.47</v>
+        <v>3.36</v>
       </c>
       <c r="T18" t="n">
-        <v>2.97</v>
+        <v>2.55</v>
       </c>
       <c r="U18" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="V18" t="n">
-        <v>7.7</v>
+        <v>5.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.87</v>
+        <v>4.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE18" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH18" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.25</v>
+        <v>1.58</v>
       </c>
       <c r="M19" t="n">
-        <v>2.94</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>2.22</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>4.05</v>
+        <v>2.09</v>
       </c>
       <c r="P19" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z19" t="n">
         <v>2.92</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AA19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH19" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.58</v>
+        <v>3.45</v>
       </c>
       <c r="M20" t="n">
-        <v>3.59</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>2.11</v>
+        <v>3.8</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.67</v>
+        <v>2.71</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="S20" t="n">
-        <v>2.78</v>
+        <v>2.49</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="U20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X20" t="n">
         <v>1.03</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y20" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="AB20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AG20" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,40 +2920,40 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.47</v>
+        <v>3.2</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="O21" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="P21" t="n">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S21" t="n">
-        <v>2.49</v>
+        <v>2.34</v>
       </c>
       <c r="T21" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U21" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="V21" t="n">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W21" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
         <v>1.08</v>
@@ -2962,31 +2962,31 @@
         <v>1.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE21" t="n">
         <v>1.93</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46006.6875</v>
@@ -3039,55 +3039,55 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="O22" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="P22" t="n">
         <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="S22" t="n">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="T22" t="n">
         <v>2.95</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V22" t="n">
         <v>7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC22" t="n">
         <v>4.1</v>
@@ -3096,16 +3096,16 @@
         <v>1.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
         <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>1.89</v>
       </c>
       <c r="M23" t="n">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>4.2</v>
+        <v>2.41</v>
       </c>
       <c r="P23" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.66</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>2.89</v>
       </c>
       <c r="T23" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="U23" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="V23" t="n">
-        <v>7.6</v>
+        <v>6.25</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>2.03</v>
       </c>
       <c r="AC23" t="n">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.24</v>
+        <v>1.9</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.41</v>
+        <v>3.04</v>
       </c>
       <c r="N24" t="n">
-        <v>3.92</v>
+        <v>1.95</v>
       </c>
       <c r="O24" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="R24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.36</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y24" t="n">
+      <c r="Z24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.25</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.9</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="O25" t="n">
         <v>3.1</v>
@@ -3444,7 +3444,7 @@
         <v>1.98</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC25" t="n">
         <v>3.22</v>
@@ -3459,7 +3459,7 @@
         <v>2.13</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH25" t="n">
         <v>1.49</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.85</v>
+        <v>3.55</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>3.27</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>2.07</v>
       </c>
       <c r="O26" t="n">
-        <v>2.3</v>
+        <v>3.65</v>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>2.96</v>
       </c>
       <c r="R26" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>3.5</v>
+        <v>2.58</v>
       </c>
       <c r="T26" t="n">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
       <c r="U26" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="W26" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.37</v>
+        <v>1.91</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.05</v>
+        <v>1.36</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.55</v>
+        <v>1.85</v>
       </c>
       <c r="M27" t="n">
-        <v>3.27</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>2.07</v>
+        <v>3.8</v>
       </c>
       <c r="O27" t="n">
-        <v>3.65</v>
+        <v>2.36</v>
       </c>
       <c r="P27" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.99</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="S27" t="n">
-        <v>2.53</v>
+        <v>3.45</v>
       </c>
       <c r="T27" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="U27" t="n">
-        <v>1.32</v>
+        <v>1.59</v>
       </c>
       <c r="V27" t="n">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="X27" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.03</v>
+        <v>1.57</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.95</v>
+        <v>2.45</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.21</v>
+        <v>1.6</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.88</v>
+        <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.87</v>
+        <v>2.4</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="M28" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="N28" t="n">
         <v>15</v>
@@ -3765,7 +3765,7 @@
         <v>1.57</v>
       </c>
       <c r="P28" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="Q28" t="n">
         <v>10</v>
@@ -3780,7 +3780,7 @@
         <v>2.35</v>
       </c>
       <c r="U28" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
         <v>5.5</v>
@@ -3792,34 +3792,34 @@
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z28" t="n">
         <v>3.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AB28" t="n">
         <v>2.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="AF28" t="n">
         <v>1.6</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AH28" t="n">
-        <v>5.18</v>
+        <v>4.33</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46006.73958333334</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N3" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
         <v>2.84</v>
@@ -817,13 +817,13 @@
         <v>1.09</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="Z3" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AB3" t="n">
         <v>1.33</v>
@@ -838,7 +838,7 @@
         <v>2.57</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG3" t="n">
         <v>1.33</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N4" t="n">
-        <v>2.15</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>4.43</v>
+        <v>2.75</v>
       </c>
       <c r="P4" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.95</v>
+        <v>5.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="S4" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="T4" t="n">
-        <v>3.74</v>
+        <v>3.82</v>
       </c>
       <c r="U4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AA4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE4" t="n">
         <v>2.35</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AF4" t="n">
         <v>1.52</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.56</v>
       </c>
       <c r="AG4" t="n">
         <v>1.31</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46006.40625</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>3.35</v>
       </c>
       <c r="M5" t="n">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="N5" t="n">
-        <v>3.6</v>
+        <v>2.22</v>
       </c>
       <c r="O5" t="n">
-        <v>2.42</v>
+        <v>4.44</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.95</v>
+        <v>2.94</v>
       </c>
       <c r="R5" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="T5" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="V5" t="n">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.94</v>
+        <v>2.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.15</v>
+        <v>2.27</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.01</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46006.40625</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>5.75</v>
       </c>
       <c r="O6" t="n">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="P6" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.2</v>
+        <v>7.34</v>
       </c>
       <c r="R6" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="S6" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="T6" t="n">
-        <v>3.82</v>
+        <v>4.25</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="V6" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
         <v>1.09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.6</v>
+        <v>6.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.35</v>
+        <v>2.79</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46006.40625</v>
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="M7" t="n">
         <v>2.8</v>
@@ -1293,16 +1293,16 @@
         <v>1.09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AC7" t="n">
         <v>6.6</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>4.85</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>6.3</v>
+        <v>2.95</v>
       </c>
       <c r="O10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.75</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6.87</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>4.85</v>
       </c>
       <c r="N11" t="n">
-        <v>2.95</v>
+        <v>6.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.8</v>
+        <v>1.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.21</v>
+        <v>2.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.55</v>
+        <v>6.87</v>
       </c>
       <c r="R11" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.86</v>
+        <v>1.95</v>
       </c>
       <c r="U11" t="n">
-        <v>1.37</v>
+        <v>1.63</v>
       </c>
       <c r="V11" t="n">
-        <v>7</v>
+        <v>4.55</v>
       </c>
       <c r="W11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.1</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.27</v>
-      </c>
       <c r="Z11" t="n">
-        <v>3.14</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.96</v>
+        <v>1.47</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="M12" t="n">
         <v>5.7</v>
@@ -1876,13 +1876,13 @@
         <v>2.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="V12" t="n">
         <v>4.75</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
         <v>1.02</v>
@@ -1891,7 +1891,7 @@
         <v>1.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.8</v>
+        <v>5.18</v>
       </c>
       <c r="AA12" t="n">
         <v>1.5</v>
@@ -1903,10 +1903,10 @@
         <v>2.32</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF12" t="n">
         <v>1.85</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V17" t="n">
         <v>7</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V17" t="n">
-        <v>7.7</v>
       </c>
       <c r="W17" t="n">
         <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
         <v>2.92</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AG17" t="n">
         <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.44</v>
+        <v>3.2</v>
       </c>
       <c r="M18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V18" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC18" t="n">
         <v>4.4</v>
       </c>
-      <c r="N18" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AD18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.4</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH18" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.58</v>
+        <v>1.4</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.95</v>
+        <v>7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>2.67</v>
+        <v>2.47</v>
       </c>
       <c r="T19" t="n">
-        <v>2.72</v>
+        <v>2.97</v>
       </c>
       <c r="U19" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="V19" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="W19" t="n">
         <v>1.03</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
         <v>2.92</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.91</v>
+        <v>2.29</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AG19" t="n">
         <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.45</v>
+        <v>1.44</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>5.75</v>
       </c>
       <c r="O20" t="n">
-        <v>3.8</v>
+        <v>1.88</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.71</v>
+        <v>6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="S20" t="n">
-        <v>2.49</v>
+        <v>3.36</v>
       </c>
       <c r="T20" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="V20" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.34</v>
+        <v>1.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AE20" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P21" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S21" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V21" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA21" t="n">
         <v>2.34</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V21" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.33</v>
       </c>
       <c r="AB21" t="n">
         <v>1.57</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AF21" t="n">
         <v>1.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46006.6875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="N22" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="O22" t="n">
+        <v>4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q22" t="n">
         <v>2.63</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S22" t="n">
-        <v>2.67</v>
+        <v>2.47</v>
       </c>
       <c r="T22" t="n">
         <v>2.95</v>
       </c>
       <c r="U22" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V22" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="W22" t="n">
         <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y22" t="n">
         <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.1</v>
+        <v>3.76</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG22" t="n">
         <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N23" t="n">
         <v>3.4</v>
       </c>
-      <c r="N23" t="n">
-        <v>3.5</v>
-      </c>
       <c r="O23" t="n">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
         <v>4</v>
       </c>
       <c r="R23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.33</v>
       </c>
-      <c r="S23" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.6</v>
+        <v>1.89</v>
       </c>
       <c r="M24" t="n">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>1.95</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q24" t="n">
         <v>4</v>
       </c>
-      <c r="P24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.63</v>
-      </c>
       <c r="R24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U24" t="n">
         <v>1.45</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AC24" t="n">
         <v>2.95</v>
       </c>
-      <c r="U24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.76</v>
-      </c>
       <c r="AD24" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.25</v>
+        <v>1.9</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N25" t="n">
-        <v>2.67</v>
+        <v>3.8</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="P25" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="S25" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="T25" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="U25" t="n">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="V25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X25" t="n">
         <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.82</v>
+        <v>2.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.22</v>
+        <v>2.45</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.28</v>
+        <v>1.6</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.49</v>
+        <v>1.95</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="O26" t="n">
         <v>3.65</v>
@@ -3530,46 +3530,46 @@
         <v>2.12</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="T26" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="U26" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V26" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="W26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X26" t="n">
         <v>1.02</v>
       </c>
-      <c r="X26" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y26" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE26" t="n">
         <v>1.83</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="M27" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>3.8</v>
+        <v>2.67</v>
       </c>
       <c r="O27" t="n">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="P27" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="R27" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="T27" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="U27" t="n">
-        <v>1.59</v>
+        <v>1.39</v>
       </c>
       <c r="V27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.5</v>
+        <v>1.82</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.45</v>
+        <v>3.22</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.95</v>
+        <v>1.49</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="M30" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="N30" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46006.89583333334</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.35</v>
+        <v>1.67</v>
       </c>
       <c r="M5" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.22</v>
+        <v>5.75</v>
       </c>
       <c r="O5" t="n">
-        <v>4.44</v>
+        <v>2.42</v>
       </c>
       <c r="P5" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.94</v>
+        <v>7.34</v>
       </c>
       <c r="R5" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="S5" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="T5" t="n">
-        <v>3.75</v>
+        <v>4.25</v>
       </c>
       <c r="U5" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="V5" t="n">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.27</v>
+        <v>2.79</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46006.40625</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.67</v>
+        <v>3.35</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="N6" t="n">
-        <v>5.75</v>
+        <v>2.22</v>
       </c>
       <c r="O6" t="n">
-        <v>2.42</v>
+        <v>4.44</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.34</v>
+        <v>2.94</v>
       </c>
       <c r="R6" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="T6" t="n">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="V6" t="n">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.07</v>
+        <v>2.21</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.79</v>
+        <v>2.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AH6" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46006.40625</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>4.85</v>
       </c>
       <c r="N10" t="n">
-        <v>2.95</v>
+        <v>6.3</v>
       </c>
       <c r="O10" t="n">
-        <v>2.8</v>
+        <v>1.75</v>
       </c>
       <c r="P10" t="n">
-        <v>2.21</v>
+        <v>2.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.55</v>
+        <v>6.87</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.86</v>
+        <v>1.95</v>
       </c>
       <c r="U10" t="n">
-        <v>1.37</v>
+        <v>1.63</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>4.55</v>
       </c>
       <c r="W10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.1</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.27</v>
-      </c>
       <c r="Z10" t="n">
-        <v>3.14</v>
+        <v>5.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.96</v>
+        <v>1.47</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>4.85</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>6.3</v>
+        <v>2.95</v>
       </c>
       <c r="O11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.75</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>6.87</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="M14" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>1.34</v>
+        <v>1.68</v>
       </c>
       <c r="O14" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="P14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S14" t="n">
         <v>2.66</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.8</v>
       </c>
-      <c r="R14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
+      <c r="AC14" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.14</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.1</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="N15" t="n">
-        <v>1.68</v>
+        <v>1.34</v>
       </c>
       <c r="O15" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>2.66</v>
+        <v>3.42</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.05</v>
+        <v>4.9</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF15" t="n">
         <v>2</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG15" t="n">
-        <v>2.1</v>
+        <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.58</v>
+        <v>3.2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>2.25</v>
       </c>
       <c r="O17" t="n">
-        <v>2.09</v>
+        <v>3.7</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.95</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.67</v>
+        <v>2.34</v>
       </c>
       <c r="T17" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="AA17" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.2</v>
+        <v>1.58</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>2.25</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.7</v>
+        <v>2.09</v>
       </c>
       <c r="P18" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>4.95</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>2.34</v>
+        <v>2.67</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="U18" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>9.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="W18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X18" t="n">
         <v>1</v>
       </c>
-      <c r="X18" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.63</v>
+        <v>2.92</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.3</v>
+        <v>2.3</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="O22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q22" t="n">
         <v>4</v>
       </c>
-      <c r="P22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.63</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S22" t="n">
-        <v>2.47</v>
+        <v>2.67</v>
       </c>
       <c r="T22" t="n">
         <v>2.95</v>
       </c>
       <c r="U22" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V22" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="W22" t="n">
         <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
         <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.76</v>
+        <v>4.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
         <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>2.63</v>
+        <v>2.41</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
         <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>2.67</v>
+        <v>2.89</v>
       </c>
       <c r="T23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AC23" t="n">
         <v>2.95</v>
       </c>
-      <c r="U23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V23" t="n">
-        <v>7</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AD23" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.89</v>
+        <v>3.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="O24" t="n">
-        <v>2.41</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="R24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.33</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y24" t="n">
+      <c r="AH24" t="n">
         <v>1.25</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.9</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="O26" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="P26" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="R26" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="T26" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="V26" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.89</v>
+        <v>3.45</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.23</v>
+        <v>1.98</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.8</v>
+        <v>3.22</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="O27" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="P27" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="T27" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="U27" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.45</v>
+        <v>2.89</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.98</v>
+        <v>2.23</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.22</v>
+        <v>3.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.3</v>
+        <v>3.44</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>3.77</v>
       </c>
       <c r="N30" t="n">
-        <v>2.7</v>
+        <v>1.81</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -4036,10 +4036,10 @@
         <v>3.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC30" t="n">
         <v>2.83</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="M3" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="O3" t="n">
         <v>2.84</v>
@@ -793,7 +793,7 @@
         <v>1.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.53</v>
+        <v>5.25</v>
       </c>
       <c r="R3" t="n">
         <v>1.66</v>
@@ -817,13 +817,13 @@
         <v>1.09</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="AB3" t="n">
         <v>1.33</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="M4" t="n">
         <v>2.95</v>
@@ -906,19 +906,19 @@
         <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P4" t="n">
         <v>1.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.2</v>
+        <v>4.75</v>
       </c>
       <c r="R4" t="n">
         <v>1.52</v>
       </c>
       <c r="S4" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="T4" t="n">
         <v>3.82</v>
@@ -927,7 +927,7 @@
         <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>8.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W4" t="n">
         <v>1.04</v>
@@ -936,28 +936,28 @@
         <v>1.11</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AC4" t="n">
         <v>5.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
         <v>2.35</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AG4" t="n">
         <v>1.31</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.67</v>
+        <v>3.6</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="N5" t="n">
-        <v>5.75</v>
+        <v>2.15</v>
       </c>
       <c r="O5" t="n">
-        <v>2.42</v>
+        <v>4.44</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.34</v>
+        <v>2.94</v>
       </c>
       <c r="R5" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="T5" t="n">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="V5" t="n">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.05</v>
+        <v>2.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.79</v>
+        <v>2.27</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.34</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="AH5" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46006.40625</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.35</v>
+        <v>2.15</v>
       </c>
       <c r="M6" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>2.22</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
-        <v>4.44</v>
+        <v>2.45</v>
       </c>
       <c r="P6" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA6" t="n">
         <v>2.94</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V6" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AB6" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.5</v>
+        <v>6.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.27</v>
+        <v>3.15</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>1.99</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46006.40625</v>
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="M7" t="n">
         <v>2.8</v>
@@ -1263,10 +1263,10 @@
         <v>2.1</v>
       </c>
       <c r="O7" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="P7" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
         <v>2.96</v>
@@ -1293,16 +1293,16 @@
         <v>1.09</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.04</v>
+        <v>3.09</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AC7" t="n">
         <v>6.6</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>4.85</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>6.3</v>
+        <v>2.95</v>
       </c>
       <c r="O10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.75</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>6.87</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.69</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>1.22</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>5.7</v>
       </c>
       <c r="N11" t="n">
-        <v>2.95</v>
+        <v>9.75</v>
       </c>
       <c r="O11" t="n">
-        <v>2.8</v>
+        <v>1.65</v>
       </c>
       <c r="P11" t="n">
-        <v>2.21</v>
+        <v>2.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.55</v>
+        <v>8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>2.69</v>
+        <v>3.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.86</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="V11" t="n">
-        <v>7</v>
+        <v>4.75</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.14</v>
+        <v>5.18</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.96</v>
+        <v>1.5</v>
       </c>
       <c r="AB11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1.85</v>
       </c>
-      <c r="AC11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>5.7</v>
+        <v>4.85</v>
       </c>
       <c r="N12" t="n">
-        <v>9.75</v>
+        <v>6.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="P12" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>6.87</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="U12" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V12" t="n">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
         <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.18</v>
+        <v>5.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AG12" t="n">
         <v>1.14</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>3.24</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O13" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="P13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="R13" t="n">
         <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="T13" t="n">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="U13" t="n">
         <v>1.33</v>
@@ -2025,16 +2025,16 @@
         <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AF13" t="n">
         <v>1.88</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46006.60416666666</v>
@@ -2337,7 +2337,7 @@
         <v>2.07</v>
       </c>
       <c r="P16" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
         <v>7.1</v>
@@ -2364,28 +2364,28 @@
         <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
         <v>2.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG16" t="n">
         <v>1.25</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.2</v>
+        <v>1.35</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="N17" t="n">
-        <v>2.25</v>
+        <v>5.9</v>
       </c>
       <c r="O17" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="P17" t="n">
-        <v>1.85</v>
+        <v>2.36</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="S17" t="n">
-        <v>2.34</v>
+        <v>3.36</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="U17" t="n">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="V17" t="n">
-        <v>9.300000000000001</v>
+        <v>5.55</v>
       </c>
       <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
         <v>1</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.63</v>
+        <v>3.84</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.33</v>
+        <v>1.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.4</v>
+        <v>2.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>2.72</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.58</v>
+        <v>3.25</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>2.94</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>2.22</v>
       </c>
       <c r="O18" t="n">
-        <v>2.09</v>
+        <v>3.7</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.95</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="S18" t="n">
-        <v>2.67</v>
+        <v>2.34</v>
       </c>
       <c r="T18" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.92</v>
+        <v>2.63</v>
       </c>
       <c r="AA18" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M19" t="n">
-        <v>4.2</v>
+        <v>3.83</v>
       </c>
       <c r="N19" t="n">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="O19" t="n">
         <v>2</v>
@@ -2700,10 +2700,10 @@
         <v>7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>2.47</v>
+        <v>2.64</v>
       </c>
       <c r="T19" t="n">
         <v>2.97</v>
@@ -2721,19 +2721,19 @@
         <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD19" t="n">
         <v>1.22</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="M20" t="n">
-        <v>4.4</v>
+        <v>3.59</v>
       </c>
       <c r="N20" t="n">
-        <v>5.75</v>
+        <v>5.3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.88</v>
+        <v>2.09</v>
       </c>
       <c r="P20" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>4.95</v>
       </c>
       <c r="R20" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>3.36</v>
+        <v>2.67</v>
       </c>
       <c r="T20" t="n">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="U20" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="V20" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
         <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.75</v>
+        <v>3.45</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
         <v>2</v>
@@ -2944,7 +2944,7 @@
         <v>2.49</v>
       </c>
       <c r="T21" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="U21" t="n">
         <v>1.36</v>
@@ -2965,22 +2965,22 @@
         <v>2.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AC21" t="n">
         <v>4.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE21" t="n">
         <v>2</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG21" t="n">
         <v>1.33</v>
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="O22" t="n">
         <v>2.63</v>
@@ -3057,10 +3057,10 @@
         <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S22" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="T22" t="n">
         <v>2.95</v>
@@ -3087,7 +3087,7 @@
         <v>2.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC22" t="n">
         <v>4.1</v>
@@ -3105,7 +3105,7 @@
         <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3167,7 +3167,7 @@
         <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="P23" t="n">
         <v>2.2</v>
@@ -3176,7 +3176,7 @@
         <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
         <v>2.89</v>
@@ -3185,13 +3185,13 @@
         <v>2.62</v>
       </c>
       <c r="U23" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="V23" t="n">
         <v>6.25</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
         <v>1</v>
@@ -3200,31 +3200,31 @@
         <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AA23" t="n">
         <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="AD23" t="n">
         <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>3.2</v>
       </c>
       <c r="M25" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="N25" t="n">
-        <v>3.8</v>
+        <v>2.25</v>
       </c>
       <c r="O25" t="n">
-        <v>2.36</v>
+        <v>3.65</v>
       </c>
       <c r="P25" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>2.98</v>
       </c>
       <c r="R25" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>3.45</v>
+        <v>2.53</v>
       </c>
       <c r="T25" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="U25" t="n">
-        <v>1.59</v>
+        <v>1.32</v>
       </c>
       <c r="V25" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
         <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.8</v>
+        <v>2.89</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.57</v>
+        <v>2.23</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.45</v>
+        <v>3.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
         <v>2.67</v>
@@ -3530,7 +3530,7 @@
         <v>2.26</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
         <v>1.4</v>
@@ -3542,7 +3542,7 @@
         <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="V26" t="n">
         <v>7</v>
@@ -3572,16 +3572,16 @@
         <v>1.28</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AF26" t="n">
         <v>2.13</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N27" t="n">
-        <v>2.25</v>
+        <v>4</v>
       </c>
       <c r="O27" t="n">
-        <v>3.65</v>
+        <v>2.34</v>
       </c>
       <c r="P27" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.98</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="S27" t="n">
-        <v>2.53</v>
+        <v>3.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="U27" t="n">
-        <v>1.32</v>
+        <v>1.62</v>
       </c>
       <c r="V27" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.89</v>
+        <v>4.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.23</v>
+        <v>1.54</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.67</v>
+        <v>2.45</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3765,7 +3765,7 @@
         <v>1.57</v>
       </c>
       <c r="P28" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="Q28" t="n">
         <v>10</v>
@@ -3780,7 +3780,7 @@
         <v>2.35</v>
       </c>
       <c r="U28" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="V28" t="n">
         <v>5.5</v>
@@ -3798,7 +3798,7 @@
         <v>3.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="AB28" t="n">
         <v>2.3</v>
@@ -3816,7 +3816,7 @@
         <v>1.6</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AH28" t="n">
         <v>4.33</v>
@@ -3872,22 +3872,22 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3991,34 +3991,34 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.44</v>
+        <v>2.6</v>
       </c>
       <c r="M30" t="n">
-        <v>3.77</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>1.81</v>
+        <v>2.48</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="P30" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.26</v>
+        <v>3.12</v>
       </c>
       <c r="R30" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S30" t="n">
-        <v>2.79</v>
+        <v>2.92</v>
       </c>
       <c r="T30" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="V30" t="n">
         <v>6.3</v>
@@ -4027,37 +4027,37 @@
         <v>1.09</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="AG30" t="n">
         <v>1.24</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46006.89583333334</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="N2" t="n">
-        <v>4.45</v>
+        <v>4.98</v>
       </c>
       <c r="O2" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.3</v>
+        <v>5.57</v>
       </c>
       <c r="R2" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>2.92</v>
+        <v>2.81</v>
       </c>
       <c r="T2" t="n">
-        <v>2.52</v>
+        <v>2.82</v>
       </c>
       <c r="U2" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="V2" t="n">
-        <v>5.8</v>
+        <v>6.35</v>
       </c>
       <c r="W2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46006.29166666666</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>4.05</v>
+        <v>4.6</v>
       </c>
       <c r="O8" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="R8" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>2.39</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.33</v>
+        <v>3.65</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46006.5</v>
@@ -1492,34 +1492,34 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="M9" t="n">
         <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>3.47</v>
       </c>
       <c r="O9" t="n">
         <v>2.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.82</v>
+        <v>4.5</v>
       </c>
       <c r="R9" t="n">
         <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="T9" t="n">
         <v>2.69</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
         <v>6.5</v>
@@ -1528,19 +1528,19 @@
         <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y9" t="n">
         <v>1.24</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AC9" t="n">
         <v>3.2</v>
@@ -1549,16 +1549,16 @@
         <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AG9" t="n">
         <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46006.52083333334</v>
@@ -1611,34 +1611,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="O10" t="n">
         <v>2.8</v>
       </c>
       <c r="P10" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="Q10" t="n">
         <v>3.55</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S10" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="T10" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V10" t="n">
         <v>7</v>
@@ -1656,25 +1656,25 @@
         <v>3.14</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
         <v>3.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE10" t="n">
         <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
         <v>1.6</v>
@@ -1968,10 +1968,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
         <v>3.15</v>
@@ -2013,10 +2013,10 @@
         <v>2.85</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC13" t="n">
         <v>3.54</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="N14" t="n">
-        <v>1.68</v>
+        <v>1.15</v>
       </c>
       <c r="O14" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>2.66</v>
+        <v>3.48</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="V14" t="n">
-        <v>6.5</v>
+        <v>4.55</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="AA14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF14" t="n">
         <v>2</v>
       </c>
-      <c r="AB14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG14" t="n">
-        <v>2.1</v>
+        <v>1.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="M15" t="n">
-        <v>5</v>
+        <v>3.56</v>
       </c>
       <c r="N15" t="n">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="O15" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="P15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S15" t="n">
         <v>2.66</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.8</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
+      <c r="AG15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.14</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.1</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="N16" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="O16" t="n">
         <v>2.07</v>
@@ -2370,10 +2370,10 @@
         <v>2.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
         <v>3.82</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="M17" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="N17" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="O17" t="n">
         <v>1.9</v>
@@ -2489,10 +2489,10 @@
         <v>3.84</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC17" t="n">
         <v>2.75</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.25</v>
+        <v>1.41</v>
       </c>
       <c r="M18" t="n">
-        <v>2.94</v>
+        <v>3.83</v>
       </c>
       <c r="N18" t="n">
-        <v>2.22</v>
+        <v>7.7</v>
       </c>
       <c r="O18" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V18" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH18" t="n">
         <v>2.63</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.3</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.41</v>
+        <v>3.47</v>
       </c>
       <c r="M19" t="n">
-        <v>3.83</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>7.7</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P19" t="n">
         <v>2</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q19" t="n">
-        <v>7</v>
+        <v>2.71</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="S19" t="n">
-        <v>2.64</v>
+        <v>2.49</v>
       </c>
       <c r="T19" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="W19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.03</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AG19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>2.63</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.58</v>
+        <v>3.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.59</v>
+        <v>2.94</v>
       </c>
       <c r="N20" t="n">
-        <v>5.3</v>
+        <v>2.22</v>
       </c>
       <c r="O20" t="n">
-        <v>2.09</v>
+        <v>3.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.95</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>2.67</v>
+        <v>2.34</v>
       </c>
       <c r="T20" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AB20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.47</v>
+        <v>1.58</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.59</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="O21" t="n">
-        <v>3.8</v>
+        <v>2.09</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.71</v>
+        <v>4.95</v>
       </c>
       <c r="R21" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="S21" t="n">
-        <v>2.49</v>
+        <v>2.67</v>
       </c>
       <c r="T21" t="n">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="V21" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AE21" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46006.6875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>3.41</v>
       </c>
       <c r="N22" t="n">
-        <v>3.15</v>
+        <v>3.92</v>
       </c>
       <c r="O22" t="n">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
         <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>2.7</v>
+        <v>2.89</v>
       </c>
       <c r="T22" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="U22" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="V22" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.88</v>
+        <v>3.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.1</v>
+        <v>2.97</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="O23" t="n">
-        <v>2.29</v>
+        <v>2.63</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
         <v>4</v>
       </c>
       <c r="R23" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.36</v>
       </c>
-      <c r="S23" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Z23" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.97</v>
+        <v>4.1</v>
       </c>
       <c r="AD23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE23" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3280,10 +3280,10 @@
         <v>3.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="N24" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="O24" t="n">
         <v>4</v>
@@ -3295,16 +3295,16 @@
         <v>2.63</v>
       </c>
       <c r="R24" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S24" t="n">
         <v>2.47</v>
       </c>
       <c r="T24" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U24" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V24" t="n">
         <v>7.6</v>
@@ -3313,7 +3313,7 @@
         <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y24" t="n">
         <v>1.36</v>
@@ -3322,13 +3322,13 @@
         <v>2.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB24" t="n">
         <v>1.62</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="AD24" t="n">
         <v>1.2</v>
@@ -3396,34 +3396,34 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="N25" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="O25" t="n">
         <v>3.65</v>
       </c>
       <c r="P25" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="U25" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
         <v>6.5</v>
@@ -3435,28 +3435,28 @@
         <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.23</v>
+        <v>2.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AG25" t="n">
         <v>1.36</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="M27" t="n">
+        <v>4</v>
+      </c>
+      <c r="N27" t="n">
         <v>3.85</v>
-      </c>
-      <c r="N27" t="n">
-        <v>4</v>
       </c>
       <c r="O27" t="n">
         <v>2.34</v>
@@ -3679,16 +3679,16 @@
         <v>4.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AE27" t="n">
         <v>1.53</v>
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="M28" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="N28" t="n">
         <v>15</v>
@@ -3798,16 +3798,16 @@
         <v>3.95</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AB28" t="n">
         <v>2.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AE28" t="n">
         <v>2.47</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,43 +897,43 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.95</v>
+        <v>3.6</v>
       </c>
       <c r="M4" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>2.15</v>
       </c>
       <c r="O4" t="n">
-        <v>2.7</v>
+        <v>4.44</v>
       </c>
       <c r="P4" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.75</v>
+        <v>2.94</v>
       </c>
       <c r="R4" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T4" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="U4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="V4" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
         <v>1.57</v>
@@ -942,28 +942,28 @@
         <v>2.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD4" t="n">
         <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46006.40625</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,43 +1016,43 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="M5" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>2.15</v>
+        <v>4.1</v>
       </c>
       <c r="O5" t="n">
-        <v>4.44</v>
+        <v>2.7</v>
       </c>
       <c r="P5" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.94</v>
+        <v>4.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="S5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T5" t="n">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="U5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y5" t="n">
         <v>1.57</v>
@@ -1061,28 +1061,28 @@
         <v>2.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AD5" t="n">
         <v>1.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46006.40625</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>5.7</v>
+        <v>4.85</v>
       </c>
       <c r="N11" t="n">
-        <v>9.75</v>
+        <v>6.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="P11" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>8</v>
+        <v>6.87</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="U11" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V11" t="n">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.18</v>
+        <v>5.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AG11" t="n">
         <v>1.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="M12" t="n">
-        <v>4.85</v>
+        <v>5.7</v>
       </c>
       <c r="N12" t="n">
-        <v>6.3</v>
+        <v>9.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="P12" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.87</v>
+        <v>8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V12" t="n">
-        <v>4.55</v>
+        <v>4.75</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X12" t="n">
         <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.5</v>
+        <v>5.18</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
         <v>1.14</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="M14" t="n">
-        <v>5.9</v>
+        <v>3.56</v>
       </c>
       <c r="N14" t="n">
-        <v>1.15</v>
+        <v>1.61</v>
       </c>
       <c r="O14" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="P14" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.8</v>
       </c>
-      <c r="R14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V14" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y14" t="n">
+      <c r="AG14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.14</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.1</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="M15" t="n">
-        <v>3.56</v>
+        <v>5.9</v>
       </c>
       <c r="N15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O15" t="n">
+        <v>6</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.61</v>
       </c>
-      <c r="O15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.36</v>
-      </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>4.55</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.94</v>
+        <v>1.44</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.76</v>
+        <v>2.59</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.28</v>
+        <v>1.86</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.29</v>
+        <v>1.84</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.1</v>
+        <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.44</v>
+        <v>3.47</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
-        <v>1.9</v>
+        <v>3.8</v>
       </c>
       <c r="P17" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>2.71</v>
       </c>
       <c r="R17" t="n">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>3.36</v>
+        <v>2.49</v>
       </c>
       <c r="T17" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>5.55</v>
+        <v>8.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.84</v>
+        <v>2.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.72</v>
+        <v>1.25</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="M18" t="n">
-        <v>3.83</v>
+        <v>3.59</v>
       </c>
       <c r="N18" t="n">
-        <v>7.7</v>
+        <v>5.3</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="P18" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V18" t="n">
         <v>7</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V18" t="n">
-        <v>7.7</v>
       </c>
       <c r="W18" t="n">
         <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.87</v>
+        <v>3.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AG18" t="n">
         <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.47</v>
+        <v>1.41</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.83</v>
       </c>
       <c r="N19" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="O19" t="n">
         <v>2</v>
       </c>
-      <c r="O19" t="n">
-        <v>3.8</v>
-      </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.71</v>
+        <v>7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>2.49</v>
+        <v>2.64</v>
       </c>
       <c r="T19" t="n">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="U19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.36</v>
       </c>
-      <c r="V19" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.37</v>
-      </c>
       <c r="Z19" t="n">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.25</v>
+        <v>2.63</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="M21" t="n">
-        <v>3.59</v>
+        <v>4.5</v>
       </c>
       <c r="N21" t="n">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.95</v>
+        <v>6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="S21" t="n">
-        <v>2.67</v>
+        <v>3.36</v>
       </c>
       <c r="T21" t="n">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="U21" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>5.55</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
         <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.25</v>
+        <v>3.84</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.45</v>
+        <v>2.75</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AE21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF21" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF21" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46006.6875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="M22" t="n">
-        <v>3.41</v>
+        <v>3.13</v>
       </c>
       <c r="N22" t="n">
-        <v>3.92</v>
+        <v>3.62</v>
       </c>
       <c r="O22" t="n">
-        <v>2.29</v>
+        <v>2.63</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
         <v>4</v>
       </c>
       <c r="R22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.36</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V22" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Z22" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.97</v>
+        <v>4.1</v>
       </c>
       <c r="AD22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE22" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.91</v>
+        <v>1.71</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.11</v>
+        <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>3.04</v>
       </c>
       <c r="N23" t="n">
-        <v>3.62</v>
+        <v>1.95</v>
       </c>
       <c r="O23" t="n">
+        <v>4</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q23" t="n">
         <v>2.63</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="S23" t="n">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="T23" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="U23" t="n">
         <v>1.32</v>
       </c>
       <c r="V23" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="W23" t="n">
         <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y23" t="n">
         <v>1.36</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG23" t="n">
         <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.71</v>
+        <v>1.25</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="M24" t="n">
-        <v>3.04</v>
+        <v>3.41</v>
       </c>
       <c r="N24" t="n">
-        <v>1.95</v>
+        <v>3.92</v>
       </c>
       <c r="O24" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q24" t="n">
         <v>4</v>
       </c>
-      <c r="P24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.63</v>
-      </c>
       <c r="R24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U24" t="n">
         <v>1.46</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.32</v>
-      </c>
       <c r="V24" t="n">
-        <v>7.6</v>
+        <v>6.25</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.62</v>
+        <v>1.93</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.74</v>
+        <v>2.97</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AE24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.25</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.62</v>
+        <v>1.85</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>2.67</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
-        <v>3.1</v>
+        <v>2.34</v>
       </c>
       <c r="P26" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="S26" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="V26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.98</v>
+        <v>1.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.82</v>
+        <v>2.35</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.22</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>3.85</v>
+        <v>2.67</v>
       </c>
       <c r="O27" t="n">
-        <v>2.34</v>
+        <v>3.1</v>
       </c>
       <c r="P27" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="T27" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="U27" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="V27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.8</v>
+        <v>3.45</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>1.82</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>3.22</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46006.70833333334</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -662,10 +662,10 @@
         <v>1.62</v>
       </c>
       <c r="M2" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>4.98</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
         <v>2.2</v>
@@ -674,58 +674,58 @@
         <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.57</v>
+        <v>5.74</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T2" t="n">
         <v>2.81</v>
       </c>
-      <c r="T2" t="n">
-        <v>2.82</v>
-      </c>
       <c r="U2" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V2" t="n">
-        <v>6.35</v>
+        <v>6.6</v>
       </c>
       <c r="W2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
         <v>1.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF2" t="n">
         <v>1.82</v>
       </c>
-      <c r="AC2" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AG2" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46006.29166666666</v>
@@ -787,22 +787,22 @@
         <v>4.4</v>
       </c>
       <c r="O3" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="P3" t="n">
         <v>1.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S3" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="T3" t="n">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="U3" t="n">
         <v>1.14</v>
@@ -829,7 +829,7 @@
         <v>1.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.95</v>
+        <v>7.1</v>
       </c>
       <c r="AD3" t="n">
         <v>1.04</v>
@@ -841,7 +841,7 @@
         <v>1.42</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AH3" t="n">
         <v>1.67</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,43 +897,43 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="M4" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N4" t="n">
-        <v>2.15</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>4.44</v>
+        <v>2.75</v>
       </c>
       <c r="P4" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.94</v>
+        <v>5.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="S4" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="T4" t="n">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="U4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y4" t="n">
         <v>1.57</v>
@@ -942,28 +942,28 @@
         <v>2.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AD4" t="n">
         <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.55</v>
+        <v>1.31</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46006.40625</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.75</v>
+        <v>7.24</v>
       </c>
       <c r="R5" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="T5" t="n">
-        <v>3.82</v>
+        <v>4.25</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="V5" t="n">
-        <v>9.300000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="W5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.04</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AE5" t="n">
-        <v>2.35</v>
+        <v>2.79</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.62</v>
+        <v>1.99</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46006.40625</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="M6" t="n">
         <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="O6" t="n">
-        <v>2.45</v>
+        <v>4.49</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.4</v>
+        <v>2.93</v>
       </c>
       <c r="R6" t="n">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="S6" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="T6" t="n">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="V6" t="n">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.94</v>
+        <v>2.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.7</v>
+        <v>5.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.15</v>
+        <v>2.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.34</v>
+        <v>1.53</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.99</v>
+        <v>1.24</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46006.40625</v>
@@ -1263,34 +1263,34 @@
         <v>2.1</v>
       </c>
       <c r="O7" t="n">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="R7" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="T7" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="U7" t="n">
         <v>1.15</v>
       </c>
       <c r="V7" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W7" t="n">
         <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y7" t="n">
         <v>1.62</v>
@@ -1305,19 +1305,19 @@
         <v>1.32</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AF7" t="n">
         <v>1.47</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH7" t="n">
         <v>1.19</v>
@@ -1382,28 +1382,28 @@
         <v>4.6</v>
       </c>
       <c r="O8" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="P8" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.45</v>
+        <v>4.12</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T8" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="W8" t="n">
         <v>1.03</v>
@@ -1415,7 +1415,7 @@
         <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="AA8" t="n">
         <v>2.15</v>
@@ -1424,22 +1424,22 @@
         <v>1.62</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.65</v>
+        <v>3.72</v>
       </c>
       <c r="AD8" t="n">
         <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46006.5</v>
@@ -1507,10 +1507,10 @@
         <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
         <v>2.65</v>
@@ -1531,10 +1531,10 @@
         <v>1.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="AA9" t="n">
         <v>1.77</v>
@@ -1543,22 +1543,22 @@
         <v>1.93</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AD9" t="n">
         <v>1.33</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
         <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46006.52083333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.45</v>
+        <v>1.27</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>9.75</v>
       </c>
       <c r="O10" t="n">
-        <v>2.8</v>
+        <v>1.65</v>
       </c>
       <c r="P10" t="n">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.55</v>
+        <v>7.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="S10" t="n">
-        <v>2.65</v>
+        <v>3.34</v>
       </c>
       <c r="T10" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="U10" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>4.75</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.14</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.2</v>
+        <v>2.33</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.6</v>
+        <v>4.26</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1730,34 +1730,34 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="M11" t="n">
-        <v>4.85</v>
+        <v>5.55</v>
       </c>
       <c r="N11" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="O11" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="P11" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.87</v>
+        <v>6.97</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T11" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="U11" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V11" t="n">
         <v>4.55</v>
@@ -1769,7 +1769,7 @@
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z11" t="n">
         <v>5.5</v>
@@ -1778,25 +1778,25 @@
         <v>1.47</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AC11" t="n">
         <v>2.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.1</v>
+        <v>3.33</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.22</v>
+        <v>2.45</v>
       </c>
       <c r="M12" t="n">
-        <v>5.7</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>9.75</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>1.65</v>
+        <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>2.75</v>
+        <v>2.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="U12" t="n">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>4.75</v>
+        <v>7</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.18</v>
+        <v>3.14</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.32</v>
+        <v>3.26</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.6</v>
+        <v>1.61</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1977,28 +1977,28 @@
         <v>3.15</v>
       </c>
       <c r="O13" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="P13" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="T13" t="n">
-        <v>3.16</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
         <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>8.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="W13" t="n">
         <v>1.02</v>
@@ -2010,7 +2010,7 @@
         <v>1.35</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AA13" t="n">
         <v>2.05</v>
@@ -2025,16 +2025,16 @@
         <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AF13" t="n">
         <v>1.88</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46006.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>12</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O14" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V14" t="n">
         <v>4.6</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="O14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.5</v>
-      </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.94</v>
+        <v>1.44</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.76</v>
+        <v>2.59</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.28</v>
+        <v>1.86</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.29</v>
+        <v>1.84</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.1</v>
+        <v>1.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="M15" t="n">
-        <v>5.9</v>
+        <v>3.56</v>
       </c>
       <c r="N15" t="n">
-        <v>1.15</v>
+        <v>1.61</v>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>4.66</v>
       </c>
       <c r="P15" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.8</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2334,7 +2334,7 @@
         <v>7.3</v>
       </c>
       <c r="O16" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="P16" t="n">
         <v>2.2</v>
@@ -2343,31 +2343,31 @@
         <v>7.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA16" t="n">
         <v>2.1</v>
@@ -2376,22 +2376,22 @@
         <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.82</v>
+        <v>3.54</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46006.65625</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.47</v>
+        <v>1.58</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.59</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="O17" t="n">
-        <v>3.8</v>
+        <v>2.09</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.71</v>
+        <v>4.95</v>
       </c>
       <c r="R17" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>2.49</v>
+        <v>2.8</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1</v>
+        <v>2.72</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="M18" t="n">
-        <v>3.59</v>
+        <v>3.83</v>
       </c>
       <c r="N18" t="n">
-        <v>5.3</v>
+        <v>7.7</v>
       </c>
       <c r="O18" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.95</v>
+        <v>6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="T18" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="W18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X18" t="n">
         <v>1.03</v>
       </c>
-      <c r="X18" t="n">
-        <v>1</v>
-      </c>
       <c r="Y18" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.25</v>
+        <v>2.87</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>2.29</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.41</v>
+        <v>3.47</v>
       </c>
       <c r="M19" t="n">
-        <v>3.83</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
-        <v>7.7</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P19" t="n">
         <v>2</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q19" t="n">
-        <v>7</v>
+        <v>2.73</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S19" t="n">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="T19" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V19" t="n">
-        <v>7.7</v>
+        <v>9</v>
       </c>
       <c r="W19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.03</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.63</v>
+        <v>1.28</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2810,7 +2810,7 @@
         <v>2.22</v>
       </c>
       <c r="O20" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P20" t="n">
         <v>1.85</v>
@@ -2822,7 +2822,7 @@
         <v>1.49</v>
       </c>
       <c r="S20" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="T20" t="n">
         <v>3.1</v>
@@ -2837,13 +2837,13 @@
         <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
         <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AA20" t="n">
         <v>2.3</v>
@@ -2861,13 +2861,13 @@
         <v>1.93</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -2929,61 +2929,61 @@
         <v>6.5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="P21" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="Q21" t="n">
         <v>6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S21" t="n">
-        <v>3.36</v>
+        <v>3.32</v>
       </c>
       <c r="T21" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="U21" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="V21" t="n">
-        <v>5.55</v>
+        <v>5.75</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AH21" t="n">
         <v>2.72</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.11</v>
+        <v>3.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.13</v>
+        <v>3.04</v>
       </c>
       <c r="N22" t="n">
-        <v>3.62</v>
+        <v>1.95</v>
       </c>
       <c r="O22" t="n">
+        <v>4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q22" t="n">
         <v>2.63</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="S22" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="T22" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="U22" t="n">
         <v>1.32</v>
       </c>
       <c r="V22" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="W22" t="n">
         <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.1</v>
+        <v>3.76</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.71</v>
+        <v>1.25</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>2.11</v>
       </c>
       <c r="M23" t="n">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>1.95</v>
+        <v>3.62</v>
       </c>
       <c r="O23" t="n">
-        <v>4</v>
+        <v>2.91</v>
       </c>
       <c r="P23" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.63</v>
+        <v>3.9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="T23" t="n">
-        <v>2.88</v>
+        <v>3.18</v>
       </c>
       <c r="U23" t="n">
         <v>1.32</v>
       </c>
       <c r="V23" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="W23" t="n">
         <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
         <v>1.36</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG23" t="n">
         <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3286,7 +3286,7 @@
         <v>3.92</v>
       </c>
       <c r="O24" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="P24" t="n">
         <v>2.2</v>
@@ -3295,13 +3295,13 @@
         <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S24" t="n">
         <v>2.89</v>
       </c>
       <c r="T24" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="U24" t="n">
         <v>1.46</v>
@@ -3313,13 +3313,13 @@
         <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA24" t="n">
         <v>1.77</v>
@@ -3328,22 +3328,22 @@
         <v>1.93</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE24" t="n">
         <v>1.72</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3411,34 +3411,34 @@
         <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="R25" t="n">
         <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="T25" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U25" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V25" t="n">
         <v>6.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y25" t="n">
         <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AA25" t="n">
         <v>2.03</v>
@@ -3447,10 +3447,10 @@
         <v>1.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AE25" t="n">
         <v>1.85</v>
@@ -3524,7 +3524,7 @@
         <v>3.85</v>
       </c>
       <c r="O26" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="P26" t="n">
         <v>2.45</v>
@@ -3536,10 +3536,10 @@
         <v>1.23</v>
       </c>
       <c r="S26" t="n">
-        <v>3.8</v>
+        <v>3.54</v>
       </c>
       <c r="T26" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="U26" t="n">
         <v>1.62</v>
@@ -3554,10 +3554,10 @@
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AA26" t="n">
         <v>1.6</v>
@@ -3572,7 +3572,7 @@
         <v>1.57</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AF26" t="n">
         <v>2.4</v>
@@ -3637,13 +3637,13 @@
         <v>2.62</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="O27" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P27" t="n">
         <v>2.26</v>
@@ -3655,7 +3655,7 @@
         <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T27" t="n">
         <v>2.8</v>
@@ -3673,19 +3673,19 @@
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z27" t="n">
         <v>3.45</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="AD27" t="n">
         <v>1.28</v>
@@ -3765,37 +3765,37 @@
         <v>1.57</v>
       </c>
       <c r="P28" t="n">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="Q28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R28" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="T28" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="U28" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="V28" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AA28" t="n">
         <v>1.55</v>
@@ -3810,16 +3810,16 @@
         <v>1.55</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.33</v>
+        <v>5.45</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46006.73958333334</v>
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M29" t="n">
-        <v>8.5</v>
+        <v>5.8</v>
       </c>
       <c r="N29" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="O29" t="n">
         <v>17</v>
       </c>
       <c r="P29" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q29" t="n">
         <v>1.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46006.79166666666</v>
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="M30" t="n">
         <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="O30" t="n">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="P30" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.12</v>
+        <v>2.7</v>
       </c>
       <c r="R30" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="U30" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="W30" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46006.89583333334</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,43 +897,43 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.95</v>
+        <v>3.6</v>
       </c>
       <c r="M4" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>2.15</v>
       </c>
       <c r="O4" t="n">
-        <v>2.75</v>
+        <v>4.49</v>
       </c>
       <c r="P4" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.2</v>
+        <v>2.93</v>
       </c>
       <c r="R4" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="S4" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="T4" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="U4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="V4" t="n">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
         <v>1.57</v>
@@ -942,28 +942,28 @@
         <v>2.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD4" t="n">
         <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
         <v>1.31</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46006.40625</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,43 +1135,43 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="M6" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>2.15</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
-        <v>4.49</v>
+        <v>2.75</v>
       </c>
       <c r="P6" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.93</v>
+        <v>5.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="S6" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="U6" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y6" t="n">
         <v>1.57</v>
@@ -1180,28 +1180,28 @@
         <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AD6" t="n">
         <v>1.08</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG6" t="n">
         <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46006.40625</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V10" t="n">
+        <v>7</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.27</v>
       </c>
-      <c r="M10" t="n">
-        <v>6</v>
-      </c>
-      <c r="N10" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V10" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Z10" t="n">
-        <v>5</v>
+        <v>3.14</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.33</v>
+        <v>3.26</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.26</v>
+        <v>1.61</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.45</v>
+        <v>1.27</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>9.75</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>1.65</v>
       </c>
       <c r="P12" t="n">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7</v>
+        <v>3.34</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="V12" t="n">
-        <v>7</v>
+        <v>4.75</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.14</v>
+        <v>5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.26</v>
+        <v>2.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.61</v>
+        <v>4.26</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.58</v>
+        <v>3.25</v>
       </c>
       <c r="M17" t="n">
-        <v>3.59</v>
+        <v>2.94</v>
       </c>
       <c r="N17" t="n">
-        <v>5.3</v>
+        <v>2.22</v>
       </c>
       <c r="O17" t="n">
-        <v>2.09</v>
+        <v>3.75</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.95</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="S17" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="T17" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="U17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V17" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.4</v>
       </c>
-      <c r="V17" t="n">
-        <v>7</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.29</v>
-      </c>
       <c r="Z17" t="n">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.97</v>
+        <v>1.24</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="N20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V20" t="n">
+        <v>7</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z20" t="n">
         <v>3.25</v>
       </c>
-      <c r="M20" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V20" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AA20" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.4</v>
+        <v>3.15</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.24</v>
+        <v>1.97</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.55</v>
+        <v>1.85</v>
       </c>
       <c r="M25" t="n">
-        <v>3.27</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>2.07</v>
+        <v>3.85</v>
       </c>
       <c r="O25" t="n">
-        <v>3.65</v>
+        <v>2.36</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.97</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="S25" t="n">
-        <v>2.81</v>
+        <v>3.54</v>
       </c>
       <c r="T25" t="n">
-        <v>2.75</v>
+        <v>2.17</v>
       </c>
       <c r="U25" t="n">
-        <v>1.31</v>
+        <v>1.62</v>
       </c>
       <c r="V25" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="X25" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="Z25" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.85</v>
+        <v>2.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.84</v>
+        <v>2.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>2.68</v>
       </c>
       <c r="O26" t="n">
-        <v>2.36</v>
+        <v>3.2</v>
       </c>
       <c r="P26" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>3.54</v>
+        <v>2.84</v>
       </c>
       <c r="T26" t="n">
-        <v>2.17</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.9</v>
+        <v>3.45</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.6</v>
+        <v>1.97</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>1.94</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.62</v>
+        <v>3.55</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="N27" t="n">
-        <v>2.68</v>
+        <v>2.07</v>
       </c>
       <c r="O27" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="P27" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="R27" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="T27" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U27" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.27</v>
       </c>
-      <c r="Z27" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AE27" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.13</v>
+        <v>1.84</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46006.70833333334</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI30"/>
+  <dimension ref="A1:AI29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,10 +659,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
         <v>4.4</v>
@@ -674,58 +674,58 @@
         <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.74</v>
+        <v>5.53</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="S2" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46006.29166666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,43 +897,43 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="M4" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N4" t="n">
-        <v>2.15</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>4.49</v>
+        <v>2.75</v>
       </c>
       <c r="P4" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.93</v>
+        <v>5.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="S4" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="T4" t="n">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="U4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y4" t="n">
         <v>1.57</v>
@@ -942,28 +942,28 @@
         <v>2.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AD4" t="n">
         <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG4" t="n">
         <v>1.31</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46006.40625</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,43 +1135,43 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.95</v>
+        <v>3.6</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>2.15</v>
       </c>
       <c r="O6" t="n">
-        <v>2.75</v>
+        <v>4.49</v>
       </c>
       <c r="P6" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.2</v>
+        <v>2.93</v>
       </c>
       <c r="R6" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="S6" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="T6" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="V6" t="n">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
         <v>1.57</v>
@@ -1180,28 +1180,28 @@
         <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD6" t="n">
         <v>1.08</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG6" t="n">
         <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46006.40625</v>
@@ -1373,70 +1373,70 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="P8" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.12</v>
+        <v>4.21</v>
       </c>
       <c r="R8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="T8" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="W8" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="AA8" t="n">
         <v>2.15</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="AD8" t="n">
         <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AF8" t="n">
         <v>1.72</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AH8" t="n">
         <v>1.9</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.45</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>5.25</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>6.7</v>
       </c>
       <c r="O10" t="n">
-        <v>2.8</v>
+        <v>1.73</v>
       </c>
       <c r="P10" t="n">
-        <v>2.24</v>
+        <v>2.56</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.42</v>
+        <v>1.21</v>
       </c>
       <c r="S10" t="n">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="T10" t="n">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="U10" t="n">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.14</v>
+        <v>5.35</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>2.65</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.26</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AF10" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.61</v>
+        <v>3.35</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,37 +1730,37 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
-        <v>5.55</v>
+        <v>5.9</v>
       </c>
       <c r="N11" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.97</v>
+        <v>7.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="T11" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="U11" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="V11" t="n">
-        <v>4.55</v>
+        <v>4.75</v>
       </c>
       <c r="W11" t="n">
         <v>1.13</v>
@@ -1769,34 +1769,34 @@
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.33</v>
+        <v>4.48</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.27</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>9.75</v>
+        <v>3.15</v>
       </c>
       <c r="O12" t="n">
-        <v>1.65</v>
+        <v>3.06</v>
       </c>
       <c r="P12" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>3.34</v>
+        <v>2.53</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="Z12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.5</v>
+        <v>1.68</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.33</v>
+        <v>3.54</v>
       </c>
       <c r="AD12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.57</v>
       </c>
-      <c r="AE12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>4.26</v>
-      </c>
       <c r="AI12" s="3" t="n">
-        <v>46006.58333333334</v>
+        <v>46006.60416666666</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,76 +1968,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>12</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>5.9</v>
       </c>
       <c r="N13" t="n">
-        <v>3.15</v>
+        <v>1.15</v>
       </c>
       <c r="O13" t="n">
-        <v>3.06</v>
+        <v>6.45</v>
       </c>
       <c r="P13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.17</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.7</v>
-      </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="V13" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.68</v>
+        <v>2.59</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.54</v>
+        <v>1.86</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.84</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.57</v>
+        <v>1.1</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46006.60416666666</v>
+        <v>46006.64583333334</v>
       </c>
     </row>
     <row r="14">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="M14" t="n">
-        <v>5.9</v>
+        <v>3.56</v>
       </c>
       <c r="N14" t="n">
-        <v>1.15</v>
+        <v>1.61</v>
       </c>
       <c r="O14" t="n">
-        <v>6.45</v>
+        <v>4.66</v>
       </c>
       <c r="P14" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>3.42</v>
+        <v>2.8</v>
       </c>
       <c r="T14" t="n">
-        <v>2.17</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>4.6</v>
+        <v>6.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.44</v>
+        <v>1.94</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.59</v>
+        <v>1.76</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.86</v>
+        <v>3.28</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.84</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,40 +2206,40 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.6</v>
+        <v>1.48</v>
       </c>
       <c r="M15" t="n">
-        <v>3.56</v>
+        <v>3.95</v>
       </c>
       <c r="N15" t="n">
-        <v>1.61</v>
+        <v>7.3</v>
       </c>
       <c r="O15" t="n">
-        <v>4.66</v>
+        <v>2.02</v>
       </c>
       <c r="P15" t="n">
         <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.25</v>
+        <v>7.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>6.75</v>
+        <v>7.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
@@ -2248,34 +2248,34 @@
         <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>2.22</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.16</v>
+        <v>2.77</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46006.64583333334</v>
+        <v>46006.65625</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,37 +2325,37 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="M16" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>7.3</v>
+        <v>4.89</v>
       </c>
       <c r="O16" t="n">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.1</v>
+        <v>4.95</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T16" t="n">
-        <v>3.02</v>
+        <v>2.83</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V16" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="W16" t="n">
         <v>1.03</v>
@@ -2364,37 +2364,37 @@
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH16" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>2.77</v>
-      </c>
       <c r="AI16" s="3" t="n">
-        <v>46006.65625</v>
+        <v>46006.6875</v>
       </c>
     </row>
     <row r="17">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.25</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
-        <v>2.94</v>
+        <v>3.83</v>
       </c>
       <c r="N17" t="n">
-        <v>2.22</v>
+        <v>7.7</v>
       </c>
       <c r="O17" t="n">
-        <v>3.75</v>
+        <v>1.95</v>
       </c>
       <c r="P17" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>9.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.24</v>
+        <v>2.8</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.41</v>
+        <v>3.25</v>
       </c>
       <c r="M18" t="n">
-        <v>3.83</v>
+        <v>2.94</v>
       </c>
       <c r="N18" t="n">
-        <v>7.7</v>
+        <v>2.22</v>
       </c>
       <c r="O18" t="n">
-        <v>1.95</v>
+        <v>3.75</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.4</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V18" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z18" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="AB18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF18" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AG18" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.8</v>
+        <v>1.24</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.47</v>
+        <v>1.44</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="O19" t="n">
-        <v>3.8</v>
+        <v>1.91</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.73</v>
+        <v>6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>2.45</v>
+        <v>3.32</v>
       </c>
       <c r="T19" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="V19" t="n">
-        <v>9</v>
+        <v>5.75</v>
       </c>
       <c r="W19" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE19" t="n">
         <v>2</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.28</v>
+        <v>2.72</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.58</v>
+        <v>3.49</v>
       </c>
       <c r="M20" t="n">
-        <v>3.59</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>2.09</v>
+        <v>3.96</v>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.95</v>
+        <v>2.62</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="T20" t="n">
-        <v>2.72</v>
+        <v>3.2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X20" t="n">
         <v>1.08</v>
       </c>
-      <c r="X20" t="n">
-        <v>1</v>
-      </c>
       <c r="Y20" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AB20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AG20" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.97</v>
+        <v>1.22</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,76 +2920,76 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R21" t="n">
         <v>1.44</v>
       </c>
-      <c r="M21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>6</v>
-      </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V21" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.33</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AH21" t="n">
-        <v>2.72</v>
+        <v>1.67</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46006.6875</v>
+        <v>46006.69791666666</v>
       </c>
     </row>
     <row r="22">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>3.41</v>
       </c>
       <c r="N23" t="n">
-        <v>3.62</v>
+        <v>3.92</v>
       </c>
       <c r="O23" t="n">
-        <v>2.91</v>
+        <v>2.4</v>
       </c>
       <c r="P23" t="n">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="S23" t="n">
-        <v>2.66</v>
+        <v>2.89</v>
       </c>
       <c r="T23" t="n">
-        <v>3.18</v>
+        <v>2.69</v>
       </c>
       <c r="U23" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="V23" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
         <v>1.05</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,76 +3277,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.75</v>
+        <v>3.55</v>
       </c>
       <c r="M24" t="n">
-        <v>3.41</v>
+        <v>3.27</v>
       </c>
       <c r="N24" t="n">
-        <v>3.92</v>
+        <v>2.07</v>
       </c>
       <c r="O24" t="n">
-        <v>2.4</v>
+        <v>3.65</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>2.97</v>
       </c>
       <c r="R24" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="T24" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="V24" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.77</v>
+        <v>2.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.98</v>
+        <v>3.85</v>
       </c>
       <c r="AD24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE24" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.98</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46006.69791666666</v>
+        <v>46006.70833333334</v>
       </c>
     </row>
     <row r="25">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,76 +3634,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.55</v>
+        <v>1.16</v>
       </c>
       <c r="M27" t="n">
-        <v>3.27</v>
+        <v>7.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.07</v>
+        <v>15</v>
       </c>
       <c r="O27" t="n">
-        <v>3.65</v>
+        <v>1.57</v>
       </c>
       <c r="P27" t="n">
-        <v>2.1</v>
+        <v>2.73</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.97</v>
+        <v>12</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>2.81</v>
+        <v>3.42</v>
       </c>
       <c r="T27" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="U27" t="n">
-        <v>1.31</v>
+        <v>1.56</v>
       </c>
       <c r="V27" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="Z27" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.03</v>
+        <v>1.55</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.85</v>
+        <v>2.37</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.27</v>
+        <v>1.55</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.85</v>
+        <v>2.46</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.84</v>
+        <v>1.56</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.36</v>
+        <v>5.45</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46006.70833333334</v>
+        <v>46006.73958333334</v>
       </c>
     </row>
     <row r="28">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,76 +3753,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.16</v>
+        <v>14</v>
       </c>
       <c r="M28" t="n">
-        <v>7.1</v>
+        <v>5.8</v>
       </c>
       <c r="N28" t="n">
-        <v>15</v>
+        <v>1.15</v>
       </c>
       <c r="O28" t="n">
-        <v>1.57</v>
+        <v>17</v>
       </c>
       <c r="P28" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>12</v>
+        <v>1.4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>3.42</v>
+        <v>3.12</v>
       </c>
       <c r="T28" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="U28" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="V28" t="n">
         <v>5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X28" t="n">
         <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>2.07</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AH28" t="n">
-        <v>5.45</v>
+        <v>1.01</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46006.73958333334</v>
+        <v>46006.79166666666</v>
       </c>
     </row>
     <row r="29">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,194 +3872,75 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>14</v>
+        <v>2.9</v>
       </c>
       <c r="M29" t="n">
-        <v>5.8</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>1.15</v>
+        <v>2.3</v>
       </c>
       <c r="O29" t="n">
-        <v>17</v>
+        <v>3.25</v>
       </c>
       <c r="P29" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>2.29</v>
+        <v>2.52</v>
       </c>
       <c r="U29" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.07</v>
+        <v>1.79</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.8</v>
+        <v>1.62</v>
       </c>
       <c r="AF29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.36</v>
       </c>
-      <c r="AG29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AI29" s="3" t="n">
-        <v>46006.79166666666</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>46006</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Arnett Gardens</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Montego Bay United</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O30" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V30" t="n">
-        <v>6</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI30" s="3" t="n">
         <v>46006.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI29"/>
+  <dimension ref="A1:AI30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -642,20 +642,20 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -778,49 +778,49 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="M3" t="n">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="N3" t="n">
-        <v>4.4</v>
+        <v>3.98</v>
       </c>
       <c r="O3" t="n">
-        <v>2.82</v>
+        <v>3.25</v>
       </c>
       <c r="P3" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="S3" t="n">
-        <v>2.07</v>
+        <v>1.89</v>
       </c>
       <c r="T3" t="n">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="V3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="W3" t="n">
         <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="Z3" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AA3" t="n">
         <v>3.04</v>
@@ -829,22 +829,22 @@
         <v>1.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
         <v>1.04</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.57</v>
+        <v>2.68</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46006.39583333334</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="M4" t="n">
-        <v>2.95</v>
+        <v>2.71</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="O4" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P4" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="S4" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="T4" t="n">
-        <v>3.82</v>
+        <v>4.33</v>
       </c>
       <c r="U4" t="n">
         <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>8.6</v>
+        <v>15</v>
       </c>
       <c r="W4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.04</v>
       </c>
-      <c r="X4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AE4" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46006.40625</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>11</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S5" t="n">
         <v>2.15</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>7.24</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.1</v>
-      </c>
       <c r="T5" t="n">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="U5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X5" t="n">
         <v>1.15</v>
       </c>
-      <c r="V5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.09</v>
-      </c>
       <c r="Y5" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.94</v>
+        <v>1.74</v>
       </c>
       <c r="AB5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.35</v>
       </c>
-      <c r="AC5" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AG5" t="n">
+      <c r="AH5" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.99</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46006.40625</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.6</v>
+        <v>1.86</v>
       </c>
       <c r="M6" t="n">
-        <v>2.85</v>
+        <v>2.38</v>
       </c>
       <c r="N6" t="n">
-        <v>2.15</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
-        <v>4.49</v>
+        <v>2.7</v>
       </c>
       <c r="P6" t="n">
         <v>1.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.93</v>
+        <v>5.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="S6" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="V6" t="n">
-        <v>8.9</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
         <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="Z6" t="n">
         <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.27</v>
+        <v>2.4</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46006.40625</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1263,28 +1263,28 @@
         <v>2.1</v>
       </c>
       <c r="O7" t="n">
-        <v>5.09</v>
+        <v>4.6</v>
       </c>
       <c r="P7" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="R7" t="n">
         <v>1.62</v>
       </c>
       <c r="S7" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="T7" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="U7" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="V7" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="W7" t="n">
         <v>1.03</v>
@@ -1305,25 +1305,25 @@
         <v>1.32</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>46006.47916666666</v>
+        <v>46006.5</v>
       </c>
     </row>
     <row r="8">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="O8" t="n">
         <v>2.41</v>
@@ -1421,7 +1421,7 @@
         <v>2.15</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC8" t="n">
         <v>3.76</v>
@@ -1501,25 +1501,25 @@
         <v>3.47</v>
       </c>
       <c r="O9" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
-        <v>2.65</v>
+        <v>3.02</v>
       </c>
       <c r="T9" t="n">
-        <v>2.69</v>
+        <v>2.89</v>
       </c>
       <c r="U9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="V9" t="n">
         <v>6.5</v>
@@ -1528,13 +1528,13 @@
         <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="AA9" t="n">
         <v>1.77</v>
@@ -1546,19 +1546,19 @@
         <v>2.97</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46006.52083333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="M10" t="n">
-        <v>5.25</v>
+        <v>5.9</v>
       </c>
       <c r="N10" t="n">
-        <v>6.7</v>
+        <v>10.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="P10" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.6</v>
+        <v>7.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S10" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>2.05</v>
+        <v>2.21</v>
       </c>
       <c r="U10" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="V10" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="W10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.35</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
         <v>1.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.35</v>
+        <v>4.48</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.26</v>
+        <v>2.45</v>
       </c>
       <c r="M11" t="n">
-        <v>5.9</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>10.5</v>
+        <v>2.75</v>
       </c>
       <c r="O11" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.65</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>2.22</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.48</v>
+        <v>1.61</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
       <c r="N12" t="n">
-        <v>3.15</v>
+        <v>6.7</v>
       </c>
       <c r="O12" t="n">
-        <v>3.06</v>
+        <v>1.73</v>
       </c>
       <c r="P12" t="n">
-        <v>2.17</v>
+        <v>2.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.46</v>
+        <v>1.21</v>
       </c>
       <c r="S12" t="n">
-        <v>2.53</v>
+        <v>3.75</v>
       </c>
       <c r="T12" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="W12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.02</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y12" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="Z12" t="n">
-        <v>3</v>
+        <v>5.35</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.68</v>
+        <v>2.65</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.54</v>
+        <v>2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.57</v>
+        <v>3.35</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46006.60416666666</v>
+        <v>46006.58333333334</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,76 +1968,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>12</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>5.9</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>1.15</v>
+        <v>3.15</v>
       </c>
       <c r="O13" t="n">
-        <v>6.45</v>
+        <v>2.88</v>
       </c>
       <c r="P13" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.75</v>
+        <v>3.6</v>
       </c>
       <c r="R13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.25</v>
       </c>
-      <c r="S13" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AE13" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
         <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.1</v>
+        <v>1.62</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46006.64583333334</v>
+        <v>46006.60416666666</v>
       </c>
     </row>
     <row r="14">
@@ -2096,25 +2096,25 @@
         <v>1.61</v>
       </c>
       <c r="O14" t="n">
-        <v>4.66</v>
+        <v>4.78</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
         <v>2.8</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V14" t="n">
         <v>6.75</v>
@@ -2129,7 +2129,7 @@
         <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA14" t="n">
         <v>1.94</v>
@@ -2141,19 +2141,19 @@
         <v>3.28</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF14" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sporting Braga</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,76 +2206,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.48</v>
+        <v>12</v>
       </c>
       <c r="M15" t="n">
-        <v>3.95</v>
+        <v>5.9</v>
       </c>
       <c r="N15" t="n">
-        <v>7.3</v>
+        <v>1.15</v>
       </c>
       <c r="O15" t="n">
-        <v>2.02</v>
+        <v>6.45</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.1</v>
+        <v>1.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>3.42</v>
       </c>
       <c r="T15" t="n">
-        <v>3.02</v>
+        <v>2.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="V15" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>2.59</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.54</v>
+        <v>1.86</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.84</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.22</v>
+        <v>1.73</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.77</v>
+        <v>1.1</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46006.65625</v>
+        <v>46006.64583333334</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Sporting Braga</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,37 +2325,37 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="N16" t="n">
-        <v>4.89</v>
+        <v>7.3</v>
       </c>
       <c r="O16" t="n">
-        <v>2.23</v>
+        <v>2.01</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.95</v>
+        <v>5.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>2.83</v>
+        <v>2.94</v>
       </c>
       <c r="U16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="W16" t="n">
         <v>1.03</v>
@@ -2364,37 +2364,37 @@
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
         <v>3.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AD16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.24</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH16" t="n">
-        <v>2.1</v>
+        <v>2.79</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46006.6875</v>
+        <v>46006.65625</v>
       </c>
     </row>
     <row r="17">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>3.25</v>
       </c>
       <c r="M17" t="n">
-        <v>3.83</v>
+        <v>2.94</v>
       </c>
       <c r="N17" t="n">
-        <v>7.7</v>
+        <v>2.22</v>
       </c>
       <c r="O17" t="n">
-        <v>1.95</v>
+        <v>3.57</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="T17" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="V17" t="n">
-        <v>7.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
         <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.87</v>
+        <v>2.66</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.25</v>
+        <v>1.41</v>
       </c>
       <c r="M18" t="n">
-        <v>2.94</v>
+        <v>3.83</v>
       </c>
       <c r="N18" t="n">
-        <v>2.22</v>
+        <v>7.7</v>
       </c>
       <c r="O18" t="n">
-        <v>3.75</v>
+        <v>1.95</v>
       </c>
       <c r="P18" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="S18" t="n">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="U18" t="n">
         <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>9.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.62</v>
+        <v>2.87</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.4</v>
+        <v>3.68</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.24</v>
+        <v>2.21</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V19" t="n">
+        <v>9</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.44</v>
       </c>
-      <c r="M19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>6</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
+      <c r="Z19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.22</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>2.72</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.49</v>
+        <v>1.44</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="O20" t="n">
-        <v>3.96</v>
+        <v>1.91</v>
       </c>
       <c r="P20" t="n">
-        <v>1.94</v>
+        <v>2.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.62</v>
+        <v>6.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>2.45</v>
+        <v>3.04</v>
       </c>
       <c r="T20" t="n">
-        <v>3.2</v>
+        <v>2.53</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
         <v>1.05</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y20" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.35</v>
+        <v>1.77</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.15</v>
+        <v>2.71</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.22</v>
+        <v>2.84</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,76 +2920,76 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.2</v>
+        <v>1.58</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.59</v>
       </c>
       <c r="N21" t="n">
-        <v>3.45</v>
+        <v>5.3</v>
       </c>
       <c r="O21" t="n">
-        <v>2.63</v>
+        <v>2.23</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.9</v>
+        <v>4.95</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="T21" t="n">
-        <v>3.18</v>
+        <v>2.83</v>
       </c>
       <c r="U21" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="V21" t="n">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="W21" t="n">
         <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.86</v>
+        <v>3.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>46006.69791666666</v>
+        <v>46006.6875</v>
       </c>
     </row>
     <row r="22">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.6</v>
+        <v>2.11</v>
       </c>
       <c r="M22" t="n">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>3.62</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.63</v>
+        <v>3.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>2.69</v>
+        <v>2.44</v>
       </c>
       <c r="T22" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="U22" t="n">
         <v>1.32</v>
       </c>
       <c r="V22" t="n">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W22" t="n">
         <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.76</v>
+        <v>3.86</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3167,40 +3167,40 @@
         <v>3.92</v>
       </c>
       <c r="O23" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="R23" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S23" t="n">
-        <v>2.89</v>
+        <v>3.25</v>
       </c>
       <c r="T23" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="U23" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="V23" t="n">
-        <v>6.25</v>
+        <v>6.05</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
         <v>1.26</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA23" t="n">
         <v>1.77</v>
@@ -3209,22 +3209,22 @@
         <v>1.93</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AD23" t="n">
         <v>1.36</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AF23" t="n">
         <v>2.16</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,76 +3277,76 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.27</v>
+        <v>3.04</v>
       </c>
       <c r="N24" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="O24" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.97</v>
+        <v>2.63</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S24" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="U24" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>46006.70833333334</v>
+        <v>46006.69791666666</v>
       </c>
     </row>
     <row r="25">
@@ -3405,40 +3405,40 @@
         <v>3.85</v>
       </c>
       <c r="O25" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="P25" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="Q25" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="R25" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S25" t="n">
         <v>3.54</v>
       </c>
       <c r="T25" t="n">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="U25" t="n">
         <v>1.62</v>
       </c>
       <c r="V25" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="W25" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X25" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
         <v>1.15</v>
       </c>
       <c r="Z25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AA25" t="n">
         <v>1.6</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.62</v>
+        <v>3.55</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="N26" t="n">
-        <v>2.68</v>
+        <v>2.07</v>
       </c>
       <c r="O26" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P26" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>2.84</v>
+        <v>2.65</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="U26" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="V26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.45</v>
+        <v>2.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,76 +3634,76 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.16</v>
+        <v>2.58</v>
       </c>
       <c r="M27" t="n">
-        <v>7.1</v>
+        <v>3.35</v>
       </c>
       <c r="N27" t="n">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="O27" t="n">
-        <v>1.57</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.73</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>12</v>
+        <v>3.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>3.42</v>
+        <v>2.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2.34</v>
+        <v>2.84</v>
       </c>
       <c r="U27" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="V27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.37</v>
+        <v>3.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.46</v>
+        <v>1.73</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.56</v>
+        <v>2.03</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="AH27" t="n">
-        <v>5.45</v>
+        <v>1.5</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46006.73958333334</v>
+        <v>46006.70833333334</v>
       </c>
     </row>
     <row r="28">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,76 +3753,76 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>14</v>
+        <v>1.16</v>
       </c>
       <c r="M28" t="n">
-        <v>5.8</v>
+        <v>7.1</v>
       </c>
       <c r="N28" t="n">
-        <v>1.15</v>
+        <v>15</v>
       </c>
       <c r="O28" t="n">
-        <v>17</v>
+        <v>1.58</v>
       </c>
       <c r="P28" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.4</v>
+        <v>9.26</v>
       </c>
       <c r="R28" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>3.12</v>
+        <v>3.42</v>
       </c>
       <c r="T28" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="U28" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="V28" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="W28" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X28" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.07</v>
+        <v>1.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AI28" s="3" t="n">
-        <v>46006.79166666666</v>
+        <v>46006.73958333334</v>
       </c>
     </row>
     <row r="29">
@@ -3831,116 +3831,235 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Spanish Town Police FC</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>14</v>
+      </c>
+      <c r="M29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O29" t="n">
+        <v>15</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V29" t="n">
+        <v>5</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AI29" s="3" t="n">
+        <v>46006.79166666666</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Arnett Gardens</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Montego Bay United</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="inlineStr">
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L29" t="n">
+      <c r="L30" t="n">
         <v>2.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M30" t="n">
         <v>3.3</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N30" t="n">
         <v>2.3</v>
       </c>
-      <c r="O29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T29" t="n">
+      <c r="O30" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T30" t="n">
         <v>2.52</v>
       </c>
-      <c r="U29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V29" t="n">
+      <c r="U30" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V30" t="n">
         <v>6</v>
       </c>
-      <c r="W29" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X29" t="n">
+      <c r="W30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X30" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="Y30" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="Z30" t="n">
         <v>3.6</v>
       </c>
-      <c r="AA29" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD29" t="n">
+      <c r="AA30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AD30" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI29" s="3" t="n">
+      <c r="AE30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI30" s="3" t="n">
         <v>46006.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -764,17 +764,17 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -880,20 +880,20 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -999,20 +999,20 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1118,20 +1118,20 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="M7" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="N7" t="n">
         <v>2.1</v>
       </c>
       <c r="O7" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="R7" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="S7" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="V7" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.09</v>
+        <v>3.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46006.5</v>
@@ -1492,58 +1492,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="N9" t="n">
-        <v>3.47</v>
+        <v>3.63</v>
       </c>
       <c r="O9" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="P9" t="n">
         <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U9" t="n">
         <v>1.39</v>
       </c>
-      <c r="S9" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.4</v>
-      </c>
       <c r="V9" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AD9" t="n">
         <v>1.3</v>
@@ -1552,13 +1552,13 @@
         <v>1.73</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46006.52083333334</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="M10" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="N10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="O10" t="n">
         <v>1.65</v>
@@ -1635,10 +1635,10 @@
         <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="U10" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="V10" t="n">
         <v>4.75</v>
@@ -1650,7 +1650,7 @@
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z10" t="n">
         <v>5</v>
@@ -1659,13 +1659,13 @@
         <v>1.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE10" t="n">
         <v>1.85</v>
@@ -1677,7 +1677,7 @@
         <v>1.12</v>
       </c>
       <c r="AH10" t="n">
-        <v>4.48</v>
+        <v>4.55</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="R11" t="n">
         <v>1.4</v>
@@ -1754,19 +1754,19 @@
         <v>2.75</v>
       </c>
       <c r="T11" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V11" t="n">
         <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
         <v>1.28</v>
@@ -1775,10 +1775,10 @@
         <v>3.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AC11" t="n">
         <v>3.1</v>
@@ -1790,13 +1790,13 @@
         <v>1.65</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.22</v>
+        <v>2.17</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z12" t="n">
         <v>5.25</v>
       </c>
-      <c r="N12" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>5.35</v>
-      </c>
       <c r="AA12" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.35</v>
+        <v>3.04</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="M13" t="n">
         <v>3.2</v>
@@ -1986,10 +1986,10 @@
         <v>3.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="T13" t="n">
         <v>3.04</v>
@@ -1998,43 +1998,43 @@
         <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>6.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AC13" t="n">
         <v>3.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46006.60416666666</v>
@@ -2087,64 +2087,64 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.6</v>
+        <v>5.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.56</v>
+        <v>3.75</v>
       </c>
       <c r="N14" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="O14" t="n">
-        <v>4.78</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="T14" t="n">
-        <v>3.03</v>
+        <v>2.6</v>
       </c>
       <c r="U14" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
         <v>6.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.94</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.95</v>
       </c>
       <c r="AF14" t="n">
         <v>1.85</v>
@@ -2153,7 +2153,7 @@
         <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2325,22 +2325,22 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M16" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="N16" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="O16" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="P16" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="R16" t="n">
         <v>1.41</v>
@@ -2364,34 +2364,34 @@
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="AD16" t="n">
         <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.79</v>
+        <v>2.95</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46006.65625</v>
@@ -2801,61 +2801,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="N20" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="P20" t="n">
         <v>2.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>6.6</v>
+        <v>6.95</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>3.04</v>
+        <v>3.22</v>
       </c>
       <c r="T20" t="n">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="U20" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE20" t="n">
         <v>1.91</v>
@@ -2864,10 +2864,10 @@
         <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.84</v>
+        <v>3.13</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="M22" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>3.62</v>
+        <v>3.45</v>
       </c>
       <c r="O22" t="n">
         <v>2.63</v>
@@ -3057,49 +3057,49 @@
         <v>3.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S22" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T22" t="n">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="U22" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V22" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
         <v>1.08</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.86</v>
+        <v>4.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG22" t="n">
         <v>1.33</v>
@@ -3158,58 +3158,58 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="M23" t="n">
-        <v>3.41</v>
+        <v>3.75</v>
       </c>
       <c r="N23" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="P23" t="n">
         <v>2.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.94</v>
+        <v>4.78</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S23" t="n">
-        <v>3.25</v>
+        <v>2.89</v>
       </c>
       <c r="T23" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="U23" t="n">
         <v>1.43</v>
       </c>
       <c r="V23" t="n">
-        <v>6.05</v>
+        <v>6.1</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
         <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AD23" t="n">
         <v>1.36</v>
@@ -3224,7 +3224,7 @@
         <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="M25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N25" t="n">
         <v>4</v>
       </c>
-      <c r="N25" t="n">
-        <v>3.85</v>
-      </c>
       <c r="O25" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="Q25" t="n">
         <v>3.9</v>
       </c>
       <c r="R25" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="T25" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="U25" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="V25" t="n">
-        <v>4.95</v>
+        <v>4.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X25" t="n">
         <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z25" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG25" t="n">
         <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3634,22 +3634,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="M27" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="O27" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P27" t="n">
         <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
         <v>1.4</v>
@@ -3661,46 +3661,46 @@
         <v>2.84</v>
       </c>
       <c r="U27" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="W27" t="n">
         <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="Z27" t="n">
         <v>3.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="AB27" t="n">
         <v>1.83</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AE27" t="n">
         <v>1.73</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3753,37 +3753,37 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="M28" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="N28" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="O28" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="P28" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>9.26</v>
+        <v>12</v>
       </c>
       <c r="R28" t="n">
         <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>3.42</v>
+        <v>3.75</v>
       </c>
       <c r="T28" t="n">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="U28" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V28" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="W28" t="n">
         <v>1.11</v>
@@ -3795,25 +3795,25 @@
         <v>1.18</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AB28" t="n">
         <v>2.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AE28" t="n">
         <v>2.25</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AG28" t="n">
         <v>1.11</v>
@@ -3881,61 +3881,61 @@
         <v>1.15</v>
       </c>
       <c r="O29" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="P29" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="R29" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="S29" t="n">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="T29" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="U29" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="V29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W29" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X29" t="n">
         <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AH29" t="n">
         <v>1.01</v>
@@ -3991,34 +3991,34 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="M30" t="n">
         <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O30" t="n">
-        <v>3.49</v>
+        <v>3.25</v>
       </c>
       <c r="P30" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="R30" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="T30" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="U30" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="V30" t="n">
         <v>6</v>
@@ -4030,34 +4030,34 @@
         <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="AD30" t="n">
         <v>1.33</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46006.89583333334</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,99 +1228,99 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.4</v>
+        <v>1.73</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7</v>
+        <v>3.24</v>
       </c>
       <c r="N7" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA7" t="n">
         <v>2.1</v>
       </c>
-      <c r="O7" t="n">
-        <v>5</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="AB7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1.75</v>
       </c>
-      <c r="Q7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="V7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AG7" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.18</v>
+        <v>1.89</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46006.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,99 +1347,99 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>5</v>
+      </c>
+      <c r="P8" t="n">
         <v>1.75</v>
       </c>
-      <c r="M8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.01</v>
-      </c>
       <c r="Q8" t="n">
-        <v>4.21</v>
+        <v>2.9</v>
       </c>
       <c r="R8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="V8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.44</v>
       </c>
-      <c r="S8" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V8" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.9</v>
+        <v>1.18</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46006.5</v>
@@ -1475,20 +1475,20 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,99 +1585,99 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.22</v>
       </c>
-      <c r="M10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N10" t="n">
-        <v>11</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.23</v>
-      </c>
       <c r="S10" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="V10" t="n">
-        <v>4.75</v>
+        <v>4.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.15</v>
       </c>
-      <c r="Z10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AH10" t="n">
-        <v>4.55</v>
+        <v>3.04</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,99 +1704,99 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.25</v>
+        <v>1.22</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>11</v>
       </c>
       <c r="O11" t="n">
-        <v>2.8</v>
+        <v>1.65</v>
       </c>
       <c r="P11" t="n">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.44</v>
+        <v>7.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>2.75</v>
+        <v>3.58</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>2.23</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="W11" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.93</v>
+        <v>2.74</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.65</v>
+        <v>4.55</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.34</v>
+        <v>2.25</v>
       </c>
       <c r="M12" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>7.66</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.75</v>
+        <v>3.44</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.43</v>
+        <v>1.89</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.8</v>
+        <v>1.93</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.02</v>
+        <v>3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.04</v>
+        <v>1.65</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.25</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.75</v>
+        <v>4.95</v>
       </c>
       <c r="N14" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>6.91</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.24</v>
+        <v>1.73</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6</v>
+        <v>2.02</v>
       </c>
       <c r="U14" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="V14" t="n">
-        <v>6.75</v>
+        <v>4.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.91</v>
+        <v>1.49</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.83</v>
+        <v>2.66</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.6</v>
+        <v>2.16</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>12</v>
+        <v>5.25</v>
       </c>
       <c r="M15" t="n">
-        <v>5.9</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="O15" t="n">
+        <v>5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.15</v>
-      </c>
-      <c r="O15" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.1</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.25</v>
+        <v>1.53</v>
       </c>
       <c r="M17" t="n">
-        <v>2.94</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>2.22</v>
+        <v>7.07</v>
       </c>
       <c r="O17" t="n">
-        <v>3.57</v>
+        <v>2.13</v>
       </c>
       <c r="P17" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.8</v>
+        <v>5.22</v>
       </c>
       <c r="R17" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>9.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>2.28</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.41</v>
+        <v>3.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.83</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>7.7</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.95</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V18" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.21</v>
+        <v>1.21</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.47</v>
+        <v>3.15</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="O19" t="n">
-        <v>3.96</v>
+        <v>3.57</v>
       </c>
       <c r="P19" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="R19" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="S19" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="T19" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V19" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AD19" t="n">
         <v>1.2</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.26</v>
+        <v>1.68</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.43</v>
+        <v>1.73</v>
       </c>
       <c r="M20" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>5.29</v>
       </c>
       <c r="O20" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.85</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V20" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AG20" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.13</v>
+        <v>2.06</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,61 +2920,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="M21" t="n">
-        <v>3.59</v>
+        <v>4.7</v>
       </c>
       <c r="N21" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="O21" t="n">
-        <v>2.23</v>
+        <v>1.85</v>
       </c>
       <c r="P21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V21" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB21" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q21" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V21" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC21" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AE21" t="n">
         <v>1.91</v>
@@ -2983,10 +2983,10 @@
         <v>1.8</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.1</v>
+        <v>3.13</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46006.6875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N22" t="n">
-        <v>3.45</v>
+        <v>1.99</v>
       </c>
       <c r="O22" t="n">
+        <v>4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q22" t="n">
         <v>2.63</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.9</v>
-      </c>
       <c r="R22" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="S22" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="T22" t="n">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="U22" t="n">
         <v>1.31</v>
       </c>
       <c r="V22" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="W22" t="n">
         <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AB22" t="n">
         <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="AD22" t="n">
         <v>1.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG22" t="n">
         <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="M23" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="O23" t="n">
-        <v>2.37</v>
+        <v>2.63</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.78</v>
+        <v>3.9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="S23" t="n">
-        <v>2.89</v>
+        <v>2.42</v>
       </c>
       <c r="T23" t="n">
-        <v>2.62</v>
+        <v>3.24</v>
       </c>
       <c r="U23" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="V23" t="n">
-        <v>6.1</v>
+        <v>8.4</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.8</v>
+        <v>2.82</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.75</v>
+        <v>2.33</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.85</v>
+        <v>4.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.16</v>
+        <v>1.83</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.6</v>
+        <v>1.88</v>
       </c>
       <c r="M24" t="n">
-        <v>3.04</v>
+        <v>3.75</v>
       </c>
       <c r="N24" t="n">
-        <v>1.95</v>
+        <v>4</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>2.37</v>
       </c>
       <c r="P24" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.63</v>
+        <v>4.78</v>
       </c>
       <c r="R24" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="T24" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="V24" t="n">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="W24" t="n">
         <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.74</v>
+        <v>2.85</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.79</v>
+        <v>2.16</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.25</v>
+        <v>2.02</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.82</v>
+        <v>2.62</v>
       </c>
       <c r="M25" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>2.68</v>
       </c>
       <c r="O25" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="P25" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="T25" t="n">
-        <v>2.1</v>
+        <v>2.84</v>
       </c>
       <c r="U25" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="V25" t="n">
-        <v>4.4</v>
+        <v>7.3</v>
       </c>
       <c r="W25" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.47</v>
+        <v>2.01</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.1</v>
+        <v>3.44</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.62</v>
+        <v>1.82</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="N27" t="n">
-        <v>2.68</v>
+        <v>4</v>
       </c>
       <c r="O27" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="T27" t="n">
-        <v>2.84</v>
+        <v>2.1</v>
       </c>
       <c r="U27" t="n">
-        <v>1.39</v>
+        <v>1.65</v>
       </c>
       <c r="V27" t="n">
-        <v>7.3</v>
+        <v>4.4</v>
       </c>
       <c r="W27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X27" t="n">
         <v>1.04</v>
       </c>
-      <c r="X27" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y27" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.01</v>
+        <v>1.47</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.83</v>
+        <v>2.63</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.44</v>
+        <v>2.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AF27" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46006.70833333334</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,99 +1585,99 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.34</v>
+        <v>2.25</v>
       </c>
       <c r="M10" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
-        <v>7.66</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="P10" t="n">
-        <v>2.7</v>
+        <v>2.13</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.75</v>
+        <v>3.44</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="V10" t="n">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.43</v>
+        <v>1.89</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.8</v>
+        <v>1.93</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.02</v>
+        <v>3.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.04</v>
+        <v>1.65</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,99 +1823,99 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.25</v>
+        <v>1.34</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>7.66</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="P12" t="n">
-        <v>2.13</v>
+        <v>2.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.44</v>
+        <v>5.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5</v>
+        <v>4.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.89</v>
+        <v>1.43</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.93</v>
+        <v>2.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.1</v>
+        <v>2.02</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.65</v>
+        <v>3.04</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,19 +2061,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2083,77 +2083,77 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>5.25</v>
       </c>
       <c r="M14" t="n">
-        <v>4.95</v>
+        <v>3.75</v>
       </c>
       <c r="N14" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="O14" t="n">
-        <v>6.91</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.73</v>
+        <v>2.24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="T14" t="n">
-        <v>2.02</v>
+        <v>2.6</v>
       </c>
       <c r="U14" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>4.5</v>
+        <v>6.75</v>
       </c>
       <c r="W14" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.66</v>
+        <v>1.83</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.16</v>
+        <v>3.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2202,77 +2202,77 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.25</v>
+        <v>8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>4.95</v>
       </c>
       <c r="N15" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>6.91</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.24</v>
+        <v>1.73</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="T15" t="n">
-        <v>2.6</v>
+        <v>2.02</v>
       </c>
       <c r="U15" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="V15" t="n">
-        <v>6.75</v>
+        <v>4.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.91</v>
+        <v>1.49</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.83</v>
+        <v>2.66</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.6</v>
+        <v>2.16</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.94</v>
+        <v>1.73</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2308,20 +2308,20 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,99 +2418,99 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>7.07</v>
+        <v>5.29</v>
       </c>
       <c r="O17" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.22</v>
+        <v>4.58</v>
       </c>
       <c r="R17" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="U17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.33</v>
       </c>
-      <c r="V17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE17" t="n">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,99 +2537,99 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="M18" t="n">
         <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="O18" t="n">
-        <v>4.01</v>
+        <v>3.57</v>
       </c>
       <c r="P18" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.65</v>
+        <v>2.92</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S18" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T18" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U18" t="n">
         <v>1.28</v>
       </c>
       <c r="V18" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>1.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.26</v>
+        <v>1.68</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,99 +2656,99 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.15</v>
+        <v>1.43</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="N19" t="n">
+        <v>8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V19" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB19" t="n">
         <v>2.25</v>
       </c>
-      <c r="O19" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V19" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AC19" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AF19" t="n">
         <v>1.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.68</v>
+        <v>1.08</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.3</v>
+        <v>3.13</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>5.29</v>
+        <v>7.07</v>
       </c>
       <c r="O20" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="P20" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.58</v>
+        <v>5.22</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S20" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="T20" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.38</v>
       </c>
-      <c r="V20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.34</v>
-      </c>
       <c r="Z20" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.14</v>
+        <v>3.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,99 +2894,99 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.43</v>
+        <v>3.5</v>
       </c>
       <c r="M21" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>1.85</v>
+        <v>4.01</v>
       </c>
       <c r="P21" t="n">
-        <v>2.45</v>
+        <v>2.04</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.95</v>
+        <v>2.65</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="S21" t="n">
-        <v>3.22</v>
+        <v>2.4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.39</v>
+        <v>3.4</v>
       </c>
       <c r="U21" t="n">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="V21" t="n">
-        <v>5.25</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.5</v>
+        <v>2.65</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.66</v>
+        <v>2.35</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.13</v>
+        <v>1.21</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46006.6875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,16 +3013,16 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="M22" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>1.99</v>
+        <v>3.45</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="P22" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.63</v>
+        <v>3.9</v>
       </c>
       <c r="R22" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="S22" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="T22" t="n">
-        <v>3.15</v>
+        <v>3.24</v>
       </c>
       <c r="U22" t="n">
         <v>1.31</v>
       </c>
       <c r="V22" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="W22" t="n">
         <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AB22" t="n">
         <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="AD22" t="n">
         <v>1.2</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG22" t="n">
         <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,99 +3132,99 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>3.45</v>
+        <v>1.99</v>
       </c>
       <c r="O23" t="n">
+        <v>4</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q23" t="n">
         <v>2.63</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.9</v>
-      </c>
       <c r="R23" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="S23" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="T23" t="n">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="U23" t="n">
         <v>1.31</v>
       </c>
       <c r="V23" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="W23" t="n">
         <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AB23" t="n">
         <v>1.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="AD23" t="n">
         <v>1.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AG23" t="n">
         <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3260,20 +3260,20 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="N25" t="n">
-        <v>2.68</v>
+        <v>2.15</v>
       </c>
       <c r="O25" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="P25" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V25" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AA25" t="n">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.44</v>
+        <v>3.78</v>
       </c>
       <c r="AD25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.44</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.55</v>
+        <v>1.82</v>
       </c>
       <c r="M26" t="n">
-        <v>3.27</v>
+        <v>4.2</v>
       </c>
       <c r="N26" t="n">
-        <v>2.07</v>
+        <v>4</v>
       </c>
       <c r="O26" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="P26" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T26" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.05</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="V26" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="X26" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.03</v>
+        <v>1.47</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>2.63</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.82</v>
+        <v>2.62</v>
       </c>
       <c r="M27" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>2.68</v>
       </c>
       <c r="O27" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="P27" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2.1</v>
+        <v>2.84</v>
       </c>
       <c r="U27" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="V27" t="n">
-        <v>4.4</v>
+        <v>7.3</v>
       </c>
       <c r="W27" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.47</v>
+        <v>2.01</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.1</v>
+        <v>3.44</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="M28" t="n">
-        <v>7.4</v>
+        <v>6.75</v>
       </c>
       <c r="N28" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="O28" t="n">
         <v>1.57</v>
@@ -3771,43 +3771,43 @@
         <v>12</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S28" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="T28" t="n">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="U28" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="V28" t="n">
-        <v>5</v>
+        <v>5.01</v>
       </c>
       <c r="W28" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="X28" t="n">
         <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AA28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.5</v>
       </c>
       <c r="AE28" t="n">
         <v>2.25</v>
@@ -3816,10 +3816,10 @@
         <v>1.6</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AH28" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46006.73958333334</v>
@@ -3917,10 +3917,10 @@
         <v>4.4</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.38</v>
+        <v>1.67</v>
       </c>
       <c r="AC29" t="n">
         <v>2.12</v>
@@ -3997,7 +3997,7 @@
         <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O30" t="n">
         <v>3.25</v>
@@ -4036,10 +4036,10 @@
         <v>3.58</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AC30" t="n">
         <v>3</v>

--- a/jogos_2025-12-15.xlsx
+++ b/jogos_2025-12-15.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,25 +1585,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.25</v>
+        <v>1.22</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>6.5</v>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>11</v>
       </c>
       <c r="O10" t="n">
-        <v>2.8</v>
+        <v>1.65</v>
       </c>
       <c r="P10" t="n">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.44</v>
+        <v>7.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="S10" t="n">
-        <v>2.75</v>
+        <v>3.58</v>
       </c>
       <c r="T10" t="n">
-        <v>2.75</v>
+        <v>2.23</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="V10" t="n">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="W10" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.89</v>
+        <v>1.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.93</v>
+        <v>2.74</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.65</v>
+        <v>4.55</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46006.58333333334</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,25 +1704,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.22</v>
+        <v>2.25</v>
       </c>
       <c r="M11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V11" t="n">
         <v>6.5</v>
       </c>
-      <c r="N11" t="n">
-        <v>11</v>
-      </c>
-      <c r="O11" t="n">
+      <c r="W11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.65</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="U11" t="n">
+      <c r="AF11" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.65</v>
-      </c>
-      <c r="V11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>4.55</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46006.58333333334</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,99 +2061,99 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O14" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF14" t="n">
         <v>2</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="O14" t="n">
-        <v>5</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V14" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,19 +2180,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>8</v>
+        <v>5.25</v>
       </c>
       <c r="M15" t="n">
-        <v>4.95</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="O15" t="n">
-        <v>6.91</v>
+        <v>5</v>
       </c>
       <c r="P15" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.73</v>
+        <v>2.24</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="T15" t="n">
-        <v>2.02</v>
+        <v>2.6</v>
       </c>
       <c r="U15" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="V15" t="n">
-        <v>4.5</v>
+        <v>6.75</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.49</v>
+        <v>1.91</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.66</v>
+        <v>1.83</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.16</v>
+        <v>3.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.73</v>
+        <v>1.94</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46006.64583333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,25 +2418,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>5.29</v>
+        <v>7.07</v>
       </c>
       <c r="O17" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="P17" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.58</v>
+        <v>5.22</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="T17" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.38</v>
       </c>
-      <c r="V17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.34</v>
-      </c>
       <c r="Z17" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.14</v>
+        <v>3.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46006.6875</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,22 +2537,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.15</v>
+        <v>1.73</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>2.25</v>
+        <v>5.29</v>
       </c>
       <c r="O18" t="n">
-        <v>3.57</v>
+        <v>2.17</v>
       </c>
       <c r="P18" t="n">
-        <v>1.89</v>
+        <v>2.12</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.92</v>
+        <v>4.58</v>
       </c>
       <c r="R18" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>3.3</v>
+        <v>2.62</v>
       </c>
       <c r="U18" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.68</v>
+        <v>1.19</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.3</v>
+        <v>2.06</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46006.6875</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,99 +2656,99 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M19" t="n">
         <v>3</v>
       </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M19" t="n">
-        <v>4.7</v>
-      </c>
       <c r="N19" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>1.85</v>
+        <v>4.01</v>
       </c>
       <c r="P19" t="n">
-        <v>2.45</v>
+        <v>2.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.95</v>
+        <v>2.65</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>3.22</v>
+        <v>2.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.39</v>
+        <v>3.4</v>
       </c>
       <c r="U19" t="n">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="V19" t="n">
-        <v>5.25</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.5</v>
+        <v>2.65</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.66</v>
+        <v>2.35</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.13</v>
+        <v>1.21</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46006.6875</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,99 +2775,99 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="N20" t="n">
-        <v>7.07</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.22</v>
+        <v>6.95</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>2.55</v>
+        <v>3.22</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>2.39</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="V20" t="n">
-        <v>7.8</v>
+        <v>5.25</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>1.66</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.58</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.28</v>
+        <v>3.13</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46006.6875</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,19 +2894,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="M21" t="n">
         <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="O21" t="n">
-        <v>4.01</v>
+        <v>3.57</v>
       </c>
       <c r="P21" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.65</v>
+        <v>2.92</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S21" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U21" t="n">
         <v>1.28</v>
       </c>
       <c r="V21" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
         <v>1.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.26</v>
+        <v>1.68</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46006.6875</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3028,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="N22" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>2.63</v>
+        <v>2.37</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.9</v>
+        <v>4.78</v>
       </c>
       <c r="R22" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
-        <v>2.42</v>
+        <v>2.89</v>
       </c>
       <c r="T22" t="n">
-        <v>3.24</v>
+        <v>2.62</v>
       </c>
       <c r="U22" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="V22" t="n">
-        <v>8.4</v>
+        <v>6.1</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.82</v>
+        <v>3.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,25 +3132,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="M23" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>1.99</v>
+        <v>3.45</v>
       </c>
       <c r="O23" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="P23" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.63</v>
+        <v>3.9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="T23" t="n">
-        <v>3.15</v>
+        <v>3.24</v>
       </c>
       <c r="U23" t="n">
         <v>1.31</v>
       </c>
       <c r="V23" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="W23" t="n">
         <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AB23" t="n">
         <v>1.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="AD23" t="n">
         <v>1.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG23" t="n">
         <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.29</v>
+        <v>1.67</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,25 +3251,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.88</v>
+        <v>3.75</v>
       </c>
       <c r="M24" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="N24" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O24" t="n">
         <v>4</v>
       </c>
-      <c r="O24" t="n">
-        <v>2.37</v>
-      </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.78</v>
+        <v>2.63</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="S24" t="n">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="U24" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="V24" t="n">
-        <v>6.1</v>
+        <v>9</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.85</v>
+        <v>3.84</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.16</v>
+        <v>1.79</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.02</v>
+        <v>1.29</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46006.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,99 +3370,99 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.5</v>
+        <v>1.82</v>
       </c>
       <c r="M25" t="n">
-        <v>3.21</v>
+        <v>4.2</v>
       </c>
       <c r="N25" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="P25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T25" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.17</v>
-      </c>
       <c r="U25" t="n">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="V25" t="n">
-        <v>8.4</v>
+        <v>4.4</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="X25" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="Z25" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.18</v>
+        <v>1.47</v>
       </c>
       <c r="AB25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC25" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE25" t="n">
-        <v>1.86</v>
+        <v>1.47</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.3</v>
+        <v>1.91</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,99 +3489,99 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.82</v>
+        <v>3.5</v>
       </c>
       <c r="M26" t="n">
-        <v>4.2</v>
+        <v>3.21</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>2.15</v>
       </c>
       <c r="O26" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="P26" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="S26" t="n">
-        <v>3.7</v>
+        <v>2.56</v>
       </c>
       <c r="T26" t="n">
-        <v>2.1</v>
+        <v>3.17</v>
       </c>
       <c r="U26" t="n">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="V26" t="n">
-        <v>4.4</v>
+        <v>8.4</v>
       </c>
       <c r="W26" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.63</v>
+        <v>1.67</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.1</v>
+        <v>3.78</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.47</v>
+        <v>1.86</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.91</v>
+        <v>1.3</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46006.70833333334</v>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -3736,20 +3736,20 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -3855,10 +3855,10 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -3881,61 +3881,61 @@
         <v>1.15</v>
       </c>
       <c r="O29" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="P29" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF29" t="n">
         <v>1.44</v>
       </c>
-      <c r="R29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V29" t="n">
-        <v>4</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AG29" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AH29" t="n">
         <v>1.01</v>
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="M30" t="n">
         <v>3.3</v>
       </c>
       <c r="N30" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC30" t="n">
         <v>2.25</v>
       </c>
-      <c r="O30" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V30" t="n">
-        <v>6</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>3</v>
-      </c>
       <c r="AD30" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46006.89583333334</v>
